--- a/Plantillas/Base Maestra/Maestra.xlsx
+++ b/Plantillas/Base Maestra/Maestra.xlsx
@@ -1,20 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47722A65-63B4-4E6A-8CF9-013C07D36876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -464,7 +476,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -557,40 +569,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -598,13 +583,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -627,75 +618,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -889,6 +811,75 @@
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -903,45 +894,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Maestra" displayName="Maestra" ref="A1:H102" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:H102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Maestra" displayName="Maestra" ref="A1:H102" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A1:H102" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="4" name="KeyPLU" dataDxfId="16">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="KeyPLU" dataDxfId="12">
       <calculatedColumnFormula>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="CLIENTE" dataDxfId="15"/>
-    <tableColumn id="7" name="SoldTO" dataDxfId="14"/>
-    <tableColumn id="9" name="Canal" dataDxfId="13"/>
-    <tableColumn id="6" name="EAN" dataDxfId="12"/>
-    <tableColumn id="3" name="GMID" dataDxfId="11"/>
-    <tableColumn id="5" name="PLU" dataDxfId="10"/>
-    <tableColumn id="1" name="PRODUCTO" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CLIENTE" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SoldTO" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canal" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EAN" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GMID" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="PLU" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MR" displayName="MR" ref="A1:C28" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:C28"/>
-  <sortState ref="A2:C47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MR" displayName="MR" ref="A1:C28" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C28" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C47">
     <sortCondition ref="B2:B47"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" name="Code" dataDxfId="6"/>
-    <tableColumn id="2" name="Reason (shift)" dataDxfId="5"/>
-    <tableColumn id="3" name="Definition" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Code" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Reason (shift)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Definition" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MR_4" displayName="MR_4" ref="A1:C28" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="MR_4" displayName="MR_4" ref="A1:C28" totalsRowShown="0" headerRowDxfId="18">
   <tableColumns count="3">
-    <tableColumn id="1" name="Code" dataDxfId="2"/>
-    <tableColumn id="2" name="Reason (shift)" dataDxfId="1"/>
-    <tableColumn id="3" name="Definition" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Code" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Reason (shift)" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Definition" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1209,7 +1200,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1914,13 +1905,13 @@
       <c r="E26" s="7">
         <v>3664798064728</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="4">
         <v>846778</v>
       </c>
       <c r="G26" s="5">
         <v>295750490</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1944,10 +1935,10 @@
       <c r="F27" s="3">
         <v>901077</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="5">
         <v>298200477</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="4" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1959,7 +1950,7 @@
       <c r="B28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="5">
         <v>100173499</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -1968,13 +1959,13 @@
       <c r="E28" s="3">
         <v>7703202221244</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="5">
         <v>782065</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="5">
         <v>11729</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1986,7 +1977,7 @@
       <c r="B29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="5">
         <v>100173499</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -1995,13 +1986,13 @@
       <c r="E29" s="3">
         <v>7703202221329</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="5">
         <v>782092</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="5">
         <v>11731</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2013,7 +2004,7 @@
       <c r="B30" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="5">
         <v>100173499</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -2022,13 +2013,13 @@
       <c r="E30" s="3">
         <v>7703202221305</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="5">
         <v>782086</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="5">
         <v>11732</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2040,7 +2031,7 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="5">
         <v>100173499</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -2049,13 +2040,13 @@
       <c r="E31" s="3">
         <v>7703202221312</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="5">
         <v>782091</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="5">
         <v>11733</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2067,7 +2058,7 @@
       <c r="B32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="5">
         <v>100173499</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -2076,13 +2067,13 @@
       <c r="E32" s="3">
         <v>7703202221169</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="5">
         <v>715503</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="5">
         <v>13221</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2094,7 +2085,7 @@
       <c r="B33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="5">
         <v>100173499</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -2103,13 +2094,13 @@
       <c r="E33" s="3">
         <v>7591044007191</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="5">
         <v>120786</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="5">
         <v>15124</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2121,7 +2112,7 @@
       <c r="B34" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="5">
         <v>100173499</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -2130,13 +2121,13 @@
       <c r="E34" s="3">
         <v>7591044009447</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="5">
         <v>120777</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="5">
         <v>15129</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2148,7 +2139,7 @@
       <c r="B35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="5">
         <v>100173499</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -2157,13 +2148,13 @@
       <c r="E35" s="3">
         <v>7703202221091</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="5">
         <v>797130</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="5">
         <v>21977</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2175,7 +2166,7 @@
       <c r="B36" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="5">
         <v>100173499</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -2184,13 +2175,13 @@
       <c r="E36" s="3">
         <v>7591044008952</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="5">
         <v>666269</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="5">
         <v>22878</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2202,7 +2193,7 @@
       <c r="B37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="5">
         <v>100173499</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -2211,13 +2202,13 @@
       <c r="E37" s="3">
         <v>7501165007956</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="5">
         <v>655678</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="5">
         <v>23893</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2229,7 +2220,7 @@
       <c r="B38" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="5">
         <v>100173499</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -2238,13 +2229,13 @@
       <c r="E38" s="3">
         <v>7591044401036</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="5">
         <v>723871</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="5">
         <v>25528</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2256,7 +2247,7 @@
       <c r="B39" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="5">
         <v>100173499</v>
       </c>
       <c r="D39" s="4" t="s">
@@ -2265,13 +2256,13 @@
       <c r="E39" s="3">
         <v>7591044009010</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="5">
         <v>732308</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="5">
         <v>25854</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2283,7 +2274,7 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="5">
         <v>100173499</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2292,13 +2283,13 @@
       <c r="E40" s="3">
         <v>7703202010329</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="5">
         <v>341667</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="5">
         <v>25860</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2310,7 +2301,7 @@
       <c r="B41" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="5">
         <v>100173499</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -2319,13 +2310,13 @@
       <c r="E41" s="3">
         <v>7703202221220</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="5">
         <v>781955</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="5">
         <v>26120</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2337,7 +2328,7 @@
       <c r="B42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="5">
         <v>100173499</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -2346,13 +2337,13 @@
       <c r="E42" s="3">
         <v>7703202221336</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="5">
         <v>782093</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="5">
         <v>46950</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="5" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2364,7 +2355,7 @@
       <c r="B43" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="5">
         <v>100173499</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -2373,13 +2364,13 @@
       <c r="E43" s="3">
         <v>3582910009900</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="5">
         <v>873229</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="5">
         <v>47409</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2391,7 +2382,7 @@
       <c r="B44" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="5">
         <v>100173499</v>
       </c>
       <c r="D44" s="4" t="s">
@@ -2400,13 +2391,13 @@
       <c r="E44" s="3">
         <v>7703202221275</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="5">
         <v>782074</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="5">
         <v>47598</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2418,7 +2409,7 @@
       <c r="B45" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="5">
         <v>100173499</v>
       </c>
       <c r="D45" s="4" t="s">
@@ -2427,13 +2418,13 @@
       <c r="E45" s="3">
         <v>7703202221176</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="5">
         <v>715717</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="5">
         <v>50348</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2445,7 +2436,7 @@
       <c r="B46" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="5">
         <v>100173499</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -2454,13 +2445,13 @@
       <c r="E46" s="3">
         <v>7703381002146</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="5">
         <v>715717</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="5">
         <v>50348</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2472,7 +2463,7 @@
       <c r="B47" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="5">
         <v>100173499</v>
       </c>
       <c r="D47" s="4" t="s">
@@ -2481,13 +2472,13 @@
       <c r="E47" s="3">
         <v>7703202221152</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="5">
         <v>715506</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="5">
         <v>58826</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2499,7 +2490,7 @@
       <c r="B48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="5">
         <v>100173499</v>
       </c>
       <c r="D48" s="4" t="s">
@@ -2508,13 +2499,13 @@
       <c r="E48" s="3">
         <v>7795312100090</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="5">
         <v>785678</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="5">
         <v>68585</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="5" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2526,7 +2517,7 @@
       <c r="B49" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="5">
         <v>100173499</v>
       </c>
       <c r="D49" s="4" t="s">
@@ -2535,13 +2526,13 @@
       <c r="E49" s="3">
         <v>7703202221800</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="5">
         <v>893499</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="5">
         <v>84797</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2553,7 +2544,7 @@
       <c r="B50" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="5">
         <v>100173499</v>
       </c>
       <c r="D50" s="4" t="s">
@@ -2562,13 +2553,13 @@
       <c r="E50" s="3">
         <v>7703202221381</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="5">
         <v>782089</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="5">
         <v>100904</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="5" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2580,7 +2571,7 @@
       <c r="B51" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="5">
         <v>100173499</v>
       </c>
       <c r="D51" s="4" t="s">
@@ -2589,13 +2580,13 @@
       <c r="E51" s="3">
         <v>7703202221428</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="5">
         <v>782090</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="5">
         <v>100905</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="5" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2607,7 +2598,7 @@
       <c r="B52" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="5">
         <v>100173499</v>
       </c>
       <c r="D52" s="4" t="s">
@@ -2616,13 +2607,13 @@
       <c r="E52" s="3">
         <v>7702771001561</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="5">
         <v>873239</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="5">
         <v>110323</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="5" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2634,7 +2625,7 @@
       <c r="B53" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="5">
         <v>100173499</v>
       </c>
       <c r="D53" s="4" t="s">
@@ -2643,13 +2634,13 @@
       <c r="E53" s="3">
         <v>7501165010444</v>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="5">
         <v>600723</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="5">
         <v>118952</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2661,7 +2652,7 @@
       <c r="B54" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="5">
         <v>100173499</v>
       </c>
       <c r="D54" s="4" t="s">
@@ -2670,13 +2661,13 @@
       <c r="E54" s="3">
         <v>7703202221282</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="5">
         <v>782085</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="5">
         <v>120610</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2688,7 +2679,7 @@
       <c r="B55" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="5">
         <v>100173499</v>
       </c>
       <c r="D55" s="4" t="s">
@@ -2697,13 +2688,13 @@
       <c r="E55" s="3">
         <v>7703202003475</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="5">
         <v>650554</v>
       </c>
-      <c r="G55" s="11">
+      <c r="G55" s="5">
         <v>120771</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2715,7 +2706,7 @@
       <c r="B56" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="5">
         <v>100173499</v>
       </c>
       <c r="D56" s="4" t="s">
@@ -2724,13 +2715,13 @@
       <c r="E56" s="3">
         <v>3664798064728</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="3">
         <v>846778</v>
       </c>
-      <c r="G56" s="12">
+      <c r="G56" s="3">
         <v>156006</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2742,22 +2733,22 @@
       <c r="B57" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="5">
         <v>100173512</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="12">
+      <c r="E57" s="3">
         <v>7703202221244</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="5">
         <v>782065</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="5">
         <v>6933</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2769,22 +2760,22 @@
       <c r="B58" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="5">
         <v>100173512</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="12">
+      <c r="E58" s="3">
         <v>7703202221329</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="5">
         <v>782092</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="5">
         <v>1271095</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2796,22 +2787,22 @@
       <c r="B59" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="5">
         <v>100173512</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="12">
+      <c r="E59" s="3">
         <v>7703202221305</v>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="5">
         <v>782086</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="5">
         <v>40999</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2823,22 +2814,22 @@
       <c r="B60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="5">
         <v>100173512</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="12">
+      <c r="E60" s="3">
         <v>7703202221169</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="5">
         <v>715503</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="5">
         <v>55442</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2850,22 +2841,22 @@
       <c r="B61" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="5">
         <v>100173512</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="12">
+      <c r="E61" s="3">
         <v>7591044007191</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="5">
         <v>120786</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="5">
         <v>64568</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2877,22 +2868,22 @@
       <c r="B62" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="5">
         <v>100173512</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="12">
+      <c r="E62" s="3">
         <v>7591044009447</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="5">
         <v>120777</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="5">
         <v>9332</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2904,22 +2895,22 @@
       <c r="B63" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="5">
         <v>100173512</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E63" s="12">
+      <c r="E63" s="3">
         <v>7591044008952</v>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="5">
         <v>666269</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63" s="5">
         <v>334003</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2931,22 +2922,22 @@
       <c r="B64" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="5">
         <v>100173512</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="12">
+      <c r="E64" s="3">
         <v>7501165007956</v>
       </c>
-      <c r="F64" s="11">
+      <c r="F64" s="5">
         <v>655678</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64" s="5">
         <v>1258820</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2958,22 +2949,22 @@
       <c r="B65" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="5">
         <v>100173512</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="12">
+      <c r="E65" s="3">
         <v>7703202003475</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="5">
         <v>650554</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65" s="5">
         <v>1269901</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2985,22 +2976,22 @@
       <c r="B66" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C66" s="10">
+      <c r="C66" s="5">
         <v>100173512</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="12">
+      <c r="E66" s="3">
         <v>7591044401036</v>
       </c>
-      <c r="F66" s="11">
+      <c r="F66" s="5">
         <v>723871</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G66" s="5">
         <v>356801</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3012,22 +3003,22 @@
       <c r="B67" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C67" s="5">
         <v>100173512</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="12">
+      <c r="E67" s="3">
         <v>7591044009010</v>
       </c>
-      <c r="F67" s="11">
+      <c r="F67" s="5">
         <v>732308</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G67" s="5">
         <v>370032</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3039,22 +3030,22 @@
       <c r="B68" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C68" s="10">
+      <c r="C68" s="5">
         <v>100173512</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="12">
+      <c r="E68" s="3">
         <v>7703202010329</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="5">
         <v>341667</v>
       </c>
-      <c r="G68" s="9">
+      <c r="G68" s="5">
         <v>370069</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3066,22 +3057,22 @@
       <c r="B69" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="5">
         <v>100173512</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="3">
         <v>7703202221220</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="5">
         <v>781955</v>
       </c>
-      <c r="G69" s="9">
+      <c r="G69" s="5">
         <v>372646</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3093,22 +3084,22 @@
       <c r="B70" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="5">
         <v>100173512</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="3">
         <v>7703202221336</v>
       </c>
-      <c r="F70" s="11">
+      <c r="F70" s="5">
         <v>782093</v>
       </c>
-      <c r="G70" s="9">
+      <c r="G70" s="5">
         <v>1271096</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="5" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3120,22 +3111,22 @@
       <c r="B71" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C71" s="10">
+      <c r="C71" s="5">
         <v>100173512</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="12">
+      <c r="E71" s="3">
         <v>3582910009900</v>
       </c>
-      <c r="F71" s="11">
+      <c r="F71" s="5">
         <v>873229</v>
       </c>
-      <c r="G71" s="9">
+      <c r="G71" s="5">
         <v>928520</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3147,22 +3138,22 @@
       <c r="B72" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C72" s="10">
+      <c r="C72" s="5">
         <v>100173512</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="12">
+      <c r="E72" s="3">
         <v>7703202221275</v>
       </c>
-      <c r="F72" s="11">
+      <c r="F72" s="5">
         <v>782074</v>
       </c>
-      <c r="G72" s="9">
+      <c r="G72" s="5">
         <v>934211</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3174,22 +3165,22 @@
       <c r="B73" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C73" s="10">
+      <c r="C73" s="5">
         <v>100173512</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="12">
+      <c r="E73" s="3">
         <v>7703202221176</v>
       </c>
-      <c r="F73" s="11">
+      <c r="F73" s="5">
         <v>715717</v>
       </c>
-      <c r="G73" s="9">
+      <c r="G73" s="5">
         <v>982597</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3201,22 +3192,22 @@
       <c r="B74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C74" s="10">
+      <c r="C74" s="5">
         <v>100173512</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="12">
+      <c r="E74" s="3">
         <v>7703381002146</v>
       </c>
-      <c r="F74" s="11">
+      <c r="F74" s="5">
         <v>715717</v>
       </c>
-      <c r="G74" s="9">
+      <c r="G74" s="5">
         <v>982597</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3228,22 +3219,22 @@
       <c r="B75" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C75" s="10">
+      <c r="C75" s="5">
         <v>100173512</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E75" s="12">
+      <c r="E75" s="3">
         <v>7703202221152</v>
       </c>
-      <c r="F75" s="11">
+      <c r="F75" s="5">
         <v>715506</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G75" s="5">
         <v>1087419</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3255,22 +3246,22 @@
       <c r="B76" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C76" s="10">
+      <c r="C76" s="5">
         <v>100173512</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="12">
+      <c r="E76" s="3">
         <v>7795312100090</v>
       </c>
-      <c r="F76" s="11">
+      <c r="F76" s="5">
         <v>785678</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76" s="5">
         <v>1167480</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="5" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3282,22 +3273,22 @@
       <c r="B77" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="5">
         <v>100173512</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E77" s="12">
+      <c r="E77" s="3">
         <v>7702605107407</v>
       </c>
-      <c r="F77" s="11">
+      <c r="F77" s="5">
         <v>893499</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="5">
         <v>1222416</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3309,22 +3300,22 @@
       <c r="B78" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C78" s="10">
+      <c r="C78" s="5">
         <v>100173512</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E78" s="12">
+      <c r="E78" s="3">
         <v>7703202221381</v>
       </c>
-      <c r="F78" s="11">
+      <c r="F78" s="5">
         <v>782089</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78" s="5">
         <v>1262181</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="5" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3336,22 +3327,22 @@
       <c r="B79" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C79" s="10">
+      <c r="C79" s="5">
         <v>100173512</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E79" s="12">
+      <c r="E79" s="3">
         <v>7703202221428</v>
       </c>
-      <c r="F79" s="11">
+      <c r="F79" s="5">
         <v>782090</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79" s="5">
         <v>1262222</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="5" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3363,22 +3354,22 @@
       <c r="B80" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C80" s="10">
+      <c r="C80" s="5">
         <v>100173512</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E80" s="12">
+      <c r="E80" s="3">
         <v>7702771001561</v>
       </c>
-      <c r="F80" s="11">
+      <c r="F80" s="5">
         <v>873239</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="5">
         <v>1266274</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="5" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3390,22 +3381,22 @@
       <c r="B81" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="5">
         <v>100173512</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E81" s="12">
+      <c r="E81" s="3">
         <v>7501165010444</v>
       </c>
-      <c r="F81" s="11">
+      <c r="F81" s="5">
         <v>600723</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G81" s="5">
         <v>1268666</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3417,22 +3408,22 @@
       <c r="B82" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C82" s="10">
+      <c r="C82" s="5">
         <v>100173512</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E82" s="14">
+      <c r="E82" s="7">
         <v>3664798064728</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="4">
         <v>846778</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="5">
         <v>1297614</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3441,25 +3432,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221244Institucional</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C83" s="3">
         <v>100173512</v>
       </c>
-      <c r="D83" s="16" t="s">
+      <c r="D83" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E83" s="15">
+      <c r="E83" s="8">
         <v>7703202221244</v>
       </c>
-      <c r="F83" s="15">
+      <c r="F83" s="8">
         <v>782065</v>
       </c>
-      <c r="G83" s="15">
+      <c r="G83" s="8">
         <v>391926</v>
       </c>
-      <c r="H83" s="16" t="s">
+      <c r="H83" s="9" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3468,25 +3459,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221305Institucional</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C84" s="3">
         <v>100173512</v>
       </c>
-      <c r="D84" s="16" t="s">
+      <c r="D84" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E84" s="15">
+      <c r="E84" s="8">
         <v>7703202221305</v>
       </c>
-      <c r="F84" s="15">
+      <c r="F84" s="8">
         <v>782086</v>
       </c>
-      <c r="G84" s="15">
+      <c r="G84" s="8">
         <v>1261915</v>
       </c>
-      <c r="H84" s="16" t="s">
+      <c r="H84" s="9" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3495,25 +3486,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221312Institucional</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C85" s="3">
         <v>100173512</v>
       </c>
-      <c r="D85" s="16" t="s">
+      <c r="D85" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E85" s="15">
+      <c r="E85" s="8">
         <v>7703202221312</v>
       </c>
-      <c r="F85" s="15">
+      <c r="F85" s="8">
         <v>782091</v>
       </c>
-      <c r="G85" s="15">
+      <c r="G85" s="8">
         <v>1270905</v>
       </c>
-      <c r="H85" s="16" t="s">
+      <c r="H85" s="9" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3522,25 +3513,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221169Institucional</v>
       </c>
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C86" s="3">
         <v>100173512</v>
       </c>
-      <c r="D86" s="16" t="s">
+      <c r="D86" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E86" s="15">
+      <c r="E86" s="8">
         <v>7703202221169</v>
       </c>
-      <c r="F86" s="15">
+      <c r="F86" s="8">
         <v>715503</v>
       </c>
-      <c r="G86" s="15">
+      <c r="G86" s="8">
         <v>391918</v>
       </c>
-      <c r="H86" s="16" t="s">
+      <c r="H86" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3549,25 +3540,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127591044007191Institucional</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C87" s="3">
         <v>100173512</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="D87" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E87" s="15">
+      <c r="E87" s="8">
         <v>7591044007191</v>
       </c>
-      <c r="F87" s="15">
+      <c r="F87" s="8">
         <v>120786</v>
       </c>
-      <c r="G87" s="15">
+      <c r="G87" s="8">
         <v>1267251</v>
       </c>
-      <c r="H87" s="16" t="s">
+      <c r="H87" s="9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3576,25 +3567,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127591044009447Institucional</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B88" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="3">
         <v>100173512</v>
       </c>
-      <c r="D88" s="16" t="s">
+      <c r="D88" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E88" s="15">
+      <c r="E88" s="8">
         <v>7591044009447</v>
       </c>
-      <c r="F88" s="15">
+      <c r="F88" s="8">
         <v>120777</v>
       </c>
-      <c r="G88" s="15">
+      <c r="G88" s="8">
         <v>1267274</v>
       </c>
-      <c r="H88" s="16" t="s">
+      <c r="H88" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3603,25 +3594,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127591044008952Institucional</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C89" s="3">
         <v>100173512</v>
       </c>
-      <c r="D89" s="16" t="s">
+      <c r="D89" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E89" s="15">
+      <c r="E89" s="8">
         <v>7591044008952</v>
       </c>
-      <c r="F89" s="15">
+      <c r="F89" s="8">
         <v>666269</v>
       </c>
-      <c r="G89" s="15">
+      <c r="G89" s="8">
         <v>1166205</v>
       </c>
-      <c r="H89" s="16" t="s">
+      <c r="H89" s="9" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3630,25 +3621,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127501165007956Institucional</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C90" s="3">
         <v>100173512</v>
       </c>
-      <c r="D90" s="16" t="s">
+      <c r="D90" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E90" s="15">
+      <c r="E90" s="8">
         <v>7501165007956</v>
       </c>
-      <c r="F90" s="15">
+      <c r="F90" s="8">
         <v>655678</v>
       </c>
-      <c r="G90" s="15">
+      <c r="G90" s="8">
         <v>1271062</v>
       </c>
-      <c r="H90" s="16" t="s">
+      <c r="H90" s="9" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3657,25 +3648,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127591044401036Institucional</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C91" s="3">
         <v>100173512</v>
       </c>
-      <c r="D91" s="16" t="s">
+      <c r="D91" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E91" s="15">
+      <c r="E91" s="8">
         <v>7591044401036</v>
       </c>
-      <c r="F91" s="15">
+      <c r="F91" s="8">
         <v>723871</v>
       </c>
-      <c r="G91" s="15">
+      <c r="G91" s="8">
         <v>1267481</v>
       </c>
-      <c r="H91" s="16" t="s">
+      <c r="H91" s="9" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3684,25 +3675,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127591044009010Institucional</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B92" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C92" s="3">
         <v>100173512</v>
       </c>
-      <c r="D92" s="16" t="s">
+      <c r="D92" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E92" s="15">
+      <c r="E92" s="8">
         <v>7591044009010</v>
       </c>
-      <c r="F92" s="15">
+      <c r="F92" s="8">
         <v>732308</v>
       </c>
-      <c r="G92" s="15">
+      <c r="G92" s="8">
         <v>1166206</v>
       </c>
-      <c r="H92" s="16" t="s">
+      <c r="H92" s="9" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3711,25 +3702,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202010329Institucional</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C93" s="3">
         <v>100173512</v>
       </c>
-      <c r="D93" s="16" t="s">
+      <c r="D93" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E93" s="15">
+      <c r="E93" s="8">
         <v>7703202010329</v>
       </c>
-      <c r="F93" s="15">
+      <c r="F93" s="8">
         <v>341667</v>
       </c>
-      <c r="G93" s="15">
+      <c r="G93" s="8">
         <v>1270898</v>
       </c>
-      <c r="H93" s="16" t="s">
+      <c r="H93" s="9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3738,25 +3729,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703381002146Institucional</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C94" s="3">
         <v>100173512</v>
       </c>
-      <c r="D94" s="16" t="s">
+      <c r="D94" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E94" s="15">
+      <c r="E94" s="8">
         <v>7703381002146</v>
       </c>
-      <c r="F94" s="15">
+      <c r="F94" s="8">
         <v>715717</v>
       </c>
-      <c r="G94" s="15">
+      <c r="G94" s="8">
         <v>1261846</v>
       </c>
-      <c r="H94" s="16" t="s">
+      <c r="H94" s="9" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3765,25 +3756,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221152Institucional</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C95" s="3">
         <v>100173512</v>
       </c>
-      <c r="D95" s="16" t="s">
+      <c r="D95" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E95" s="15">
+      <c r="E95" s="8">
         <v>7703202221152</v>
       </c>
-      <c r="F95" s="15">
+      <c r="F95" s="8">
         <v>715506</v>
       </c>
-      <c r="G95" s="15">
+      <c r="G95" s="8">
         <v>1284625</v>
       </c>
-      <c r="H95" s="16" t="s">
+      <c r="H95" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3792,25 +3783,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127795312100090Institucional</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C96" s="3">
         <v>100173512</v>
       </c>
-      <c r="D96" s="16" t="s">
+      <c r="D96" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E96" s="15">
+      <c r="E96" s="8">
         <v>7795312100090</v>
       </c>
-      <c r="F96" s="15">
+      <c r="F96" s="8">
         <v>785678</v>
       </c>
-      <c r="G96" s="15">
+      <c r="G96" s="8">
         <v>1260643</v>
       </c>
-      <c r="H96" s="16" t="s">
+      <c r="H96" s="9" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3819,25 +3810,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127702605107407Institucional</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C97" s="3">
         <v>100173512</v>
       </c>
-      <c r="D97" s="16" t="s">
+      <c r="D97" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E97" s="15">
+      <c r="E97" s="8">
         <v>7702605107407</v>
       </c>
-      <c r="F97" s="15">
+      <c r="F97" s="8">
         <v>893499</v>
       </c>
-      <c r="G97" s="15">
+      <c r="G97" s="8">
         <v>1251857</v>
       </c>
-      <c r="H97" s="16" t="s">
+      <c r="H97" s="9" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3846,25 +3837,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221381Institucional</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C98" s="3">
         <v>100173512</v>
       </c>
-      <c r="D98" s="16" t="s">
+      <c r="D98" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E98" s="15">
+      <c r="E98" s="8">
         <v>7703202221381</v>
       </c>
-      <c r="F98" s="15">
+      <c r="F98" s="8">
         <v>782089</v>
       </c>
-      <c r="G98" s="15">
+      <c r="G98" s="8">
         <v>1289603</v>
       </c>
-      <c r="H98" s="16" t="s">
+      <c r="H98" s="9" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3873,25 +3864,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221428Institucional</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C99" s="3">
         <v>100173512</v>
       </c>
-      <c r="D99" s="16" t="s">
+      <c r="D99" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E99" s="15">
+      <c r="E99" s="8">
         <v>7703202221428</v>
       </c>
-      <c r="F99" s="15">
+      <c r="F99" s="8">
         <v>782090</v>
       </c>
-      <c r="G99" s="15">
+      <c r="G99" s="8">
         <v>1271562</v>
       </c>
-      <c r="H99" s="16" t="s">
+      <c r="H99" s="9" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3900,25 +3891,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127702771001561Institucional</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C100" s="3">
         <v>100173512</v>
       </c>
-      <c r="D100" s="16" t="s">
+      <c r="D100" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E100" s="15">
+      <c r="E100" s="8">
         <v>7702771001561</v>
       </c>
-      <c r="F100" s="15">
+      <c r="F100" s="8">
         <v>873239</v>
       </c>
-      <c r="G100" s="15">
+      <c r="G100" s="8">
         <v>1270904</v>
       </c>
-      <c r="H100" s="16" t="s">
+      <c r="H100" s="9" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3927,25 +3918,25 @@
         <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
         <v>1001735127703202221282Institucional</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C101" s="3">
         <v>100173512</v>
       </c>
-      <c r="D101" s="16" t="s">
+      <c r="D101" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E101" s="15">
+      <c r="E101" s="8">
         <v>7703202221282</v>
       </c>
-      <c r="F101" s="15">
+      <c r="F101" s="8">
         <v>782085</v>
       </c>
-      <c r="G101" s="15">
+      <c r="G101" s="8">
         <v>1276014</v>
       </c>
-      <c r="H101" s="16" t="s">
+      <c r="H101" s="9" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3960,7 +3951,7 @@
       <c r="C102" s="3">
         <v>100173512</v>
       </c>
-      <c r="D102" s="9" t="s">
+      <c r="D102" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E102" s="3">
@@ -3969,10 +3960,10 @@
       <c r="F102" s="3">
         <v>873229</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="5">
         <v>1165164</v>
       </c>
-      <c r="H102" s="9" t="s">
+      <c r="H102" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3985,7 +3976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3995,308 +3986,308 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
+      <c r="A2" s="12">
         <v>10</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="13" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="13" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="20" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="21" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="20" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="13" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="13" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="13" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="13" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="13" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4309,7 +4300,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4319,308 +4310,308 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
+      <c r="A2" s="12">
         <v>10</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="13" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="13" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="15" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="15" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="15" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="15" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="16" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="15" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="15" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="13" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="13" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="13" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="13" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="13" t="s">
         <v>77</v>
       </c>
     </row>

--- a/Plantillas/Base Maestra/Maestra.xlsx
+++ b/Plantillas/Base Maestra/Maestra.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47722A65-63B4-4E6A-8CF9-013C07D36876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E7AA0A-DBA5-4B29-8F64-91AC3AFCF128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="6240" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="395">
   <si>
     <t>KeyPLU</t>
   </si>
@@ -471,13 +471,760 @@
   </si>
   <si>
     <t>Retoma de producto en nueva orden</t>
+  </si>
+  <si>
+    <t>ZS</t>
+  </si>
+  <si>
+    <t>Substitution</t>
+  </si>
+  <si>
+    <t>Sustituido en otro SKU</t>
+  </si>
+  <si>
+    <t>Z2</t>
+  </si>
+  <si>
+    <t>Stockout - To Be Analyzed</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>Unexpected Demand</t>
+  </si>
+  <si>
+    <t>Z3</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Z4</t>
+  </si>
+  <si>
+    <t>Capacity Constraints</t>
+  </si>
+  <si>
+    <t>Z6</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Y4</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>ZV</t>
+  </si>
+  <si>
+    <t>Validity Period</t>
+  </si>
+  <si>
+    <t>Contrato de cliente expirado</t>
+  </si>
+  <si>
+    <t>Y6</t>
+  </si>
+  <si>
+    <t>Typing Error</t>
+  </si>
+  <si>
+    <t>Error proceso de pedido</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>Financial &amp; System Issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error en sistema </t>
+  </si>
+  <si>
+    <t>Z8</t>
+  </si>
+  <si>
+    <t>Upstream Distribution</t>
+  </si>
+  <si>
+    <t>Z9</t>
+  </si>
+  <si>
+    <t>Importation Issue</t>
+  </si>
+  <si>
+    <t>ZH</t>
+  </si>
+  <si>
+    <t>DC Change</t>
+  </si>
+  <si>
+    <t>Z5</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>Z7</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Y3</t>
+  </si>
+  <si>
+    <t>Regulatory Problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruptura </t>
+  </si>
+  <si>
+    <t>Error en sistema Opella</t>
+  </si>
+  <si>
+    <t>CRUZ VERDE</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120MG TAB REC  CAJ X 10</t>
+  </si>
+  <si>
+    <t>ALLEGRA 180MG TAB REC  CAJ X 10</t>
+  </si>
+  <si>
+    <t>ALLEGRA D (25+60)MG TAB REC  CAJ X 10</t>
+  </si>
+  <si>
+    <t>ALLEGRA PED 30MG/5ML(0.6%) SUSP ORAL  FCO X 150ML</t>
+  </si>
+  <si>
+    <t>BISOLVON LICTUS NINOS 4MG/5ML(0.08%) JBE  FCO X 120ML  FRESA</t>
+  </si>
+  <si>
+    <t>BISOLVON MAX 30MG/5ML(0.6%) JBE  FCO X 120ML</t>
+  </si>
+  <si>
+    <t>BISOLVON TS 10MG/5ML(0.2%) JBE  FCO X 120ML</t>
+  </si>
+  <si>
+    <t>BUSCAMINT CAP BLAND CAJ X 12</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 10MG TAB REC  CAJ X 20</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 20MG/ML SOL INY  CAJ X 3AMP</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA NF (100+2)MG/ML(10+0.2)% SOL ORAL  FCO X 30ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA NF (325+10)MG TAB REC  CAJ X 10</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA NF (325+10)MG TAB REC  CAJ X 100</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA NF (325+10)MG TAB REC  CAJ X 20</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM (20+400)MG TAB REC CAJ X 6</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM (20+400)MG TAB REC  CAJ X 90</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5MG TAB LIB RET CAJ X 10</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5MG TAB LIB RET CAJ X 20</t>
+  </si>
+  <si>
+    <t>DULCOLAX P 7.5MG/ML(0.75%) SOL ORAL  FCO X 15ML</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA 2000MUI/5ML SUSP ORAL  CAJ X 10AMPACKX5ML</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA PLUS 4000MUI/5ML SUSP ORAL  CAJ X 5FCOX5ML</t>
+  </si>
+  <si>
+    <t>GELICART  POLV SUSP ORAL  CAJ X 30</t>
+  </si>
+  <si>
+    <t>GELICART ADVANCE MULTIPLES COMPONENTES   CAJ X 30SOB</t>
+  </si>
+  <si>
+    <t>MIGRINON (30+300+30)MG TAB REC CAJ X 100</t>
+  </si>
+  <si>
+    <t>NASACORT AQ 55MCG/DOSIS SUSP NAS  SPRAY X 120DOSIS</t>
+  </si>
+  <si>
+    <t>NOVALGINA 500MG TAB  CAJ X 50</t>
+  </si>
+  <si>
+    <t>NOVALGINA IM-IV 1GR/2ML(0.5GR/ML) SOL INY  CAJ X 10AMP X 2ML</t>
+  </si>
+  <si>
+    <t>NOVALGINA IM-IV 2.5GR/5ML(0.5GR/ML) SOL INY  CAJ X 5AMP X 5ML</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120MG TAB REC INST</t>
+  </si>
+  <si>
+    <t>ALLEGRA 180MG TAB REC INST</t>
+  </si>
+  <si>
+    <t>ALLEGRA D (25+60)MG TABLETA RECUBIERTA INST CAJ X 10</t>
+  </si>
+  <si>
+    <t>ALLEGRA PED 30MG/5ML(0.6%) SUSP ORAL INST FCO X 150ML</t>
+  </si>
+  <si>
+    <t>BISOLVON MAX 30MG/5ML(0.6%) JBE INST FCO X 120ML</t>
+  </si>
+  <si>
+    <t>BISOLVON TS 10MG/5ML(0.2%) JBE INST FCO X 120ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 10MG TAB REC INST CAJ X 20</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 20MG/ML SOL INY INST CAJ X 3AMP</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMP NF (325+10)MG TAB REC INST CAJ X 100</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA NF (100+2)MG/ML(10+0.2)% SOL ORAL INST FCO X 30ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM (20+400)MG TAB REC INST CAJ X 6</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM CAJA X 90</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5MG TAB LIB RET INST CAJ X 10</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5MG TAB LIB RET INST CAJ X 20</t>
+  </si>
+  <si>
+    <t>DULCOLAX P GOTAS 7.5MG/ML(0.75%) SOL ORAL INST FCO X 15ML</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA 2000MUI/5ML SUSP ORAL INST CAJ X 10AMPACK X 5ML</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA PLUS 4000MUI/5ML SUSP ORAL INST CAJ X 5FCOX5ML</t>
+  </si>
+  <si>
+    <t>MIGRINON (30+300+30)MG TAB REC INST CAJ X 100</t>
+  </si>
+  <si>
+    <t>NASACORT AQ 55MCG/DOSIS SUSP NAS INST FCO X 120DOSIS</t>
+  </si>
+  <si>
+    <t>NOVALGINA 1GR/2ML(0.5GR/ML) SOL INY INST CAJ X 10AMP X 2ML</t>
+  </si>
+  <si>
+    <t>NOVALGINA 2.5GR/5ML(0.5GR/ML) SOL INY INST CAJ X 5AMP X 5ML</t>
+  </si>
+  <si>
+    <t>NOVALGINA 500MG TAB INST CAJ X 50</t>
+  </si>
+  <si>
+    <t>ALLEGRA 30MG SUSPENSION X 150 ML</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120 MG CJ X 10 COMP.</t>
+  </si>
+  <si>
+    <t>ALLEGRA 180 MG CJ X 10 TAB.</t>
+  </si>
+  <si>
+    <t>ALLEGRA D 60/25 MG CJ X 10 TAB</t>
+  </si>
+  <si>
+    <t>INS ALLEGRA 30MG SUSPENSION X 150 ml</t>
+  </si>
+  <si>
+    <t>INS ALLEGRA 180 MG CJ X 10 TAB</t>
+  </si>
+  <si>
+    <t>INS ALLEGRA D 60/25 MG CJ X 10 TAB.</t>
+  </si>
+  <si>
+    <t>BISOLVON ADULTOS JBE X 120 ML</t>
+  </si>
+  <si>
+    <t>BISOLVON MAX TOS C/FLEMAS FCO X 120 ML</t>
+  </si>
+  <si>
+    <t>BISOLVON NIÑOS JBE FCO X 120 ML</t>
+  </si>
+  <si>
+    <t>BISOLVON TS JBE FCO X 120 ML</t>
+  </si>
+  <si>
+    <t>INS BISOLVON LINCTUS ADULTOS JBE X 120ML</t>
+  </si>
+  <si>
+    <t>INS BISOLVON LINCTUS NIÑOS JBE X 120ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 10 MG CJ X 20 GRAGEAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 20MG CJ X 3 AMP X 1 ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMP 10/325 MG CJ X 10 TAB</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMP 10/325 MG CJ X 20 TAB</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPOS NF SOL ORAL FCO X 30 ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM MG CJ X 6 COMP</t>
+  </si>
+  <si>
+    <t>INS BUSCAPINA FEM 400MG/20MG CJ X 90 TAB</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5 MG CJ X 10 GRAG</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5 MG CJ X 20 GRAG</t>
+  </si>
+  <si>
+    <t>DULCOLAX P 7.5 MG SOLUC ORAL FCO X15 ML</t>
+  </si>
+  <si>
+    <t>INS DULCOLAX 5 MG CJ X 20 GRAG</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA CJ X 10 AMP BEB</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA PLUS CJ X 5 VIAL BEBIBLES</t>
+  </si>
+  <si>
+    <t>INS ENTEROGERMINA CJ X 10 AMP BEB.</t>
+  </si>
+  <si>
+    <t>GELICART ADVANCE HIDROLIZADO CJX 30 SBS.</t>
+  </si>
+  <si>
+    <t>GELICART CJ X 30 SACHETS.</t>
+  </si>
+  <si>
+    <t>MIGRINON 300/30 MG CJ X 100TAB</t>
+  </si>
+  <si>
+    <t>NASACORT A.Q X 120 DOSIS</t>
+  </si>
+  <si>
+    <t>NOVALGINA 500 MG CJ X 50 TAB</t>
+  </si>
+  <si>
+    <t>INS NASACORT A.Q X 120 DOSIS.</t>
+  </si>
+  <si>
+    <t>ETICOS</t>
+  </si>
+  <si>
+    <t>OLIMPICA</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120 MG CAJA X 10 TABLETAS RECUBIERTA</t>
+  </si>
+  <si>
+    <t>ALLEGRA 180 MG X 10 TABLETAS. (196451)</t>
+  </si>
+  <si>
+    <t>ALLEGRA D 60/25 MG X 10 TABLETAS.</t>
+  </si>
+  <si>
+    <t>ALLEGRA PEDIATRICO 30 MG/5 ML SUSP FCO X 150 ML</t>
+  </si>
+  <si>
+    <t>BISOLVON ADULTO JARABE X 120 ML</t>
+  </si>
+  <si>
+    <t>BISOLVON MAX JARABE FCO X 120 ML</t>
+  </si>
+  <si>
+    <t>BISOLVON NIÑO JARABE X 120 ML.</t>
+  </si>
+  <si>
+    <t>BISOLVON TOS SECA JARABE FCO X 120 ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 10 MG CAJA X 20 GRAGEAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPOSITUM NF 325/10 MG X 100 COMPRIMIDOS RECUBIERTOS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPOSITUM NF 325/10 MG X 20 COMPRIMIDOS RECUBIERTOS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPOSITUM NF NIÑOS GOTAS FCO X 30 ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM 20/400 MG CAJA X 6 COMPRIMIDOS RECUBIERTOS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM 20/400 MG CAJA X 90 COMPRIMIDOS RECUBIERTOS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA SIMPLE X 3 AMPOLLAS.</t>
+  </si>
+  <si>
+    <t>CALMIDOL COMPUESTO 200/30 MG CAJA X 48 CAPSULAS</t>
+  </si>
+  <si>
+    <t>CALMIDOL MAX CAJA X 48 TABLETAS RECUBIERTAS</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5 MG CAJA X 10 GRAGEAS</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5 MG CAJA X 20 GRAGEAS</t>
+  </si>
+  <si>
+    <t>DULCOLAX P GOTAS FCO X 15 ML</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA AMPOLLAS BEBIBLE X 10 UI.</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA PLUS 4000 MILL AMPOLLAS BEBIBLE X 5 FCOS DE 5 ML (193447)</t>
+  </si>
+  <si>
+    <t>GELICART ADVANCE 25/75% CAJA X 30 SOBRES DE 20 GR S/DIETARIO</t>
+  </si>
+  <si>
+    <t>GELICART CAJA X 30 SOBRES DE 10 GR S/DIETARIO</t>
+  </si>
+  <si>
+    <t>MIGRINON 300/30/30 MG DISPLAY X 20 CAJAS DE 5 TABLETAS RECUBIERTAS</t>
+  </si>
+  <si>
+    <t>NASACORT AQ 55 MCG SPRAY NASAL X 120 APLIC</t>
+  </si>
+  <si>
+    <t>NOVALGINA 500 MG CAJA X 50 TABLETAS (196583)</t>
+  </si>
+  <si>
+    <t>NOVALGINA 500 MG/ML GOTAS X 10 ML (196407)</t>
+  </si>
+  <si>
+    <t>NOVALGINA X  5 AMPOLLA DE 5 ML</t>
+  </si>
+  <si>
+    <t>NOVALGINA X 10 AMPOLLA DE 2 ML</t>
+  </si>
+  <si>
+    <t>AXA</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM 20+400 MG CAJA 6 TABLETAS RECUBIERTAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COOPIDROGAS </t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM 20+400MG X 6 COMP REC</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120 MG CAJA X 10 TAB BR</t>
+  </si>
+  <si>
+    <t>ALLEGRA 180MG 1X10 CPR EXP</t>
+  </si>
+  <si>
+    <t>NASACORT AQ 16.5 MG SOL NASAL X 1 FCO GB</t>
+  </si>
+  <si>
+    <t>NOVALGINA 2.5g INY AMP 5mlX5 IMP BR</t>
+  </si>
+  <si>
+    <t>BISOLVON ADULTOS JBE 8MG/5ML X 120ML</t>
+  </si>
+  <si>
+    <t>BISOLVON PED JBE 4MG/5ML X 120ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA SOL INY 20MG/ML X 3 AMP</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMP NF GTS 2+100MG/ML X 30 ML</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 10MG X 20 GRG</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5MG TABSC BL10 M36 CO</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA CAJA X 10 AMP BEB IT</t>
+  </si>
+  <si>
+    <t>DULCOLAX 112.5MG/+ DROP BT1 M24 CO</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM 20+400MG X 90 COMP REC</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5MG TABSC BL20 M36 CO</t>
+  </si>
+  <si>
+    <t>ALLEGRA SUS 900mg X 150 mL BR OTC</t>
+  </si>
+  <si>
+    <t>ALLEGRA D 60mg CAJA X 10 TAB MX</t>
+  </si>
+  <si>
+    <t>GELICART 10G POWD SK30 XB</t>
+  </si>
+  <si>
+    <t>BISOLVON MAX JBE 30MG/5ML X 120ML</t>
+  </si>
+  <si>
+    <t>BISOLVON TS JBE 10MG/5ML X 120ML</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA 4BCFU/5ML SUSP 5 BOT IT</t>
+  </si>
+  <si>
+    <t>NOVALGINA 500mg CAJA X 50 TAB MX</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMP 10-325MG TABCO BL10X10 CO</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPO 10-325MG TABCO BL2X10 CO</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPOSI 10-325MG TABCO BL10 CO</t>
+  </si>
+  <si>
+    <t>GELICART ACTION 20G POWD SC30 M24 XB</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120MG TAB BL2 M36 CO (X5 UNID)</t>
+  </si>
+  <si>
+    <t>BUSCAMINT 181.6MG CAPSG BL12 M36 XL</t>
+  </si>
+  <si>
+    <t>NOVALGINA 1g INY AMP 2mlX10 IMP BR</t>
+  </si>
+  <si>
+    <t>PASTEUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	1275000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	1275002</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120 MG CAJA X 2 (New Size)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	137537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	253024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	377184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	377434</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMP 4/500MG/ML X 5ML X 3 AMP</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120 MG CAJA 10 COMPRIMIDOS</t>
+  </si>
+  <si>
+    <t>ALLEGRA 120 MG CAJA 2 TABLETAS.</t>
+  </si>
+  <si>
+    <t>ALLEGRA 180 MG CAJA 10 COMPRIMIDOS</t>
+  </si>
+  <si>
+    <t>ALLEGRA D 60 MG/25 MG CAJA 10 TABLETAS</t>
+  </si>
+  <si>
+    <t>ALLEGRA PEDIATRICO 30 MG FRASCO 150 ML JARABE</t>
+  </si>
+  <si>
+    <t>BISOLVON MAX 30 MG/5ML FRASCO 120 ML JARABE</t>
+  </si>
+  <si>
+    <t>BISOLVON PEDIATRICO 4 MG/5ML FRASCO 120 ML JARABE</t>
+  </si>
+  <si>
+    <t>BISOLVON TOS 10 MG/5ML FRASCO 120 ML JARABE</t>
+  </si>
+  <si>
+    <t>BUSCAMINT CAJA 12 CAPS BLANDAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA 10 MG CAJA 20 GRAGEAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA 10/325 ML CAJA 10 TABLETAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA 10/325 ML CAJA 100 TABLETAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA 10/325 ML CAJA 20 TABLETAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA 10/325MG CAJA 30 TABLETAS RECUBIERTAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA NF 2+100 MG/ML FRASCO 30 ML GOTAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM 20+400 MG CAJA 24 TABLETAS RECUBIERTAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA FEM 20+400 MG CAJA 90 TABLETAS RECUBIERTAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA SOLUCION INYECTABLE 20 MG/ML CAJA 3 AMPOLLA</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5 MG CAJA 10 GRAGEAS</t>
+  </si>
+  <si>
+    <t>DULCOLAX 5 MG CAJA 20 GRAGEAS</t>
+  </si>
+  <si>
+    <t>DULCOLAX 7.5 MG/ML FRASCO 15 ML GOTAS</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA BEBIBLES CAJA 10 AMPOLLA</t>
+  </si>
+  <si>
+    <t>ENTEROGERMINA PLUS VIAL 5 ML CAJA 5 VIALES</t>
+  </si>
+  <si>
+    <t>GELICART ADVANCE POLVO CAJA 30 SOBRES 10 GR</t>
+  </si>
+  <si>
+    <t>GELICART POLVO CAJA 30 SOBRES 10 GR</t>
+  </si>
+  <si>
+    <t>NASACORT AQ INHALADOR NASAL 55MCG FRASCO 120 DOSIS</t>
+  </si>
+  <si>
+    <t>NOVALGINA 2 ML CAJA 10 AMPOLLAS</t>
+  </si>
+  <si>
+    <t>NOVALGINA 2.5 G/5 ML CAJA 5 AMPOLLAS</t>
+  </si>
+  <si>
+    <t>NOVALGINA 500 MG CAJA 50 TABLETAS</t>
+  </si>
+  <si>
+    <t>BUSCAPINA COMPUESTA 500 MG/5 ML CAJA 3 AMPOLLA</t>
+  </si>
+  <si>
+    <t>UNIDROGAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	041069</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,8 +1259,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -526,8 +1280,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -565,11 +1325,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -606,18 +1458,146 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -811,75 +1791,6 @@
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -894,45 +1805,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Maestra" displayName="Maestra" ref="A1:H102" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:H102" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Maestra" displayName="Maestra" ref="A1:H369" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:H369" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="8">
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="KeyPLU" dataDxfId="12">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="KeyPLU" dataDxfId="17">
       <calculatedColumnFormula>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CLIENTE" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SoldTO" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canal" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EAN" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GMID" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="PLU" dataDxfId="6"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CLIENTE" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SoldTO" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canal" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EAN" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GMID" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="PLU" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MR" displayName="MR" ref="A1:C28" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:C28" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C47">
-    <sortCondition ref="B2:B47"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}" name="MR_8" displayName="MR_8" ref="A1:C44" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:C44" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Code" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Reason (shift)" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Definition" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9E916551-61FD-448A-B81B-5ADC55507D88}" name="Code" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{9566008B-5A00-4796-9B0E-602672187BF5}" name="Reason (shift)" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{85494BE8-8F70-4A24-AB4B-AE2EEF433E3E}" name="Definition" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="MR_4" displayName="MR_4" ref="A1:C28" totalsRowShown="0" headerRowDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C283A7A-442C-43A3-984C-CEFD22907B9A}" name="MR_7" displayName="MR_7" ref="A1:C44" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C44" xr:uid="{6C283A7A-442C-43A3-984C-CEFD22907B9A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Code" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Reason (shift)" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Definition" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{E2C9FFF9-ECC7-427D-8735-33E33790C3E9}" name="Code" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{83957DAE-DC52-4558-9499-0075AFBDD203}" name="Reason (shift)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{8C5DC287-A9AC-47B8-B209-A750C1A41565}" name="Definition" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1201,14 +2110,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H369"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="75" bestFit="1" customWidth="1"/>
@@ -3965,6 +4874,7215 @@
       </c>
       <c r="H102" s="5" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044008952Retail</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C103" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="3">
+        <v>7591044008952</v>
+      </c>
+      <c r="F103" s="3">
+        <v>666269</v>
+      </c>
+      <c r="G103" s="5">
+        <v>119410</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044009010Retail</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C104" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="3">
+        <v>7591044009010</v>
+      </c>
+      <c r="F104" s="3">
+        <v>732308</v>
+      </c>
+      <c r="G104" s="5">
+        <v>121499</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202010329Retail</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C105" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="3">
+        <v>7703202010329</v>
+      </c>
+      <c r="F105" s="3">
+        <v>341667</v>
+      </c>
+      <c r="G105" s="5">
+        <v>121485</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097795312100090Retail</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C106" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="3">
+        <v>7795312100090</v>
+      </c>
+      <c r="F106" s="3">
+        <v>785678</v>
+      </c>
+      <c r="G106" s="5">
+        <v>121486</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221220Retail</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C107" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="3">
+        <v>7703202221220</v>
+      </c>
+      <c r="F107" s="3">
+        <v>781955</v>
+      </c>
+      <c r="G107" s="5">
+        <v>21427</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221428Retail</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C108" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="3">
+        <v>7703202221428</v>
+      </c>
+      <c r="F108" s="3">
+        <v>782090</v>
+      </c>
+      <c r="G108" s="5">
+        <v>120906</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221381Retail</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C109" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="3">
+        <v>7703202221381</v>
+      </c>
+      <c r="F109" s="3">
+        <v>782089</v>
+      </c>
+      <c r="G109" s="5">
+        <v>120908</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735093664798064728Retail</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C110" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="3">
+        <v>3664798064728</v>
+      </c>
+      <c r="F110" s="3">
+        <v>846778</v>
+      </c>
+      <c r="G110" s="5">
+        <v>561351</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221244Retail</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C111" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="3">
+        <v>7703202221244</v>
+      </c>
+      <c r="F111" s="3">
+        <v>782065</v>
+      </c>
+      <c r="G111" s="5">
+        <v>20134</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221091Retail</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C112" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="3">
+        <v>7703202221091</v>
+      </c>
+      <c r="F112" s="3">
+        <v>797130</v>
+      </c>
+      <c r="G112" s="5">
+        <v>20131</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221305Retail</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C113" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="3">
+        <v>7703202221305</v>
+      </c>
+      <c r="F113" s="3">
+        <v>782086</v>
+      </c>
+      <c r="G113" s="5">
+        <v>20164</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221336Retail</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C114" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="3">
+        <v>7703202221336</v>
+      </c>
+      <c r="F114" s="3">
+        <v>782093</v>
+      </c>
+      <c r="G114" s="5">
+        <v>157863</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221312Retail</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C115" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="3">
+        <v>7703202221312</v>
+      </c>
+      <c r="F115" s="3">
+        <v>782091</v>
+      </c>
+      <c r="G115" s="5">
+        <v>20115</v>
+      </c>
+      <c r="H115" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221329Retail</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C116" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="3">
+        <v>7703202221329</v>
+      </c>
+      <c r="F116" s="3">
+        <v>782092</v>
+      </c>
+      <c r="G116" s="5">
+        <v>159030</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221275Retail</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C117" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="3">
+        <v>7703202221275</v>
+      </c>
+      <c r="F117" s="3">
+        <v>782074</v>
+      </c>
+      <c r="G117" s="5">
+        <v>54448</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221282Retail</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C118" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="3">
+        <v>7703202221282</v>
+      </c>
+      <c r="F118" s="3">
+        <v>782085</v>
+      </c>
+      <c r="G118" s="5">
+        <v>66022</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221169Retail</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C119" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="3">
+        <v>7703202221169</v>
+      </c>
+      <c r="F119" s="3">
+        <v>715503</v>
+      </c>
+      <c r="G119" s="5">
+        <v>20258</v>
+      </c>
+      <c r="H119" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221152Retail</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C120" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="3">
+        <v>7703202221152</v>
+      </c>
+      <c r="F120" s="3">
+        <v>715506</v>
+      </c>
+      <c r="G120" s="5">
+        <v>71766</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221176Retail</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C121" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="3">
+        <v>7703202221176</v>
+      </c>
+      <c r="F121" s="3">
+        <v>715717</v>
+      </c>
+      <c r="G121" s="5">
+        <v>63380</v>
+      </c>
+      <c r="H121" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735093664798069211Retail</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C122" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="3">
+        <v>3664798069211</v>
+      </c>
+      <c r="F122" s="3">
+        <v>715717</v>
+      </c>
+      <c r="G122" s="5">
+        <v>63380</v>
+      </c>
+      <c r="H122" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735093582910009900Retail</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C123" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="3">
+        <v>3582910009900</v>
+      </c>
+      <c r="F123" s="3">
+        <v>873229</v>
+      </c>
+      <c r="G123" s="5">
+        <v>121505</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097702771001561Retail</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C124" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="3">
+        <v>7702771001561</v>
+      </c>
+      <c r="F124" s="3">
+        <v>873239</v>
+      </c>
+      <c r="G124" s="5">
+        <v>129907</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097501165007956Retail</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C125" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="3">
+        <v>7501165007956</v>
+      </c>
+      <c r="F125" s="3">
+        <v>655678</v>
+      </c>
+      <c r="G125" s="5">
+        <v>114460</v>
+      </c>
+      <c r="H125" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202003475Retail</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C126" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="3">
+        <v>7703202003475</v>
+      </c>
+      <c r="F126" s="3">
+        <v>650554</v>
+      </c>
+      <c r="G126" s="5">
+        <v>145558</v>
+      </c>
+      <c r="H126" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221800Retail</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C127" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="3">
+        <v>7703202221800</v>
+      </c>
+      <c r="F127" s="3">
+        <v>893499</v>
+      </c>
+      <c r="G127" s="5">
+        <v>97353</v>
+      </c>
+      <c r="H127" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044401036Retail</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C128" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="3">
+        <v>7591044401036</v>
+      </c>
+      <c r="F128" s="3">
+        <v>723871</v>
+      </c>
+      <c r="G128" s="5">
+        <v>21450</v>
+      </c>
+      <c r="H128" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097501165010444Retail</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C129" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="3">
+        <v>7501165010444</v>
+      </c>
+      <c r="F129" s="3">
+        <v>600723</v>
+      </c>
+      <c r="G129" s="5">
+        <v>141268</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044009447Retail</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C130" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="3">
+        <v>7591044009447</v>
+      </c>
+      <c r="F130" s="3">
+        <v>120777</v>
+      </c>
+      <c r="G130" s="5">
+        <v>21714</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044007191Retail</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C131" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="3">
+        <v>7591044007191</v>
+      </c>
+      <c r="F131" s="3">
+        <v>120786</v>
+      </c>
+      <c r="G131" s="5">
+        <v>21716</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044008952Institucional</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C132" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E132" s="3">
+        <v>7591044008952</v>
+      </c>
+      <c r="F132" s="3">
+        <v>666269</v>
+      </c>
+      <c r="G132" s="5">
+        <v>78565</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044009010Institucional</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C133" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E133" s="3">
+        <v>7591044009010</v>
+      </c>
+      <c r="F133" s="3">
+        <v>732308</v>
+      </c>
+      <c r="G133" s="5">
+        <v>78566</v>
+      </c>
+      <c r="H133" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202010329Institucional</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C134" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E134" s="3">
+        <v>7703202010329</v>
+      </c>
+      <c r="F134" s="3">
+        <v>341667</v>
+      </c>
+      <c r="G134" s="5">
+        <v>84742</v>
+      </c>
+      <c r="H134" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097795312100090Institucional</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C135" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E135" s="3">
+        <v>7795312100090</v>
+      </c>
+      <c r="F135" s="3">
+        <v>785678</v>
+      </c>
+      <c r="G135" s="5">
+        <v>80460</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221428Institucional</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C136" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E136" s="3">
+        <v>7703202221428</v>
+      </c>
+      <c r="F136" s="3">
+        <v>782090</v>
+      </c>
+      <c r="G136" s="5">
+        <v>144732</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221381Institucional</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C137" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E137" s="3">
+        <v>7703202221381</v>
+      </c>
+      <c r="F137" s="3">
+        <v>782089</v>
+      </c>
+      <c r="G137" s="5">
+        <v>144638</v>
+      </c>
+      <c r="H137" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221244Institucional</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C138" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E138" s="3">
+        <v>7703202221244</v>
+      </c>
+      <c r="F138" s="3">
+        <v>782065</v>
+      </c>
+      <c r="G138" s="5">
+        <v>156861</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221091Institucional</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C139" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E139" s="3">
+        <v>7703202221091</v>
+      </c>
+      <c r="F139" s="3">
+        <v>797130</v>
+      </c>
+      <c r="G139" s="5">
+        <v>51294</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221312Institucional</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C140" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E140" s="3">
+        <v>7703202221312</v>
+      </c>
+      <c r="F140" s="3">
+        <v>782091</v>
+      </c>
+      <c r="G140" s="5">
+        <v>158353</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221305Institucional</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C141" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E141" s="3">
+        <v>7703202221305</v>
+      </c>
+      <c r="F141" s="3">
+        <v>782086</v>
+      </c>
+      <c r="G141" s="5">
+        <v>145615</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221275Institucional</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C142" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E142" s="3">
+        <v>7703202221275</v>
+      </c>
+      <c r="F142" s="3">
+        <v>782074</v>
+      </c>
+      <c r="G142" s="5">
+        <v>399766</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221282Institucional</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C143" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E143" s="3">
+        <v>7703202221282</v>
+      </c>
+      <c r="F143" s="3">
+        <v>782085</v>
+      </c>
+      <c r="G143" s="5">
+        <v>146961</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221169Institucional</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C144" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E144" s="3">
+        <v>7703202221169</v>
+      </c>
+      <c r="F144" s="3">
+        <v>715503</v>
+      </c>
+      <c r="G144" s="5">
+        <v>385952</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221152Institucional</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C145" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E145" s="3">
+        <v>7703202221152</v>
+      </c>
+      <c r="F145" s="3">
+        <v>715506</v>
+      </c>
+      <c r="G145" s="5">
+        <v>385946</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221176Institucional</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C146" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E146" s="3">
+        <v>7703202221176</v>
+      </c>
+      <c r="F146" s="3">
+        <v>715717</v>
+      </c>
+      <c r="G146" s="5">
+        <v>145617</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735093664798069211Institucional</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C147" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E147" s="3">
+        <v>3664798069211</v>
+      </c>
+      <c r="F147" s="3">
+        <v>715717</v>
+      </c>
+      <c r="G147" s="5">
+        <v>145617</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735093582910009900Institucional</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C148" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E148" s="3">
+        <v>3582910009900</v>
+      </c>
+      <c r="F148" s="3">
+        <v>873229</v>
+      </c>
+      <c r="G148" s="5">
+        <v>54706</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097702771001561Institucional</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C149" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E149" s="3">
+        <v>7702771001561</v>
+      </c>
+      <c r="F149" s="3">
+        <v>873239</v>
+      </c>
+      <c r="G149" s="5">
+        <v>537317</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097703202221800Institucional</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C150" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E150" s="3">
+        <v>7703202221800</v>
+      </c>
+      <c r="F150" s="3">
+        <v>893499</v>
+      </c>
+      <c r="G150" s="5">
+        <v>145619</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044401036Institucional</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C151" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E151" s="3">
+        <v>7591044401036</v>
+      </c>
+      <c r="F151" s="3">
+        <v>723871</v>
+      </c>
+      <c r="G151" s="5">
+        <v>120049</v>
+      </c>
+      <c r="H151" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097501165010444Institucional</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C152" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E152" s="3">
+        <v>7501165010444</v>
+      </c>
+      <c r="F152" s="3">
+        <v>120777</v>
+      </c>
+      <c r="G152" s="5">
+        <v>384773</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044009447Institucional</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C153" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E153" s="3">
+        <v>7591044009447</v>
+      </c>
+      <c r="F153" s="3">
+        <v>120786</v>
+      </c>
+      <c r="G153" s="5">
+        <v>384775</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735097591044007191Institucional</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C154" s="3">
+        <v>100173509</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E154" s="3">
+        <v>7591044007191</v>
+      </c>
+      <c r="F154" s="3">
+        <v>600723</v>
+      </c>
+      <c r="G154" s="5">
+        <v>384774</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077795312100090Retail</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C155" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="23">
+        <v>7795312100090</v>
+      </c>
+      <c r="F155" s="3">
+        <v>785678</v>
+      </c>
+      <c r="G155" s="22">
+        <v>1117327</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077591044008952Retail</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C156" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="23">
+        <v>7591044008952</v>
+      </c>
+      <c r="F156" s="3">
+        <v>666269</v>
+      </c>
+      <c r="G156" s="22">
+        <v>1010996</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077591044009010Retail</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C157" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="23">
+        <v>7591044009010</v>
+      </c>
+      <c r="F157" s="3">
+        <v>732308</v>
+      </c>
+      <c r="G157" s="22">
+        <v>1011422</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202010329Retail</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C158" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="23">
+        <v>7703202010329</v>
+      </c>
+      <c r="F158" s="3">
+        <v>341667</v>
+      </c>
+      <c r="G158" s="22">
+        <v>1130572</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077706263600645Retail</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C159" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="23">
+        <v>7706263600645</v>
+      </c>
+      <c r="F159" s="3">
+        <v>785678</v>
+      </c>
+      <c r="G159" s="22">
+        <v>100527</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077706263600621Retail</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C160" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="23">
+        <v>7706263600621</v>
+      </c>
+      <c r="F160" s="3">
+        <v>732308</v>
+      </c>
+      <c r="G160" s="22">
+        <v>70328</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077706263600638Retail</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C161" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="23">
+        <v>7706263600638</v>
+      </c>
+      <c r="F161" s="3">
+        <v>341667</v>
+      </c>
+      <c r="G161" s="22">
+        <v>70329</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221237Retail</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C162" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="23">
+        <v>7703202221237</v>
+      </c>
+      <c r="F162" s="3">
+        <v>782064</v>
+      </c>
+      <c r="G162" s="22">
+        <v>1283326</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221428Retail</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C163" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="23">
+        <v>7703202221428</v>
+      </c>
+      <c r="F163" s="3">
+        <v>782090</v>
+      </c>
+      <c r="G163" s="22">
+        <v>1283331</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221220Retail</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C164" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="23">
+        <v>7703202221220</v>
+      </c>
+      <c r="F164" s="3">
+        <v>781955</v>
+      </c>
+      <c r="G164" s="22">
+        <v>1283325</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221381Retail</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C165" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="23">
+        <v>7703202221381</v>
+      </c>
+      <c r="F165" s="3">
+        <v>782089</v>
+      </c>
+      <c r="G165" s="22">
+        <v>1283330</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202121230Retail</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C166" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="23">
+        <v>7703202121230</v>
+      </c>
+      <c r="F166" s="3">
+        <v>782064</v>
+      </c>
+      <c r="G166" s="22">
+        <v>72977</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202121223Retail</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C167" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="23">
+        <v>7703202121223</v>
+      </c>
+      <c r="F167" s="3">
+        <v>781955</v>
+      </c>
+      <c r="G167" s="22">
+        <v>72978</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221244Retail</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C168" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="23">
+        <v>7703202221244</v>
+      </c>
+      <c r="F168" s="3">
+        <v>782065</v>
+      </c>
+      <c r="G168" s="22">
+        <v>1283327</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221091Retail</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C169" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="23">
+        <v>7703202221091</v>
+      </c>
+      <c r="F169" s="3">
+        <v>797130</v>
+      </c>
+      <c r="G169" s="22">
+        <v>1284312</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221336Retail</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C170" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="23">
+        <v>7703202221336</v>
+      </c>
+      <c r="F170" s="3">
+        <v>782093</v>
+      </c>
+      <c r="G170" s="22">
+        <v>1289613</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221329Retail</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C171" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="23">
+        <v>7703202221329</v>
+      </c>
+      <c r="F171" s="3">
+        <v>782092</v>
+      </c>
+      <c r="G171" s="22">
+        <v>1289612</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221305Retail</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C172" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="23">
+        <v>7703202221305</v>
+      </c>
+      <c r="F172" s="3">
+        <v>782086</v>
+      </c>
+      <c r="G172" s="22">
+        <v>1283329</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221275Retail</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C173" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F173" s="3">
+        <v>782074</v>
+      </c>
+      <c r="G173" s="22">
+        <v>1283328</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202121292Retail</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C174" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="23">
+        <v>7703202121292</v>
+      </c>
+      <c r="F174" s="3">
+        <v>782085</v>
+      </c>
+      <c r="G174" s="22">
+        <v>78563</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221169Retail</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C175" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="23">
+        <v>7703202221169</v>
+      </c>
+      <c r="F175" s="3">
+        <v>715503</v>
+      </c>
+      <c r="G175" s="22">
+        <v>1283321</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221152Retail</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C176" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="23">
+        <v>7703202221152</v>
+      </c>
+      <c r="F176" s="3">
+        <v>715506</v>
+      </c>
+      <c r="G176" s="22">
+        <v>1283320</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221176Retail</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C177" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="23">
+        <v>7703202221176</v>
+      </c>
+      <c r="F177" s="3">
+        <v>715717</v>
+      </c>
+      <c r="G177" s="22">
+        <v>1283322</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202121155Retail</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C178" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="23">
+        <v>7703202121155</v>
+      </c>
+      <c r="F178" s="3">
+        <v>715506</v>
+      </c>
+      <c r="G178" s="22">
+        <v>78564</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735073582910009900Retail</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C179" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="23">
+        <v>3582910009900</v>
+      </c>
+      <c r="F179" s="3">
+        <v>873229</v>
+      </c>
+      <c r="G179" s="22">
+        <v>1203136</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077702771001561Retail</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C180" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="23">
+        <v>7702771001561</v>
+      </c>
+      <c r="F180" s="3">
+        <v>873239</v>
+      </c>
+      <c r="G180" s="22">
+        <v>1245994</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077706263600072Retail</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C181" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="23">
+        <v>7706263600072</v>
+      </c>
+      <c r="F181" s="3">
+        <v>873229</v>
+      </c>
+      <c r="G181" s="22">
+        <v>76061</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202003475Retail</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C182" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="23">
+        <v>7703202003475</v>
+      </c>
+      <c r="F182" s="3">
+        <v>650554</v>
+      </c>
+      <c r="G182" s="22">
+        <v>1281624</v>
+      </c>
+      <c r="H182" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077501165007956Retail</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C183" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="23">
+        <v>7501165007956</v>
+      </c>
+      <c r="F183" s="3">
+        <v>655678</v>
+      </c>
+      <c r="G183" s="22">
+        <v>1200431</v>
+      </c>
+      <c r="H183" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077703202221800Retail</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C184" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="23">
+        <v>7703202221800</v>
+      </c>
+      <c r="F184" s="3">
+        <v>893499</v>
+      </c>
+      <c r="G184" s="22">
+        <v>1361156</v>
+      </c>
+      <c r="H184" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077591044401036Retail</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C185" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="23">
+        <v>7591044401036</v>
+      </c>
+      <c r="F185" s="3">
+        <v>723871</v>
+      </c>
+      <c r="G185" s="22">
+        <v>1015474</v>
+      </c>
+      <c r="H185" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077501165010444Retail</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C186" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="23">
+        <v>7501165010444</v>
+      </c>
+      <c r="F186" s="3">
+        <v>600723</v>
+      </c>
+      <c r="G186" s="22">
+        <v>1281081</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735077706263600775Retail</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C187" s="3">
+        <v>100173507</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="23">
+        <v>7706263600775</v>
+      </c>
+      <c r="F187" s="3">
+        <v>723871</v>
+      </c>
+      <c r="G187" s="22">
+        <v>71073</v>
+      </c>
+      <c r="H187" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087591044008952Retail</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C188" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="26">
+        <v>7591044008952</v>
+      </c>
+      <c r="F188" s="3">
+        <v>666269</v>
+      </c>
+      <c r="G188" s="24">
+        <v>35106</v>
+      </c>
+      <c r="H188" s="25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087591044009010Retail</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C189" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="26">
+        <v>7591044009010</v>
+      </c>
+      <c r="F189" s="3">
+        <v>732308</v>
+      </c>
+      <c r="G189" s="24">
+        <v>35115</v>
+      </c>
+      <c r="H189" s="25" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202010329Retail</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C190" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="26">
+        <v>7703202010329</v>
+      </c>
+      <c r="F190" s="3">
+        <v>341667</v>
+      </c>
+      <c r="G190" s="24">
+        <v>35116</v>
+      </c>
+      <c r="H190" s="25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087795312100090Retail</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C191" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="26">
+        <v>7795312100090</v>
+      </c>
+      <c r="F191" s="3">
+        <v>785678</v>
+      </c>
+      <c r="G191" s="24">
+        <v>35157</v>
+      </c>
+      <c r="H191" s="25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221237Retail</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C192" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="26">
+        <v>7703202221237</v>
+      </c>
+      <c r="F192" s="3">
+        <v>782064</v>
+      </c>
+      <c r="G192" s="24">
+        <v>13146</v>
+      </c>
+      <c r="H192" s="25" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221428Retail</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C193" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="26">
+        <v>7703202221428</v>
+      </c>
+      <c r="F193" s="3">
+        <v>782090</v>
+      </c>
+      <c r="G193" s="24">
+        <v>13271</v>
+      </c>
+      <c r="H193" s="25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221220Retail</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C194" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="26">
+        <v>7703202221220</v>
+      </c>
+      <c r="F194" s="3">
+        <v>781955</v>
+      </c>
+      <c r="G194" s="24">
+        <v>13145</v>
+      </c>
+      <c r="H194" s="25" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221381Retail</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C195" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="26">
+        <v>7703202221381</v>
+      </c>
+      <c r="F195" s="3">
+        <v>782089</v>
+      </c>
+      <c r="G195" s="24">
+        <v>13275</v>
+      </c>
+      <c r="H195" s="25" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221244Retail</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C196" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="26">
+        <v>7703202221244</v>
+      </c>
+      <c r="F196" s="3">
+        <v>782065</v>
+      </c>
+      <c r="G196" s="24">
+        <v>13014</v>
+      </c>
+      <c r="H196" s="25" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221312Retail</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C197" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="26">
+        <v>7703202221312</v>
+      </c>
+      <c r="F197" s="3">
+        <v>782091</v>
+      </c>
+      <c r="G197" s="24">
+        <v>13303</v>
+      </c>
+      <c r="H197" s="25" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221329Retail</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C198" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="26">
+        <v>7703202221329</v>
+      </c>
+      <c r="F198" s="3">
+        <v>782092</v>
+      </c>
+      <c r="G198" s="24">
+        <v>13305</v>
+      </c>
+      <c r="H198" s="25" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221305Retail</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C199" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="26">
+        <v>7703202221305</v>
+      </c>
+      <c r="F199" s="3">
+        <v>782086</v>
+      </c>
+      <c r="G199" s="24">
+        <v>13051</v>
+      </c>
+      <c r="H199" s="25" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221275Retail</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C200" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="26">
+        <v>7703202221275</v>
+      </c>
+      <c r="F200" s="3">
+        <v>939016</v>
+      </c>
+      <c r="G200" s="24">
+        <v>13175</v>
+      </c>
+      <c r="H200" s="25" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221282Retail</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C201" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="26">
+        <v>7703202221282</v>
+      </c>
+      <c r="F201" s="3">
+        <v>782085</v>
+      </c>
+      <c r="G201" s="24">
+        <v>13189</v>
+      </c>
+      <c r="H201" s="25" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221091Retail</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C202" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" s="26">
+        <v>7703202221091</v>
+      </c>
+      <c r="F202" s="3">
+        <v>797130</v>
+      </c>
+      <c r="G202" s="24">
+        <v>13013</v>
+      </c>
+      <c r="H202" s="25" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087706263200364Retail</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C203" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="26">
+        <v>7706263200364</v>
+      </c>
+      <c r="F203" s="3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G203" s="24">
+        <v>42163</v>
+      </c>
+      <c r="H203" s="25" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087706263200388Retail</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C204" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="26">
+        <v>7706263200388</v>
+      </c>
+      <c r="F204" s="3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G204" s="24">
+        <v>42403</v>
+      </c>
+      <c r="H204" s="25" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221169Retail</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C205" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="26">
+        <v>7703202221169</v>
+      </c>
+      <c r="F205" s="3">
+        <v>715503</v>
+      </c>
+      <c r="G205" s="24">
+        <v>13081</v>
+      </c>
+      <c r="H205" s="25" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221152Retail</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C206" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="26">
+        <v>7703202221152</v>
+      </c>
+      <c r="F206" s="3">
+        <v>715506</v>
+      </c>
+      <c r="G206" s="24">
+        <v>13195</v>
+      </c>
+      <c r="H206" s="25" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221176Retail</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C207" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="26">
+        <v>7703202221176</v>
+      </c>
+      <c r="F207" s="3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G207" s="24">
+        <v>13179</v>
+      </c>
+      <c r="H207" s="25" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735083582910009900Retail</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C208" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="26">
+        <v>3582910009900</v>
+      </c>
+      <c r="F208" s="3">
+        <v>873229</v>
+      </c>
+      <c r="G208" s="24">
+        <v>14063</v>
+      </c>
+      <c r="H208" s="25" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087702771001561Retail</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C209" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209" s="26">
+        <v>7702771001561</v>
+      </c>
+      <c r="F209" s="3">
+        <v>873239</v>
+      </c>
+      <c r="G209" s="24">
+        <v>14068</v>
+      </c>
+      <c r="H209" s="25" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202003475Retail</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C210" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="26">
+        <v>7703202003475</v>
+      </c>
+      <c r="F210" s="3">
+        <v>650554</v>
+      </c>
+      <c r="G210" s="24">
+        <v>35232</v>
+      </c>
+      <c r="H210" s="25" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087501165007956Retail</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C211" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211" s="26">
+        <v>7501165007956</v>
+      </c>
+      <c r="F211" s="3">
+        <v>655678</v>
+      </c>
+      <c r="G211" s="24">
+        <v>35214</v>
+      </c>
+      <c r="H211" s="25" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087703202221800Retail</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C212" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E212" s="26">
+        <v>7703202221800</v>
+      </c>
+      <c r="F212" s="3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G212" s="24">
+        <v>276272</v>
+      </c>
+      <c r="H212" s="25" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087591044401036Retail</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C213" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E213" s="26">
+        <v>7591044401036</v>
+      </c>
+      <c r="F213" s="3">
+        <v>723871</v>
+      </c>
+      <c r="G213" s="24">
+        <v>77148</v>
+      </c>
+      <c r="H213" s="25" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087501165010444Retail</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C214" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" s="26">
+        <v>7501165010444</v>
+      </c>
+      <c r="F214" s="3">
+        <v>600723</v>
+      </c>
+      <c r="G214" s="24">
+        <v>35230</v>
+      </c>
+      <c r="H214" s="25" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087591044009225Retail</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C215" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" s="26">
+        <v>7591044009225</v>
+      </c>
+      <c r="F215" s="3">
+        <v>321589</v>
+      </c>
+      <c r="G215" s="24">
+        <v>35054</v>
+      </c>
+      <c r="H215" s="25" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087591044007191Retail</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C216" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216" s="26">
+        <v>7591044007191</v>
+      </c>
+      <c r="F216" s="3">
+        <v>120786</v>
+      </c>
+      <c r="G216" s="24">
+        <v>35057</v>
+      </c>
+      <c r="H216" s="25" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735087591044009447Retail</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C217" s="3">
+        <v>100173508</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217" s="26">
+        <v>7591044009447</v>
+      </c>
+      <c r="F217" s="3">
+        <v>120777</v>
+      </c>
+      <c r="G217" s="24">
+        <v>35056</v>
+      </c>
+      <c r="H217" s="25" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221275Retail</v>
+      </c>
+      <c r="B218" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C218" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D218" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F218" s="23">
+        <v>782074</v>
+      </c>
+      <c r="G218" s="22">
+        <v>7629</v>
+      </c>
+      <c r="H218" s="22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221244Retail</v>
+      </c>
+      <c r="B219" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C219" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D219" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219" s="23">
+        <v>7703202221244</v>
+      </c>
+      <c r="F219" s="23">
+        <v>782065</v>
+      </c>
+      <c r="G219" s="22">
+        <v>11729</v>
+      </c>
+      <c r="H219" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221329Retail</v>
+      </c>
+      <c r="B220" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C220" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D220" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E220" s="23">
+        <v>7703202221329</v>
+      </c>
+      <c r="F220" s="23">
+        <v>782092</v>
+      </c>
+      <c r="G220" s="22">
+        <v>11731</v>
+      </c>
+      <c r="H220" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221305Retail</v>
+      </c>
+      <c r="B221" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C221" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D221" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E221" s="23">
+        <v>7703202221305</v>
+      </c>
+      <c r="F221" s="23">
+        <v>782086</v>
+      </c>
+      <c r="G221" s="22">
+        <v>11732</v>
+      </c>
+      <c r="H221" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221312Retail</v>
+      </c>
+      <c r="B222" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C222" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D222" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="23">
+        <v>7703202221312</v>
+      </c>
+      <c r="F222" s="23">
+        <v>782091</v>
+      </c>
+      <c r="G222" s="22">
+        <v>11733</v>
+      </c>
+      <c r="H222" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221169Retail</v>
+      </c>
+      <c r="B223" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C223" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D223" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="23">
+        <v>7703202221169</v>
+      </c>
+      <c r="F223" s="23">
+        <v>715503</v>
+      </c>
+      <c r="G223" s="22">
+        <v>13221</v>
+      </c>
+      <c r="H223" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997591044007191Retail</v>
+      </c>
+      <c r="B224" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C224" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D224" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="23">
+        <v>7591044007191</v>
+      </c>
+      <c r="F224" s="23">
+        <v>120786</v>
+      </c>
+      <c r="G224" s="22">
+        <v>15124</v>
+      </c>
+      <c r="H224" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997591044009447Retail</v>
+      </c>
+      <c r="B225" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C225" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D225" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="23">
+        <v>7591044009447</v>
+      </c>
+      <c r="F225" s="23">
+        <v>120777</v>
+      </c>
+      <c r="G225" s="22">
+        <v>15129</v>
+      </c>
+      <c r="H225" s="22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221091Retail</v>
+      </c>
+      <c r="B226" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C226" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D226" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" s="23">
+        <v>7703202221091</v>
+      </c>
+      <c r="F226" s="23">
+        <v>797130</v>
+      </c>
+      <c r="G226" s="22">
+        <v>21977</v>
+      </c>
+      <c r="H226" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997591044008952Retail</v>
+      </c>
+      <c r="B227" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C227" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D227" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" s="23">
+        <v>7591044008952</v>
+      </c>
+      <c r="F227" s="23">
+        <v>666269</v>
+      </c>
+      <c r="G227" s="22">
+        <v>22878</v>
+      </c>
+      <c r="H227" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997501165007956Retail</v>
+      </c>
+      <c r="B228" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C228" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D228" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" s="23">
+        <v>7501165007956</v>
+      </c>
+      <c r="F228" s="23">
+        <v>655678</v>
+      </c>
+      <c r="G228" s="22">
+        <v>23893</v>
+      </c>
+      <c r="H228" s="22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997591044401036Retail</v>
+      </c>
+      <c r="B229" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C229" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D229" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" s="23">
+        <v>7591044401036</v>
+      </c>
+      <c r="F229" s="23">
+        <v>723871</v>
+      </c>
+      <c r="G229" s="22">
+        <v>25528</v>
+      </c>
+      <c r="H229" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997591044009010Retail</v>
+      </c>
+      <c r="B230" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C230" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D230" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" s="23">
+        <v>7591044009010</v>
+      </c>
+      <c r="F230" s="23">
+        <v>732308</v>
+      </c>
+      <c r="G230" s="22">
+        <v>25854</v>
+      </c>
+      <c r="H230" s="22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202010329Retail</v>
+      </c>
+      <c r="B231" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C231" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D231" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" s="23">
+        <v>7703202010329</v>
+      </c>
+      <c r="F231" s="23">
+        <v>341667</v>
+      </c>
+      <c r="G231" s="22">
+        <v>25860</v>
+      </c>
+      <c r="H231" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221220Retail</v>
+      </c>
+      <c r="B232" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C232" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D232" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E232" s="23">
+        <v>7703202221220</v>
+      </c>
+      <c r="F232" s="23">
+        <v>781955</v>
+      </c>
+      <c r="G232" s="22">
+        <v>26120</v>
+      </c>
+      <c r="H232" s="22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221336Retail</v>
+      </c>
+      <c r="B233" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C233" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D233" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233" s="23">
+        <v>7703202221336</v>
+      </c>
+      <c r="F233" s="23">
+        <v>782093</v>
+      </c>
+      <c r="G233" s="22">
+        <v>46950</v>
+      </c>
+      <c r="H233" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734993582910009900Retail</v>
+      </c>
+      <c r="B234" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C234" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D234" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" s="23">
+        <v>3582910009900</v>
+      </c>
+      <c r="F234" s="23">
+        <v>873229</v>
+      </c>
+      <c r="G234" s="22">
+        <v>47409</v>
+      </c>
+      <c r="H234" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221275Retail</v>
+      </c>
+      <c r="B235" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C235" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D235" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F235" s="23">
+        <v>939016</v>
+      </c>
+      <c r="G235" s="22">
+        <v>7629</v>
+      </c>
+      <c r="H235" s="22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221176Retail</v>
+      </c>
+      <c r="B236" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C236" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D236" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" s="23">
+        <v>7703202221176</v>
+      </c>
+      <c r="F236" s="23">
+        <v>715717</v>
+      </c>
+      <c r="G236" s="22">
+        <v>50348</v>
+      </c>
+      <c r="H236" s="22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703381002146Retail</v>
+      </c>
+      <c r="B237" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C237" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D237" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" s="23">
+        <v>7703381002146</v>
+      </c>
+      <c r="F237" s="23">
+        <v>715717</v>
+      </c>
+      <c r="G237" s="22">
+        <v>50348</v>
+      </c>
+      <c r="H237" s="22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221152Retail</v>
+      </c>
+      <c r="B238" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C238" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D238" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" s="23">
+        <v>7703202221152</v>
+      </c>
+      <c r="F238" s="23">
+        <v>715506</v>
+      </c>
+      <c r="G238" s="22">
+        <v>58826</v>
+      </c>
+      <c r="H238" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997795312100090Retail</v>
+      </c>
+      <c r="B239" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C239" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D239" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" s="23">
+        <v>7795312100090</v>
+      </c>
+      <c r="F239" s="23">
+        <v>785678</v>
+      </c>
+      <c r="G239" s="22">
+        <v>68585</v>
+      </c>
+      <c r="H239" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221800Retail</v>
+      </c>
+      <c r="B240" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C240" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D240" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240" s="23">
+        <v>7703202221800</v>
+      </c>
+      <c r="F240" s="23">
+        <v>893499</v>
+      </c>
+      <c r="G240" s="22">
+        <v>84797</v>
+      </c>
+      <c r="H240" s="22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221381Retail</v>
+      </c>
+      <c r="B241" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C241" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D241" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" s="23">
+        <v>7703202221381</v>
+      </c>
+      <c r="F241" s="23">
+        <v>782089</v>
+      </c>
+      <c r="G241" s="22">
+        <v>100904</v>
+      </c>
+      <c r="H241" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221428Retail</v>
+      </c>
+      <c r="B242" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C242" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D242" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" s="23">
+        <v>7703202221428</v>
+      </c>
+      <c r="F242" s="23">
+        <v>782090</v>
+      </c>
+      <c r="G242" s="22">
+        <v>100905</v>
+      </c>
+      <c r="H242" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997702771001561Retail</v>
+      </c>
+      <c r="B243" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C243" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D243" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243" s="23">
+        <v>7702771001561</v>
+      </c>
+      <c r="F243" s="23">
+        <v>873239</v>
+      </c>
+      <c r="G243" s="22">
+        <v>110323</v>
+      </c>
+      <c r="H243" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997501165010444Retail</v>
+      </c>
+      <c r="B244" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C244" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D244" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E244" s="23">
+        <v>7501165010444</v>
+      </c>
+      <c r="F244" s="23">
+        <v>600723</v>
+      </c>
+      <c r="G244" s="22">
+        <v>118952</v>
+      </c>
+      <c r="H244" s="22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221282Retail</v>
+      </c>
+      <c r="B245" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C245" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D245" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245" s="23">
+        <v>7703202221282</v>
+      </c>
+      <c r="F245" s="23">
+        <v>782085</v>
+      </c>
+      <c r="G245" s="22">
+        <v>120610</v>
+      </c>
+      <c r="H245" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202003475Retail</v>
+      </c>
+      <c r="B246" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C246" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D246" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246" s="23">
+        <v>7703202003475</v>
+      </c>
+      <c r="F246" s="23">
+        <v>650554</v>
+      </c>
+      <c r="G246" s="22">
+        <v>120771</v>
+      </c>
+      <c r="H246" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734993664798064728Retail</v>
+      </c>
+      <c r="B247" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C247" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D247" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247" s="23">
+        <v>3664798064728</v>
+      </c>
+      <c r="F247" s="23">
+        <v>846778</v>
+      </c>
+      <c r="G247" s="22">
+        <v>156006</v>
+      </c>
+      <c r="H247" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221275Retail</v>
+      </c>
+      <c r="B248" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C248" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D248" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F248" s="23">
+        <v>782074</v>
+      </c>
+      <c r="G248" s="22">
+        <v>100011666</v>
+      </c>
+      <c r="H248" s="22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107591044008952Retail</v>
+      </c>
+      <c r="B249" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C249" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D249" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E249" s="23">
+        <v>7591044008952</v>
+      </c>
+      <c r="F249" s="23">
+        <v>666269</v>
+      </c>
+      <c r="G249" s="22">
+        <v>100000317</v>
+      </c>
+      <c r="H249" s="22" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107591044009010Retail</v>
+      </c>
+      <c r="B250" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C250" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D250" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E250" s="23">
+        <v>7591044009010</v>
+      </c>
+      <c r="F250" s="23">
+        <v>732308</v>
+      </c>
+      <c r="G250" s="22">
+        <v>100000318</v>
+      </c>
+      <c r="H250" s="22" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107591044401036Retail</v>
+      </c>
+      <c r="B251" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C251" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D251" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251" s="23">
+        <v>7591044401036</v>
+      </c>
+      <c r="F251" s="23">
+        <v>723871</v>
+      </c>
+      <c r="G251" s="22">
+        <v>100000367</v>
+      </c>
+      <c r="H251" s="22" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107591044007191Retail</v>
+      </c>
+      <c r="B252" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C252" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D252" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" s="23">
+        <v>7591044007191</v>
+      </c>
+      <c r="F252" s="23">
+        <v>120786</v>
+      </c>
+      <c r="G252" s="22">
+        <v>100000376</v>
+      </c>
+      <c r="H252" s="22" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221237Retail</v>
+      </c>
+      <c r="B253" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C253" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D253" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" s="23">
+        <v>7703202221237</v>
+      </c>
+      <c r="F253" s="23">
+        <v>782064</v>
+      </c>
+      <c r="G253" s="22">
+        <v>100000914</v>
+      </c>
+      <c r="H253" s="22" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221220Retail</v>
+      </c>
+      <c r="B254" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C254" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D254" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" s="23">
+        <v>7703202221220</v>
+      </c>
+      <c r="F254" s="23">
+        <v>781955</v>
+      </c>
+      <c r="G254" s="22">
+        <v>100000916</v>
+      </c>
+      <c r="H254" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221091Retail</v>
+      </c>
+      <c r="B255" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C255" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D255" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255" s="23">
+        <v>7703202221091</v>
+      </c>
+      <c r="F255" s="23">
+        <v>797130</v>
+      </c>
+      <c r="G255" s="22">
+        <v>100000918</v>
+      </c>
+      <c r="H255" s="22" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221305Retail</v>
+      </c>
+      <c r="B256" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C256" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D256" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256" s="23">
+        <v>7703202221305</v>
+      </c>
+      <c r="F256" s="23">
+        <v>782086</v>
+      </c>
+      <c r="G256" s="22">
+        <v>100000924</v>
+      </c>
+      <c r="H256" s="22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221244Retail</v>
+      </c>
+      <c r="B257" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C257" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D257" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E257" s="23">
+        <v>7703202221244</v>
+      </c>
+      <c r="F257" s="23">
+        <v>782065</v>
+      </c>
+      <c r="G257" s="22">
+        <v>100007750</v>
+      </c>
+      <c r="H257" s="22" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221169Retail</v>
+      </c>
+      <c r="B258" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C258" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D258" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E258" s="23">
+        <v>7703202221169</v>
+      </c>
+      <c r="F258" s="23">
+        <v>715503</v>
+      </c>
+      <c r="G258" s="22">
+        <v>100007751</v>
+      </c>
+      <c r="H258" s="22" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735103582910009900Retail</v>
+      </c>
+      <c r="B259" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C259" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D259" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E259" s="23">
+        <v>3582910009900</v>
+      </c>
+      <c r="F259" s="23">
+        <v>873229</v>
+      </c>
+      <c r="G259" s="22">
+        <v>100011580</v>
+      </c>
+      <c r="H259" s="22" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221275Retail</v>
+      </c>
+      <c r="B260" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C260" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D260" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E260" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F260" s="23">
+        <v>939016</v>
+      </c>
+      <c r="G260" s="22">
+        <v>100011666</v>
+      </c>
+      <c r="H260" s="22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703381002146Retail</v>
+      </c>
+      <c r="B261" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C261" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D261" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E261" s="23">
+        <v>7703381002146</v>
+      </c>
+      <c r="F261" s="23">
+        <v>715717</v>
+      </c>
+      <c r="G261" s="22">
+        <v>100012451</v>
+      </c>
+      <c r="H261" s="22" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221282Retail</v>
+      </c>
+      <c r="B262" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C262" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D262" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262" s="23">
+        <v>7703202221282</v>
+      </c>
+      <c r="F262" s="23">
+        <v>782085</v>
+      </c>
+      <c r="G262" s="22">
+        <v>100013901</v>
+      </c>
+      <c r="H262" s="22" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221152Retail</v>
+      </c>
+      <c r="B263" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C263" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D263" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E263" s="23">
+        <v>7703202221152</v>
+      </c>
+      <c r="F263" s="23">
+        <v>715506</v>
+      </c>
+      <c r="G263" s="22">
+        <v>100014078</v>
+      </c>
+      <c r="H263" s="22" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107795312100090Retail</v>
+      </c>
+      <c r="B264" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C264" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D264" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E264" s="23">
+        <v>7795312100090</v>
+      </c>
+      <c r="F264" s="23">
+        <v>785678</v>
+      </c>
+      <c r="G264" s="22">
+        <v>100015676</v>
+      </c>
+      <c r="H264" s="22" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202010329Retail</v>
+      </c>
+      <c r="B265" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C265" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D265" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E265" s="23">
+        <v>7703202010329</v>
+      </c>
+      <c r="F265" s="23">
+        <v>341667</v>
+      </c>
+      <c r="G265" s="22">
+        <v>100016576</v>
+      </c>
+      <c r="H265" s="22" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107501165007956Retail</v>
+      </c>
+      <c r="B266" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C266" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D266" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E266" s="23">
+        <v>7501165007956</v>
+      </c>
+      <c r="F266" s="23">
+        <v>655678</v>
+      </c>
+      <c r="G266" s="22">
+        <v>100020434</v>
+      </c>
+      <c r="H266" s="22" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221428Retail</v>
+      </c>
+      <c r="B267" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C267" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D267" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E267" s="23">
+        <v>7703202221428</v>
+      </c>
+      <c r="F267" s="23">
+        <v>782090</v>
+      </c>
+      <c r="G267" s="22">
+        <v>100021503</v>
+      </c>
+      <c r="H267" s="22" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221381Retail</v>
+      </c>
+      <c r="B268" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C268" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D268" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268" s="23">
+        <v>7703202221381</v>
+      </c>
+      <c r="F268" s="23">
+        <v>782089</v>
+      </c>
+      <c r="G268" s="22">
+        <v>100021565</v>
+      </c>
+      <c r="H268" s="22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107702771001561Retail</v>
+      </c>
+      <c r="B269" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C269" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D269" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E269" s="23">
+        <v>7702771001561</v>
+      </c>
+      <c r="F269" s="23">
+        <v>873239</v>
+      </c>
+      <c r="G269" s="22">
+        <v>100022711</v>
+      </c>
+      <c r="H269" s="22" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107501165010444Retail</v>
+      </c>
+      <c r="B270" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C270" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D270" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E270" s="23">
+        <v>7501165010444</v>
+      </c>
+      <c r="F270" s="23">
+        <v>600723</v>
+      </c>
+      <c r="G270" s="22">
+        <v>100024193</v>
+      </c>
+      <c r="H270" s="22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221312Retail</v>
+      </c>
+      <c r="B271" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C271" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D271" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E271" s="23">
+        <v>7703202221312</v>
+      </c>
+      <c r="F271" s="23">
+        <v>782091</v>
+      </c>
+      <c r="G271" s="22">
+        <v>100024939</v>
+      </c>
+      <c r="H271" s="22" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221329Retail</v>
+      </c>
+      <c r="B272" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C272" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D272" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E272" s="23">
+        <v>7703202221329</v>
+      </c>
+      <c r="F272" s="23">
+        <v>782092</v>
+      </c>
+      <c r="G272" s="22">
+        <v>100024940</v>
+      </c>
+      <c r="H272" s="22" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202221336Retail</v>
+      </c>
+      <c r="B273" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C273" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D273" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E273" s="23">
+        <v>7703202221336</v>
+      </c>
+      <c r="F273" s="23">
+        <v>782093</v>
+      </c>
+      <c r="G273" s="22">
+        <v>100024941</v>
+      </c>
+      <c r="H273" s="22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107703202003475Retail</v>
+      </c>
+      <c r="B274" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C274" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D274" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E274" s="23">
+        <v>7703202003475</v>
+      </c>
+      <c r="F274" s="23">
+        <v>650554</v>
+      </c>
+      <c r="G274" s="22">
+        <v>100024967</v>
+      </c>
+      <c r="H274" s="22" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735103664798067910Retail</v>
+      </c>
+      <c r="B275" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C275" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D275" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E275" s="23">
+        <v>3664798067910</v>
+      </c>
+      <c r="F275" s="23">
+        <v>892229</v>
+      </c>
+      <c r="G275" s="22">
+        <v>100028083</v>
+      </c>
+      <c r="H275" s="22" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735103664798064728Retail</v>
+      </c>
+      <c r="B276" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C276" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D276" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E276" s="23">
+        <v>3664798064728</v>
+      </c>
+      <c r="F276" s="23">
+        <v>846778</v>
+      </c>
+      <c r="G276" s="22">
+        <v>100028123</v>
+      </c>
+      <c r="H276" s="22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735107591044009447Retail</v>
+      </c>
+      <c r="B277" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C277" s="23">
+        <v>100173510</v>
+      </c>
+      <c r="D277" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E277" s="23">
+        <v>7591044009447</v>
+      </c>
+      <c r="F277" s="23">
+        <v>120777</v>
+      </c>
+      <c r="G277" s="22">
+        <v>100000375</v>
+      </c>
+      <c r="H277" s="22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221220Retail</v>
+      </c>
+      <c r="B278" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C278" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D278" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E278" s="23">
+        <v>7703202221220</v>
+      </c>
+      <c r="F278" s="23">
+        <v>781955</v>
+      </c>
+      <c r="G278" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="H278" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221428Retail</v>
+      </c>
+      <c r="B279" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C279" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D279" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E279" s="23">
+        <v>7703202221428</v>
+      </c>
+      <c r="F279" s="23">
+        <v>782090</v>
+      </c>
+      <c r="G279" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="H279" s="22" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221381Retail</v>
+      </c>
+      <c r="B280" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C280" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D280" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E280" s="23">
+        <v>7703202221381</v>
+      </c>
+      <c r="F280" s="23">
+        <v>782089</v>
+      </c>
+      <c r="G280" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="H280" s="22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221305Retail</v>
+      </c>
+      <c r="B281" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C281" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D281" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281" s="23">
+        <v>7703202221305</v>
+      </c>
+      <c r="F281" s="23">
+        <v>782086</v>
+      </c>
+      <c r="G281" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="H281" s="22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221336Retail</v>
+      </c>
+      <c r="B282" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C282" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D282" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E282" s="23">
+        <v>7703202221336</v>
+      </c>
+      <c r="F282" s="23">
+        <v>782093</v>
+      </c>
+      <c r="G282" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="H282" s="22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221329Retail</v>
+      </c>
+      <c r="B283" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C283" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D283" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E283" s="23">
+        <v>7703202221329</v>
+      </c>
+      <c r="F283" s="23">
+        <v>782092</v>
+      </c>
+      <c r="G283" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="H283" s="22" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221312Retail</v>
+      </c>
+      <c r="B284" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C284" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D284" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284" s="23">
+        <v>7703202221312</v>
+      </c>
+      <c r="F284" s="23">
+        <v>782091</v>
+      </c>
+      <c r="G284" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="H284" s="22" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734997703202221275Retail</v>
+      </c>
+      <c r="B285" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C285" s="23">
+        <v>100173499</v>
+      </c>
+      <c r="D285" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E285" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F285" s="23">
+        <v>782074</v>
+      </c>
+      <c r="G285" s="22">
+        <v>47598</v>
+      </c>
+      <c r="H285" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221282Retail</v>
+      </c>
+      <c r="B286" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C286" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D286" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E286" s="23">
+        <v>7703202221282</v>
+      </c>
+      <c r="F286" s="23">
+        <v>782085</v>
+      </c>
+      <c r="G286" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="H286" s="22" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221244Retail</v>
+      </c>
+      <c r="B287" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C287" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D287" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E287" s="23">
+        <v>7703202221244</v>
+      </c>
+      <c r="F287" s="23">
+        <v>782065</v>
+      </c>
+      <c r="G287" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="H287" s="22" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221169Retail</v>
+      </c>
+      <c r="B288" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C288" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D288" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E288" s="23">
+        <v>7703202221169</v>
+      </c>
+      <c r="F288" s="23">
+        <v>715503</v>
+      </c>
+      <c r="G288" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="H288" s="22" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221152Retail</v>
+      </c>
+      <c r="B289" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C289" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D289" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E289" s="23">
+        <v>7703202221152</v>
+      </c>
+      <c r="F289" s="23">
+        <v>715506</v>
+      </c>
+      <c r="G289" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="H289" s="22" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735273664798069211Retail</v>
+      </c>
+      <c r="B290" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C290" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D290" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E290" s="23">
+        <v>3664798069211</v>
+      </c>
+      <c r="F290" s="23">
+        <v>715717</v>
+      </c>
+      <c r="G290" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="H290" s="22" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735273664798064728Retail</v>
+      </c>
+      <c r="B291" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C291" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D291" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E291" s="23">
+        <v>3664798064728</v>
+      </c>
+      <c r="F291" s="23">
+        <v>846778</v>
+      </c>
+      <c r="G291" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="H291" s="22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735273664798066531Retail</v>
+      </c>
+      <c r="B292" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C292" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D292" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292" s="23">
+        <v>3664798066531</v>
+      </c>
+      <c r="F292" s="23">
+        <v>882451</v>
+      </c>
+      <c r="G292" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="H292" s="22" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202010329Retail</v>
+      </c>
+      <c r="B293" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C293" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D293" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E293" s="23">
+        <v>7703202010329</v>
+      </c>
+      <c r="F293" s="23">
+        <v>341667</v>
+      </c>
+      <c r="G293" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="H293" s="22" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277591044009010Retail</v>
+      </c>
+      <c r="B294" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C294" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D294" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E294" s="23">
+        <v>7591044009010</v>
+      </c>
+      <c r="F294" s="23">
+        <v>732308</v>
+      </c>
+      <c r="G294" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="H294" s="22" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277591044008952Retail</v>
+      </c>
+      <c r="B295" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C295" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D295" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E295" s="23">
+        <v>7591044008952</v>
+      </c>
+      <c r="F295" s="23">
+        <v>666269</v>
+      </c>
+      <c r="G295" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="H295" s="22" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277795312100090Retail</v>
+      </c>
+      <c r="B296" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C296" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D296" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E296" s="23">
+        <v>7795312100090</v>
+      </c>
+      <c r="F296" s="23">
+        <v>785678</v>
+      </c>
+      <c r="G296" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="H296" s="22" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277591044009447Retail</v>
+      </c>
+      <c r="B297" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C297" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D297" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E297" s="23">
+        <v>7591044009447</v>
+      </c>
+      <c r="F297" s="23">
+        <v>120777</v>
+      </c>
+      <c r="G297" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="H297" s="22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277591044007191Retail</v>
+      </c>
+      <c r="B298" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C298" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D298" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E298" s="23">
+        <v>7591044007191</v>
+      </c>
+      <c r="F298" s="23">
+        <v>120786</v>
+      </c>
+      <c r="G298" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="H298" s="22" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735273582910009900Retail</v>
+      </c>
+      <c r="B299" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C299" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D299" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E299" s="23">
+        <v>3582910009900</v>
+      </c>
+      <c r="F299" s="23">
+        <v>873229</v>
+      </c>
+      <c r="G299" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="H299" s="22" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277501165007956Retail</v>
+      </c>
+      <c r="B300" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C300" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D300" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E300" s="23">
+        <v>7501165007956</v>
+      </c>
+      <c r="F300" s="23">
+        <v>655678</v>
+      </c>
+      <c r="G300" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="H300" s="22" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277591044401036Retail</v>
+      </c>
+      <c r="B301" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C301" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D301" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E301" s="23">
+        <v>7591044401036</v>
+      </c>
+      <c r="F301" s="23">
+        <v>723871</v>
+      </c>
+      <c r="G301" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="H301" s="22" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277501165010444Retail</v>
+      </c>
+      <c r="B302" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C302" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D302" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E302" s="23">
+        <v>7501165010444</v>
+      </c>
+      <c r="F302" s="23">
+        <v>600723</v>
+      </c>
+      <c r="G302" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="H302" s="22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221091Retail</v>
+      </c>
+      <c r="B303" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C303" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D303" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E303" s="23">
+        <v>7703202221091</v>
+      </c>
+      <c r="F303" s="23">
+        <v>797130</v>
+      </c>
+      <c r="G303" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="H303" s="22" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277702771001561Retail</v>
+      </c>
+      <c r="B304" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C304" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D304" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E304" s="23">
+        <v>7702771001561</v>
+      </c>
+      <c r="F304" s="23">
+        <v>873239</v>
+      </c>
+      <c r="G304" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="H304" s="22" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202003475Retail</v>
+      </c>
+      <c r="B305" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C305" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D305" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E305" s="23">
+        <v>7703202003475</v>
+      </c>
+      <c r="F305" s="23">
+        <v>650554</v>
+      </c>
+      <c r="G305" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="H305" s="22" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221107Retail</v>
+      </c>
+      <c r="B306" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C306" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D306" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E306" s="23">
+        <v>7703202221107</v>
+      </c>
+      <c r="F306" s="23">
+        <v>797125</v>
+      </c>
+      <c r="G306" s="22">
+        <v>253026</v>
+      </c>
+      <c r="H306" s="22" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677591044008952Retail</v>
+      </c>
+      <c r="B307" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C307" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D307" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E307" s="23">
+        <v>7591044008952</v>
+      </c>
+      <c r="F307" s="23">
+        <v>666269</v>
+      </c>
+      <c r="G307" s="22">
+        <v>7608</v>
+      </c>
+      <c r="H307" s="22" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734673664798066531Retail</v>
+      </c>
+      <c r="B308" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C308" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D308" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E308" s="23">
+        <v>3664798066531</v>
+      </c>
+      <c r="F308" s="23">
+        <v>882451</v>
+      </c>
+      <c r="G308" s="22">
+        <v>0</v>
+      </c>
+      <c r="H308" s="22" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677591044009010Retail</v>
+      </c>
+      <c r="B309" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C309" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D309" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E309" s="23">
+        <v>7591044009010</v>
+      </c>
+      <c r="F309" s="23">
+        <v>732308</v>
+      </c>
+      <c r="G309" s="22">
+        <v>7606</v>
+      </c>
+      <c r="H309" s="22" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202010329Retail</v>
+      </c>
+      <c r="B310" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C310" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D310" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E310" s="23">
+        <v>7703202010329</v>
+      </c>
+      <c r="F310" s="23">
+        <v>341667</v>
+      </c>
+      <c r="G310" s="22">
+        <v>7598</v>
+      </c>
+      <c r="H310" s="22" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677795312100090Retail</v>
+      </c>
+      <c r="B311" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C311" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D311" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E311" s="23">
+        <v>7795312100090</v>
+      </c>
+      <c r="F311" s="23">
+        <v>785678</v>
+      </c>
+      <c r="G311" s="22">
+        <v>7607</v>
+      </c>
+      <c r="H311" s="22" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221428Retail</v>
+      </c>
+      <c r="B312" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C312" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D312" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E312" s="23">
+        <v>7703202221428</v>
+      </c>
+      <c r="F312" s="23">
+        <v>782090</v>
+      </c>
+      <c r="G312" s="22">
+        <v>7609</v>
+      </c>
+      <c r="H312" s="22" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221220Retail</v>
+      </c>
+      <c r="B313" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C313" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D313" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E313" s="23">
+        <v>7703202221220</v>
+      </c>
+      <c r="F313" s="23">
+        <v>781955</v>
+      </c>
+      <c r="G313" s="22">
+        <v>7600</v>
+      </c>
+      <c r="H313" s="22" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221381Retail</v>
+      </c>
+      <c r="B314" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C314" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D314" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E314" s="23">
+        <v>7703202221381</v>
+      </c>
+      <c r="F314" s="23">
+        <v>782089</v>
+      </c>
+      <c r="G314" s="22">
+        <v>7599</v>
+      </c>
+      <c r="H314" s="22" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734673664798064728Retail</v>
+      </c>
+      <c r="B315" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C315" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D315" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E315" s="23">
+        <v>3664798064728</v>
+      </c>
+      <c r="F315" s="23">
+        <v>846778</v>
+      </c>
+      <c r="G315" s="22">
+        <v>436076</v>
+      </c>
+      <c r="H315" s="22" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221244Retail</v>
+      </c>
+      <c r="B316" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C316" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D316" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E316" s="23">
+        <v>7703202221244</v>
+      </c>
+      <c r="F316" s="23">
+        <v>782065</v>
+      </c>
+      <c r="G316" s="22">
+        <v>7588</v>
+      </c>
+      <c r="H316" s="22" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221336Retail</v>
+      </c>
+      <c r="B317" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C317" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D317" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E317" s="23">
+        <v>7703202221336</v>
+      </c>
+      <c r="F317" s="23">
+        <v>782093</v>
+      </c>
+      <c r="G317" s="22">
+        <v>7637</v>
+      </c>
+      <c r="H317" s="22" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221312Retail</v>
+      </c>
+      <c r="B318" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C318" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D318" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E318" s="23">
+        <v>7703202221312</v>
+      </c>
+      <c r="F318" s="23">
+        <v>782091</v>
+      </c>
+      <c r="G318" s="22">
+        <v>7636</v>
+      </c>
+      <c r="H318" s="22" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221329Retail</v>
+      </c>
+      <c r="B319" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C319" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D319" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E319" s="23">
+        <v>7703202221329</v>
+      </c>
+      <c r="F319" s="23">
+        <v>782092</v>
+      </c>
+      <c r="G319" s="22">
+        <v>7612</v>
+      </c>
+      <c r="H319" s="22" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221343Retail</v>
+      </c>
+      <c r="B320" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C320" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D320" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E320" s="23">
+        <v>7703202221343</v>
+      </c>
+      <c r="F320" s="23">
+        <v>782094</v>
+      </c>
+      <c r="G320" s="22">
+        <v>21971</v>
+      </c>
+      <c r="H320" s="22" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221305Retail</v>
+      </c>
+      <c r="B321" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C321" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D321" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E321" s="23">
+        <v>7703202221305</v>
+      </c>
+      <c r="F321" s="23">
+        <v>782086</v>
+      </c>
+      <c r="G321" s="22">
+        <v>7584</v>
+      </c>
+      <c r="H321" s="22" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221268Retail</v>
+      </c>
+      <c r="B322" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C322" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D322" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E322" s="23">
+        <v>7703202221268</v>
+      </c>
+      <c r="F322" s="23">
+        <v>782066</v>
+      </c>
+      <c r="G322" s="22">
+        <v>7628</v>
+      </c>
+      <c r="H322" s="22" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221282Retail</v>
+      </c>
+      <c r="B323" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C323" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D323" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E323" s="23">
+        <v>7703202221282</v>
+      </c>
+      <c r="F323" s="23">
+        <v>782085</v>
+      </c>
+      <c r="G323" s="22">
+        <v>7630</v>
+      </c>
+      <c r="H323" s="22" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221091Retail</v>
+      </c>
+      <c r="B324" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C324" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D324" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E324" s="23">
+        <v>7703202221091</v>
+      </c>
+      <c r="F324" s="23">
+        <v>797130</v>
+      </c>
+      <c r="G324" s="22">
+        <v>7587</v>
+      </c>
+      <c r="H324" s="22" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221169Retail</v>
+      </c>
+      <c r="B325" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C325" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D325" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E325" s="23">
+        <v>7703202221169</v>
+      </c>
+      <c r="F325" s="23">
+        <v>715503</v>
+      </c>
+      <c r="G325" s="22">
+        <v>7590</v>
+      </c>
+      <c r="H325" s="22" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221152Retail</v>
+      </c>
+      <c r="B326" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C326" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D326" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E326" s="23">
+        <v>7703202221152</v>
+      </c>
+      <c r="F326" s="23">
+        <v>715506</v>
+      </c>
+      <c r="G326" s="22">
+        <v>7589</v>
+      </c>
+      <c r="H326" s="22" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221176Retail</v>
+      </c>
+      <c r="B327" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C327" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D327" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E327" s="23">
+        <v>7703202221176</v>
+      </c>
+      <c r="F327" s="23">
+        <v>715717</v>
+      </c>
+      <c r="G327" s="22">
+        <v>7586</v>
+      </c>
+      <c r="H327" s="22" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734673582910009900Retail</v>
+      </c>
+      <c r="B328" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C328" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D328" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E328" s="23">
+        <v>3582910009900</v>
+      </c>
+      <c r="F328" s="23">
+        <v>873229</v>
+      </c>
+      <c r="G328" s="22">
+        <v>7620</v>
+      </c>
+      <c r="H328" s="22" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677702771001561Retail</v>
+      </c>
+      <c r="B329" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C329" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D329" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E329" s="23">
+        <v>7702771001561</v>
+      </c>
+      <c r="F329" s="23">
+        <v>873239</v>
+      </c>
+      <c r="G329" s="22">
+        <v>7619</v>
+      </c>
+      <c r="H329" s="22" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202003475Retail</v>
+      </c>
+      <c r="B330" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C330" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D330" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E330" s="23">
+        <v>7703202003475</v>
+      </c>
+      <c r="F330" s="23">
+        <v>650554</v>
+      </c>
+      <c r="G330" s="22">
+        <v>7635</v>
+      </c>
+      <c r="H330" s="22" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677501165007956Retail</v>
+      </c>
+      <c r="B331" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C331" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D331" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E331" s="23">
+        <v>7501165007956</v>
+      </c>
+      <c r="F331" s="23">
+        <v>655678</v>
+      </c>
+      <c r="G331" s="22">
+        <v>7634</v>
+      </c>
+      <c r="H331" s="22" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677591044401036Retail</v>
+      </c>
+      <c r="B332" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C332" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D332" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E332" s="23">
+        <v>7591044401036</v>
+      </c>
+      <c r="F332" s="23">
+        <v>723871</v>
+      </c>
+      <c r="G332" s="22">
+        <v>7591</v>
+      </c>
+      <c r="H332" s="22" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677591044009447Retail</v>
+      </c>
+      <c r="B333" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C333" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D333" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E333" s="23">
+        <v>7591044009447</v>
+      </c>
+      <c r="F333" s="23">
+        <v>120777</v>
+      </c>
+      <c r="G333" s="22">
+        <v>7596</v>
+      </c>
+      <c r="H333" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677591044007191Retail</v>
+      </c>
+      <c r="B334" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C334" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D334" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E334" s="23">
+        <v>7591044007191</v>
+      </c>
+      <c r="F334" s="23">
+        <v>120786</v>
+      </c>
+      <c r="G334" s="22">
+        <v>13921</v>
+      </c>
+      <c r="H334" s="22" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677501165010444Retail</v>
+      </c>
+      <c r="B335" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C335" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D335" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E335" s="23">
+        <v>7501165010444</v>
+      </c>
+      <c r="F335" s="23">
+        <v>600723</v>
+      </c>
+      <c r="G335" s="22">
+        <v>7594</v>
+      </c>
+      <c r="H335" s="22" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734677703202221107Retail</v>
+      </c>
+      <c r="B336" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C336" s="23">
+        <v>100173467</v>
+      </c>
+      <c r="D336" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E336" s="23">
+        <v>7703202221107</v>
+      </c>
+      <c r="F336" s="23">
+        <v>797125</v>
+      </c>
+      <c r="G336" s="22">
+        <v>7617</v>
+      </c>
+      <c r="H336" s="22" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497591044009447Retail</v>
+      </c>
+      <c r="B337" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C337" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D337" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E337" s="23">
+        <v>7591044009447</v>
+      </c>
+      <c r="F337" s="23">
+        <v>120777</v>
+      </c>
+      <c r="G337" s="22">
+        <v>0</v>
+      </c>
+      <c r="H337" s="22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497591044007191Retail</v>
+      </c>
+      <c r="B338" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C338" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D338" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E338" s="23">
+        <v>7591044007191</v>
+      </c>
+      <c r="F338" s="23">
+        <v>120786</v>
+      </c>
+      <c r="G338" s="22">
+        <v>0</v>
+      </c>
+      <c r="H338" s="22" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202010329Retail</v>
+      </c>
+      <c r="B339" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C339" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D339" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E339" s="23">
+        <v>7703202010329</v>
+      </c>
+      <c r="F339" s="23">
+        <v>341667</v>
+      </c>
+      <c r="G339" s="22">
+        <v>0</v>
+      </c>
+      <c r="H339" s="22" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497701165010444Retail</v>
+      </c>
+      <c r="B340" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C340" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D340" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E340" s="23">
+        <v>7701165010444</v>
+      </c>
+      <c r="F340" s="23">
+        <v>600723</v>
+      </c>
+      <c r="G340" s="22">
+        <v>0</v>
+      </c>
+      <c r="H340" s="22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202003475Retail</v>
+      </c>
+      <c r="B341" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C341" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D341" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E341" s="23">
+        <v>7703202003475</v>
+      </c>
+      <c r="F341" s="23">
+        <v>650554</v>
+      </c>
+      <c r="G341" s="22">
+        <v>0</v>
+      </c>
+      <c r="H341" s="22" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497501165007956Retail</v>
+      </c>
+      <c r="B342" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C342" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D342" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E342" s="23">
+        <v>7501165007956</v>
+      </c>
+      <c r="F342" s="23">
+        <v>655678</v>
+      </c>
+      <c r="G342" s="22">
+        <v>0</v>
+      </c>
+      <c r="H342" s="22" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497591044008952Retail</v>
+      </c>
+      <c r="B343" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C343" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D343" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E343" s="23">
+        <v>7591044008952</v>
+      </c>
+      <c r="F343" s="23">
+        <v>666269</v>
+      </c>
+      <c r="G343" s="22">
+        <v>0</v>
+      </c>
+      <c r="H343" s="22" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221169Retail</v>
+      </c>
+      <c r="B344" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C344" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D344" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E344" s="23">
+        <v>7703202221169</v>
+      </c>
+      <c r="F344" s="23">
+        <v>715503</v>
+      </c>
+      <c r="G344" s="22">
+        <v>0</v>
+      </c>
+      <c r="H344" s="22" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221152Retail</v>
+      </c>
+      <c r="B345" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C345" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D345" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E345" s="23">
+        <v>7703202221152</v>
+      </c>
+      <c r="F345" s="23">
+        <v>715506</v>
+      </c>
+      <c r="G345" s="22">
+        <v>0</v>
+      </c>
+      <c r="H345" s="22" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703381002146Retail</v>
+      </c>
+      <c r="B346" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C346" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D346" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E346" s="23">
+        <v>7703381002146</v>
+      </c>
+      <c r="F346" s="23">
+        <v>715717</v>
+      </c>
+      <c r="G346" s="22">
+        <v>0</v>
+      </c>
+      <c r="H346" s="22" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497591044401036Retail</v>
+      </c>
+      <c r="B347" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C347" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D347" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E347" s="23">
+        <v>7591044401036</v>
+      </c>
+      <c r="F347" s="23">
+        <v>723871</v>
+      </c>
+      <c r="G347" s="22">
+        <v>0</v>
+      </c>
+      <c r="H347" s="22" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497591044009010Retail</v>
+      </c>
+      <c r="B348" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C348" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D348" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E348" s="23">
+        <v>7591044009010</v>
+      </c>
+      <c r="F348" s="23">
+        <v>732308</v>
+      </c>
+      <c r="G348" s="22">
+        <v>0</v>
+      </c>
+      <c r="H348" s="22" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221220Retail</v>
+      </c>
+      <c r="B349" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C349" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D349" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E349" s="23">
+        <v>7703202221220</v>
+      </c>
+      <c r="F349" s="23">
+        <v>781955</v>
+      </c>
+      <c r="G349" s="22">
+        <v>0</v>
+      </c>
+      <c r="H349" s="22" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221244Retail</v>
+      </c>
+      <c r="B350" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C350" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D350" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E350" s="23">
+        <v>7703202221244</v>
+      </c>
+      <c r="F350" s="23">
+        <v>782065</v>
+      </c>
+      <c r="G350" s="22">
+        <v>0</v>
+      </c>
+      <c r="H350" s="22" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221282Retail</v>
+      </c>
+      <c r="B351" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C351" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D351" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E351" s="23">
+        <v>7703202221282</v>
+      </c>
+      <c r="F351" s="23">
+        <v>782085</v>
+      </c>
+      <c r="G351" s="22">
+        <v>0</v>
+      </c>
+      <c r="H351" s="22" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221305Retail</v>
+      </c>
+      <c r="B352" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C352" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D352" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E352" s="23">
+        <v>7703202221305</v>
+      </c>
+      <c r="F352" s="23">
+        <v>782086</v>
+      </c>
+      <c r="G352" s="22">
+        <v>0</v>
+      </c>
+      <c r="H352" s="22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221381Retail</v>
+      </c>
+      <c r="B353" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C353" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D353" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E353" s="23">
+        <v>7703202221381</v>
+      </c>
+      <c r="F353" s="23">
+        <v>782089</v>
+      </c>
+      <c r="G353" s="22">
+        <v>0</v>
+      </c>
+      <c r="H353" s="22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221428Retail</v>
+      </c>
+      <c r="B354" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C354" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D354" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E354" s="23">
+        <v>7703202221428</v>
+      </c>
+      <c r="F354" s="23">
+        <v>782090</v>
+      </c>
+      <c r="G354" s="22">
+        <v>0</v>
+      </c>
+      <c r="H354" s="22" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221312Retail</v>
+      </c>
+      <c r="B355" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C355" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D355" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E355" s="23">
+        <v>7703202221312</v>
+      </c>
+      <c r="F355" s="23">
+        <v>782091</v>
+      </c>
+      <c r="G355" s="22">
+        <v>0</v>
+      </c>
+      <c r="H355" s="22" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221329Retail</v>
+      </c>
+      <c r="B356" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C356" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D356" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E356" s="23">
+        <v>7703202221329</v>
+      </c>
+      <c r="F356" s="23">
+        <v>782092</v>
+      </c>
+      <c r="G356" s="22">
+        <v>0</v>
+      </c>
+      <c r="H356" s="22" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221336Retail</v>
+      </c>
+      <c r="B357" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C357" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D357" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E357" s="23">
+        <v>7703202221336</v>
+      </c>
+      <c r="F357" s="23">
+        <v>782093</v>
+      </c>
+      <c r="G357" s="22">
+        <v>0</v>
+      </c>
+      <c r="H357" s="22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497795312100090Retail</v>
+      </c>
+      <c r="B358" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C358" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D358" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E358" s="23">
+        <v>7795312100090</v>
+      </c>
+      <c r="F358" s="23">
+        <v>785678</v>
+      </c>
+      <c r="G358" s="22">
+        <v>0</v>
+      </c>
+      <c r="H358" s="22" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221091Retail</v>
+      </c>
+      <c r="B359" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C359" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D359" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E359" s="23">
+        <v>7703202221091</v>
+      </c>
+      <c r="F359" s="23">
+        <v>797130</v>
+      </c>
+      <c r="G359" s="22">
+        <v>0</v>
+      </c>
+      <c r="H359" s="22" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734493664798064728Retail</v>
+      </c>
+      <c r="B360" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C360" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D360" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E360" s="23">
+        <v>3664798064728</v>
+      </c>
+      <c r="F360" s="23">
+        <v>846778</v>
+      </c>
+      <c r="G360" s="22">
+        <v>0</v>
+      </c>
+      <c r="H360" s="22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734493582910009900Retail</v>
+      </c>
+      <c r="B361" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C361" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D361" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E361" s="23">
+        <v>3582910009900</v>
+      </c>
+      <c r="F361" s="23">
+        <v>873229</v>
+      </c>
+      <c r="G361" s="22">
+        <v>0</v>
+      </c>
+      <c r="H361" s="22" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497702771001561Retail</v>
+      </c>
+      <c r="B362" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C362" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D362" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E362" s="23">
+        <v>7702771001561</v>
+      </c>
+      <c r="F362" s="23">
+        <v>873239</v>
+      </c>
+      <c r="G362" s="22">
+        <v>0</v>
+      </c>
+      <c r="H362" s="22" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734493664798066531Retail</v>
+      </c>
+      <c r="B363" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C363" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D363" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E363" s="23">
+        <v>3664798066531</v>
+      </c>
+      <c r="F363" s="23">
+        <v>882451</v>
+      </c>
+      <c r="G363" s="22">
+        <v>0</v>
+      </c>
+      <c r="H363" s="22" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221237Retail</v>
+      </c>
+      <c r="B364" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C364" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D364" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E364" s="23">
+        <v>7703202221237</v>
+      </c>
+      <c r="F364" s="23">
+        <v>782064</v>
+      </c>
+      <c r="G364" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="H364" s="22" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221275Retail</v>
+      </c>
+      <c r="B365" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C365" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D365" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E365" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F365" s="23">
+        <v>782074</v>
+      </c>
+      <c r="G365" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="H365" s="22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735277703202221275Retail</v>
+      </c>
+      <c r="B366" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C366" s="23">
+        <v>100173527</v>
+      </c>
+      <c r="D366" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F366" s="23">
+        <v>939016</v>
+      </c>
+      <c r="G366" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="H366" s="22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221275Retail</v>
+      </c>
+      <c r="B367" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C367" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D367" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F367" s="23">
+        <v>782074</v>
+      </c>
+      <c r="G367" s="22">
+        <v>0</v>
+      </c>
+      <c r="H367" s="22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A368" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001734497703202221275Retail</v>
+      </c>
+      <c r="B368" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="C368" s="23">
+        <v>100173449</v>
+      </c>
+      <c r="D368" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" s="23">
+        <v>7703202221275</v>
+      </c>
+      <c r="F368" s="23">
+        <v>939016</v>
+      </c>
+      <c r="G368" s="22">
+        <v>0</v>
+      </c>
+      <c r="H368" s="22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" s="3" t="str">
+        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
+        <v>1001735103664798066531Retail</v>
+      </c>
+      <c r="B369" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="C369" s="29">
+        <v>100173510</v>
+      </c>
+      <c r="D369" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="29">
+        <v>3664798066531</v>
+      </c>
+      <c r="F369" s="29">
+        <v>882451</v>
+      </c>
+      <c r="G369" s="31">
+        <v>100028578</v>
+      </c>
+      <c r="H369" s="32" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -3977,7 +12095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -4113,7 +12231,7 @@
       <c r="B12" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4124,7 +12242,7 @@
       <c r="B13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4135,7 +12253,7 @@
       <c r="B14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4146,7 +12264,7 @@
       <c r="B15" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4166,7 +12284,7 @@
       <c r="B17" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="15" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4177,7 +12295,7 @@
       <c r="B18" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4188,7 +12306,7 @@
       <c r="B19" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4289,6 +12407,182 @@
       </c>
       <c r="C28" s="13" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4301,7 +12595,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -4437,7 +12731,7 @@
       <c r="B12" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>139</v>
       </c>
     </row>
@@ -4448,7 +12742,7 @@
       <c r="B13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4459,7 +12753,7 @@
       <c r="B14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4470,7 +12764,7 @@
       <c r="B15" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>142</v>
       </c>
     </row>
@@ -4490,7 +12784,7 @@
       <c r="B17" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4501,7 +12795,7 @@
       <c r="B18" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -4512,7 +12806,7 @@
       <c r="B19" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4613,6 +12907,182 @@
       </c>
       <c r="C28" s="13" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4621,4 +13091,11 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ae1773b1-39ae-4dac-b4e5-79a9bafdcb23}" enabled="1" method="Privileged" siteId="{060430f9-1b51-44c6-b474-e4c29481970b}" removed="0"/>
+  <clbl:label id="{d9088468-0951-4aef-9cc3-0a346e475ddc}" enabled="1" method="Privileged" siteId="{aca3c8d6-aa71-4e1a-a10e-03572fc58c0b}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Plantillas/Base Maestra/Maestra.xlsx
+++ b/Plantillas/Base Maestra/Maestra.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E7AA0A-DBA5-4B29-8F64-91AC3AFCF128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D072E3-3F71-49D0-8AA9-6458F801316D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="6240" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="389">
   <si>
     <t>KeyPLU</t>
   </si>
@@ -452,27 +452,9 @@
     <t>Credit card missing</t>
   </si>
   <si>
-    <t>Ajuste por SITH</t>
-  </si>
-  <si>
-    <t>Ajuste por forecast de cliente</t>
-  </si>
-  <si>
     <t>Excedido en limite de cuota</t>
   </si>
   <si>
-    <t>Allocation por Ruptura</t>
-  </si>
-  <si>
-    <t>Out of stock (Back Order not accept)</t>
-  </si>
-  <si>
-    <t>Ruptura</t>
-  </si>
-  <si>
-    <t>Retoma de producto en nueva orden</t>
-  </si>
-  <si>
     <t>ZS</t>
   </si>
   <si>
@@ -581,12 +563,6 @@
     <t>Regulatory Problem</t>
   </si>
   <si>
-    <t xml:space="preserve">Ruptura </t>
-  </si>
-  <si>
-    <t>Error en sistema Opella</t>
-  </si>
-  <si>
     <t>CRUZ VERDE</t>
   </si>
   <si>
@@ -1218,13 +1194,19 @@
   </si>
   <si>
     <t xml:space="preserve">	041069</t>
+  </si>
+  <si>
+    <t>ode</t>
+  </si>
+  <si>
+    <t>Error en sistema</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1262,6 +1244,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1421,7 +1411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1506,6 +1496,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1839,7 +1838,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C283A7A-442C-43A3-984C-CEFD22907B9A}" name="MR_7" displayName="MR_7" ref="A1:C44" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:C44" xr:uid="{6C283A7A-442C-43A3-984C-CEFD22907B9A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E2C9FFF9-ECC7-427D-8735-33E33790C3E9}" name="Code" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{E2C9FFF9-ECC7-427D-8735-33E33790C3E9}" name="ode" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{83957DAE-DC52-4558-9499-0075AFBDD203}" name="Reason (shift)" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{8C5DC287-A9AC-47B8-B209-A750C1A41565}" name="Definition" dataDxfId="0"/>
   </tableColumns>
@@ -4882,7 +4881,7 @@
         <v>1001735097591044008952Retail</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C103" s="3">
         <v>100173509</v>
@@ -4900,7 +4899,7 @@
         <v>119410</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -4909,7 +4908,7 @@
         <v>1001735097591044009010Retail</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C104" s="3">
         <v>100173509</v>
@@ -4927,7 +4926,7 @@
         <v>121499</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -4936,7 +4935,7 @@
         <v>1001735097703202010329Retail</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C105" s="3">
         <v>100173509</v>
@@ -4954,7 +4953,7 @@
         <v>121485</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -4963,7 +4962,7 @@
         <v>1001735097795312100090Retail</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C106" s="3">
         <v>100173509</v>
@@ -4981,7 +4980,7 @@
         <v>121486</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -4990,7 +4989,7 @@
         <v>1001735097703202221220Retail</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C107" s="3">
         <v>100173509</v>
@@ -5008,7 +5007,7 @@
         <v>21427</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -5017,7 +5016,7 @@
         <v>1001735097703202221428Retail</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C108" s="3">
         <v>100173509</v>
@@ -5035,7 +5034,7 @@
         <v>120906</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -5044,7 +5043,7 @@
         <v>1001735097703202221381Retail</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C109" s="3">
         <v>100173509</v>
@@ -5062,7 +5061,7 @@
         <v>120908</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -5071,7 +5070,7 @@
         <v>1001735093664798064728Retail</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C110" s="3">
         <v>100173509</v>
@@ -5089,7 +5088,7 @@
         <v>561351</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -5098,7 +5097,7 @@
         <v>1001735097703202221244Retail</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C111" s="3">
         <v>100173509</v>
@@ -5116,7 +5115,7 @@
         <v>20134</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -5125,7 +5124,7 @@
         <v>1001735097703202221091Retail</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C112" s="3">
         <v>100173509</v>
@@ -5143,7 +5142,7 @@
         <v>20131</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -5152,7 +5151,7 @@
         <v>1001735097703202221305Retail</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C113" s="3">
         <v>100173509</v>
@@ -5170,7 +5169,7 @@
         <v>20164</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -5179,7 +5178,7 @@
         <v>1001735097703202221336Retail</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C114" s="3">
         <v>100173509</v>
@@ -5197,7 +5196,7 @@
         <v>157863</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -5206,7 +5205,7 @@
         <v>1001735097703202221312Retail</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C115" s="3">
         <v>100173509</v>
@@ -5224,7 +5223,7 @@
         <v>20115</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -5233,7 +5232,7 @@
         <v>1001735097703202221329Retail</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C116" s="3">
         <v>100173509</v>
@@ -5251,7 +5250,7 @@
         <v>159030</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -5260,7 +5259,7 @@
         <v>1001735097703202221275Retail</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C117" s="3">
         <v>100173509</v>
@@ -5278,7 +5277,7 @@
         <v>54448</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -5287,7 +5286,7 @@
         <v>1001735097703202221282Retail</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C118" s="3">
         <v>100173509</v>
@@ -5305,7 +5304,7 @@
         <v>66022</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -5314,7 +5313,7 @@
         <v>1001735097703202221169Retail</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C119" s="3">
         <v>100173509</v>
@@ -5332,7 +5331,7 @@
         <v>20258</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -5341,7 +5340,7 @@
         <v>1001735097703202221152Retail</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C120" s="3">
         <v>100173509</v>
@@ -5359,7 +5358,7 @@
         <v>71766</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -5368,7 +5367,7 @@
         <v>1001735097703202221176Retail</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C121" s="3">
         <v>100173509</v>
@@ -5386,7 +5385,7 @@
         <v>63380</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -5395,7 +5394,7 @@
         <v>1001735093664798069211Retail</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C122" s="3">
         <v>100173509</v>
@@ -5413,7 +5412,7 @@
         <v>63380</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -5422,7 +5421,7 @@
         <v>1001735093582910009900Retail</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C123" s="3">
         <v>100173509</v>
@@ -5440,7 +5439,7 @@
         <v>121505</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -5449,7 +5448,7 @@
         <v>1001735097702771001561Retail</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C124" s="3">
         <v>100173509</v>
@@ -5467,7 +5466,7 @@
         <v>129907</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -5476,7 +5475,7 @@
         <v>1001735097501165007956Retail</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C125" s="3">
         <v>100173509</v>
@@ -5494,7 +5493,7 @@
         <v>114460</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -5503,7 +5502,7 @@
         <v>1001735097703202003475Retail</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C126" s="3">
         <v>100173509</v>
@@ -5521,7 +5520,7 @@
         <v>145558</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -5530,7 +5529,7 @@
         <v>1001735097703202221800Retail</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C127" s="3">
         <v>100173509</v>
@@ -5548,7 +5547,7 @@
         <v>97353</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -5557,7 +5556,7 @@
         <v>1001735097591044401036Retail</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C128" s="3">
         <v>100173509</v>
@@ -5575,7 +5574,7 @@
         <v>21450</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -5584,7 +5583,7 @@
         <v>1001735097501165010444Retail</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C129" s="3">
         <v>100173509</v>
@@ -5602,7 +5601,7 @@
         <v>141268</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -5611,7 +5610,7 @@
         <v>1001735097591044009447Retail</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C130" s="3">
         <v>100173509</v>
@@ -5629,7 +5628,7 @@
         <v>21714</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -5638,7 +5637,7 @@
         <v>1001735097591044007191Retail</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C131" s="3">
         <v>100173509</v>
@@ -5656,7 +5655,7 @@
         <v>21716</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -5665,7 +5664,7 @@
         <v>1001735097591044008952Institucional</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C132" s="3">
         <v>100173509</v>
@@ -5683,7 +5682,7 @@
         <v>78565</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -5692,7 +5691,7 @@
         <v>1001735097591044009010Institucional</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C133" s="3">
         <v>100173509</v>
@@ -5710,7 +5709,7 @@
         <v>78566</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -5719,7 +5718,7 @@
         <v>1001735097703202010329Institucional</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C134" s="3">
         <v>100173509</v>
@@ -5737,7 +5736,7 @@
         <v>84742</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -5746,7 +5745,7 @@
         <v>1001735097795312100090Institucional</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C135" s="3">
         <v>100173509</v>
@@ -5764,7 +5763,7 @@
         <v>80460</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -5773,7 +5772,7 @@
         <v>1001735097703202221428Institucional</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C136" s="3">
         <v>100173509</v>
@@ -5791,7 +5790,7 @@
         <v>144732</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -5800,7 +5799,7 @@
         <v>1001735097703202221381Institucional</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C137" s="3">
         <v>100173509</v>
@@ -5818,7 +5817,7 @@
         <v>144638</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -5827,7 +5826,7 @@
         <v>1001735097703202221244Institucional</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C138" s="3">
         <v>100173509</v>
@@ -5845,7 +5844,7 @@
         <v>156861</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -5854,7 +5853,7 @@
         <v>1001735097703202221091Institucional</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C139" s="3">
         <v>100173509</v>
@@ -5872,7 +5871,7 @@
         <v>51294</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -5881,7 +5880,7 @@
         <v>1001735097703202221312Institucional</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C140" s="3">
         <v>100173509</v>
@@ -5899,7 +5898,7 @@
         <v>158353</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -5908,7 +5907,7 @@
         <v>1001735097703202221305Institucional</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C141" s="3">
         <v>100173509</v>
@@ -5926,7 +5925,7 @@
         <v>145615</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -5935,7 +5934,7 @@
         <v>1001735097703202221275Institucional</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C142" s="3">
         <v>100173509</v>
@@ -5953,7 +5952,7 @@
         <v>399766</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -5962,7 +5961,7 @@
         <v>1001735097703202221282Institucional</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C143" s="3">
         <v>100173509</v>
@@ -5980,7 +5979,7 @@
         <v>146961</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -5989,7 +5988,7 @@
         <v>1001735097703202221169Institucional</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C144" s="3">
         <v>100173509</v>
@@ -6007,7 +6006,7 @@
         <v>385952</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -6016,7 +6015,7 @@
         <v>1001735097703202221152Institucional</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C145" s="3">
         <v>100173509</v>
@@ -6034,7 +6033,7 @@
         <v>385946</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -6043,7 +6042,7 @@
         <v>1001735097703202221176Institucional</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C146" s="3">
         <v>100173509</v>
@@ -6061,7 +6060,7 @@
         <v>145617</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -6070,7 +6069,7 @@
         <v>1001735093664798069211Institucional</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C147" s="3">
         <v>100173509</v>
@@ -6088,7 +6087,7 @@
         <v>145617</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -6097,7 +6096,7 @@
         <v>1001735093582910009900Institucional</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C148" s="3">
         <v>100173509</v>
@@ -6115,7 +6114,7 @@
         <v>54706</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -6124,7 +6123,7 @@
         <v>1001735097702771001561Institucional</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C149" s="3">
         <v>100173509</v>
@@ -6142,7 +6141,7 @@
         <v>537317</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -6151,7 +6150,7 @@
         <v>1001735097703202221800Institucional</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C150" s="3">
         <v>100173509</v>
@@ -6169,7 +6168,7 @@
         <v>145619</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -6178,7 +6177,7 @@
         <v>1001735097591044401036Institucional</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C151" s="3">
         <v>100173509</v>
@@ -6196,7 +6195,7 @@
         <v>120049</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -6205,7 +6204,7 @@
         <v>1001735097501165010444Institucional</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C152" s="3">
         <v>100173509</v>
@@ -6223,7 +6222,7 @@
         <v>384773</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -6232,7 +6231,7 @@
         <v>1001735097591044009447Institucional</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C153" s="3">
         <v>100173509</v>
@@ -6250,7 +6249,7 @@
         <v>384775</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -6259,7 +6258,7 @@
         <v>1001735097591044007191Institucional</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C154" s="3">
         <v>100173509</v>
@@ -6277,7 +6276,7 @@
         <v>384774</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -6286,7 +6285,7 @@
         <v>1001735077795312100090Retail</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C155" s="3">
         <v>100173507</v>
@@ -6304,7 +6303,7 @@
         <v>1117327</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -6313,7 +6312,7 @@
         <v>1001735077591044008952Retail</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C156" s="3">
         <v>100173507</v>
@@ -6331,7 +6330,7 @@
         <v>1010996</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -6340,7 +6339,7 @@
         <v>1001735077591044009010Retail</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C157" s="3">
         <v>100173507</v>
@@ -6358,7 +6357,7 @@
         <v>1011422</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -6367,7 +6366,7 @@
         <v>1001735077703202010329Retail</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C158" s="3">
         <v>100173507</v>
@@ -6385,7 +6384,7 @@
         <v>1130572</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -6394,7 +6393,7 @@
         <v>1001735077706263600645Retail</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C159" s="3">
         <v>100173507</v>
@@ -6412,7 +6411,7 @@
         <v>100527</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -6421,7 +6420,7 @@
         <v>1001735077706263600621Retail</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C160" s="3">
         <v>100173507</v>
@@ -6439,7 +6438,7 @@
         <v>70328</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -6448,7 +6447,7 @@
         <v>1001735077706263600638Retail</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C161" s="3">
         <v>100173507</v>
@@ -6466,7 +6465,7 @@
         <v>70329</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -6475,7 +6474,7 @@
         <v>1001735077703202221237Retail</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C162" s="3">
         <v>100173507</v>
@@ -6493,7 +6492,7 @@
         <v>1283326</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -6502,7 +6501,7 @@
         <v>1001735077703202221428Retail</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C163" s="3">
         <v>100173507</v>
@@ -6520,7 +6519,7 @@
         <v>1283331</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -6529,7 +6528,7 @@
         <v>1001735077703202221220Retail</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C164" s="3">
         <v>100173507</v>
@@ -6547,7 +6546,7 @@
         <v>1283325</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -6556,7 +6555,7 @@
         <v>1001735077703202221381Retail</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C165" s="3">
         <v>100173507</v>
@@ -6574,7 +6573,7 @@
         <v>1283330</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -6583,7 +6582,7 @@
         <v>1001735077703202121230Retail</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C166" s="3">
         <v>100173507</v>
@@ -6601,7 +6600,7 @@
         <v>72977</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -6610,7 +6609,7 @@
         <v>1001735077703202121223Retail</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C167" s="3">
         <v>100173507</v>
@@ -6628,7 +6627,7 @@
         <v>72978</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -6637,7 +6636,7 @@
         <v>1001735077703202221244Retail</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C168" s="3">
         <v>100173507</v>
@@ -6655,7 +6654,7 @@
         <v>1283327</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -6664,7 +6663,7 @@
         <v>1001735077703202221091Retail</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C169" s="3">
         <v>100173507</v>
@@ -6682,7 +6681,7 @@
         <v>1284312</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -6691,7 +6690,7 @@
         <v>1001735077703202221336Retail</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C170" s="3">
         <v>100173507</v>
@@ -6709,7 +6708,7 @@
         <v>1289613</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -6718,7 +6717,7 @@
         <v>1001735077703202221329Retail</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C171" s="3">
         <v>100173507</v>
@@ -6736,7 +6735,7 @@
         <v>1289612</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -6745,7 +6744,7 @@
         <v>1001735077703202221305Retail</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C172" s="3">
         <v>100173507</v>
@@ -6763,7 +6762,7 @@
         <v>1283329</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -6772,7 +6771,7 @@
         <v>1001735077703202221275Retail</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C173" s="3">
         <v>100173507</v>
@@ -6790,7 +6789,7 @@
         <v>1283328</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -6799,7 +6798,7 @@
         <v>1001735077703202121292Retail</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C174" s="3">
         <v>100173507</v>
@@ -6817,7 +6816,7 @@
         <v>78563</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -6826,7 +6825,7 @@
         <v>1001735077703202221169Retail</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C175" s="3">
         <v>100173507</v>
@@ -6844,7 +6843,7 @@
         <v>1283321</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -6853,7 +6852,7 @@
         <v>1001735077703202221152Retail</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C176" s="3">
         <v>100173507</v>
@@ -6871,7 +6870,7 @@
         <v>1283320</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -6880,7 +6879,7 @@
         <v>1001735077703202221176Retail</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C177" s="3">
         <v>100173507</v>
@@ -6898,7 +6897,7 @@
         <v>1283322</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -6907,7 +6906,7 @@
         <v>1001735077703202121155Retail</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C178" s="3">
         <v>100173507</v>
@@ -6925,7 +6924,7 @@
         <v>78564</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -6934,7 +6933,7 @@
         <v>1001735073582910009900Retail</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C179" s="3">
         <v>100173507</v>
@@ -6952,7 +6951,7 @@
         <v>1203136</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -6961,7 +6960,7 @@
         <v>1001735077702771001561Retail</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C180" s="3">
         <v>100173507</v>
@@ -6979,7 +6978,7 @@
         <v>1245994</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -6988,7 +6987,7 @@
         <v>1001735077706263600072Retail</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C181" s="3">
         <v>100173507</v>
@@ -7006,7 +7005,7 @@
         <v>76061</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -7015,7 +7014,7 @@
         <v>1001735077703202003475Retail</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C182" s="3">
         <v>100173507</v>
@@ -7033,7 +7032,7 @@
         <v>1281624</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -7042,7 +7041,7 @@
         <v>1001735077501165007956Retail</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C183" s="3">
         <v>100173507</v>
@@ -7060,7 +7059,7 @@
         <v>1200431</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -7069,7 +7068,7 @@
         <v>1001735077703202221800Retail</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C184" s="3">
         <v>100173507</v>
@@ -7087,7 +7086,7 @@
         <v>1361156</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -7096,7 +7095,7 @@
         <v>1001735077591044401036Retail</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C185" s="3">
         <v>100173507</v>
@@ -7114,7 +7113,7 @@
         <v>1015474</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -7123,7 +7122,7 @@
         <v>1001735077501165010444Retail</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C186" s="3">
         <v>100173507</v>
@@ -7141,7 +7140,7 @@
         <v>1281081</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -7150,7 +7149,7 @@
         <v>1001735077706263600775Retail</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C187" s="3">
         <v>100173507</v>
@@ -7168,7 +7167,7 @@
         <v>71073</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -7177,7 +7176,7 @@
         <v>1001735087591044008952Retail</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C188" s="3">
         <v>100173508</v>
@@ -7195,7 +7194,7 @@
         <v>35106</v>
       </c>
       <c r="H188" s="25" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -7204,7 +7203,7 @@
         <v>1001735087591044009010Retail</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C189" s="3">
         <v>100173508</v>
@@ -7222,7 +7221,7 @@
         <v>35115</v>
       </c>
       <c r="H189" s="25" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -7231,7 +7230,7 @@
         <v>1001735087703202010329Retail</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C190" s="3">
         <v>100173508</v>
@@ -7249,7 +7248,7 @@
         <v>35116</v>
       </c>
       <c r="H190" s="25" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -7258,7 +7257,7 @@
         <v>1001735087795312100090Retail</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C191" s="3">
         <v>100173508</v>
@@ -7276,7 +7275,7 @@
         <v>35157</v>
       </c>
       <c r="H191" s="25" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -7285,7 +7284,7 @@
         <v>1001735087703202221237Retail</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C192" s="3">
         <v>100173508</v>
@@ -7303,7 +7302,7 @@
         <v>13146</v>
       </c>
       <c r="H192" s="25" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -7312,7 +7311,7 @@
         <v>1001735087703202221428Retail</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C193" s="3">
         <v>100173508</v>
@@ -7330,7 +7329,7 @@
         <v>13271</v>
       </c>
       <c r="H193" s="25" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -7339,7 +7338,7 @@
         <v>1001735087703202221220Retail</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C194" s="3">
         <v>100173508</v>
@@ -7357,7 +7356,7 @@
         <v>13145</v>
       </c>
       <c r="H194" s="25" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -7366,7 +7365,7 @@
         <v>1001735087703202221381Retail</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C195" s="3">
         <v>100173508</v>
@@ -7384,7 +7383,7 @@
         <v>13275</v>
       </c>
       <c r="H195" s="25" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -7393,7 +7392,7 @@
         <v>1001735087703202221244Retail</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C196" s="3">
         <v>100173508</v>
@@ -7411,7 +7410,7 @@
         <v>13014</v>
       </c>
       <c r="H196" s="25" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -7420,7 +7419,7 @@
         <v>1001735087703202221312Retail</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C197" s="3">
         <v>100173508</v>
@@ -7438,7 +7437,7 @@
         <v>13303</v>
       </c>
       <c r="H197" s="25" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -7447,7 +7446,7 @@
         <v>1001735087703202221329Retail</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C198" s="3">
         <v>100173508</v>
@@ -7465,7 +7464,7 @@
         <v>13305</v>
       </c>
       <c r="H198" s="25" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -7474,7 +7473,7 @@
         <v>1001735087703202221305Retail</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C199" s="3">
         <v>100173508</v>
@@ -7492,7 +7491,7 @@
         <v>13051</v>
       </c>
       <c r="H199" s="25" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -7501,7 +7500,7 @@
         <v>1001735087703202221275Retail</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C200" s="3">
         <v>100173508</v>
@@ -7519,7 +7518,7 @@
         <v>13175</v>
       </c>
       <c r="H200" s="25" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -7528,7 +7527,7 @@
         <v>1001735087703202221282Retail</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C201" s="3">
         <v>100173508</v>
@@ -7546,7 +7545,7 @@
         <v>13189</v>
       </c>
       <c r="H201" s="25" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -7555,7 +7554,7 @@
         <v>1001735087703202221091Retail</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C202" s="3">
         <v>100173508</v>
@@ -7573,7 +7572,7 @@
         <v>13013</v>
       </c>
       <c r="H202" s="25" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -7582,7 +7581,7 @@
         <v>1001735087706263200364Retail</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C203" s="3">
         <v>100173508</v>
@@ -7600,7 +7599,7 @@
         <v>42163</v>
       </c>
       <c r="H203" s="25" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -7609,7 +7608,7 @@
         <v>1001735087706263200388Retail</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C204" s="3">
         <v>100173508</v>
@@ -7627,7 +7626,7 @@
         <v>42403</v>
       </c>
       <c r="H204" s="25" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -7636,7 +7635,7 @@
         <v>1001735087703202221169Retail</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C205" s="3">
         <v>100173508</v>
@@ -7654,7 +7653,7 @@
         <v>13081</v>
       </c>
       <c r="H205" s="25" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -7663,7 +7662,7 @@
         <v>1001735087703202221152Retail</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C206" s="3">
         <v>100173508</v>
@@ -7681,7 +7680,7 @@
         <v>13195</v>
       </c>
       <c r="H206" s="25" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -7690,7 +7689,7 @@
         <v>1001735087703202221176Retail</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C207" s="3">
         <v>100173508</v>
@@ -7708,7 +7707,7 @@
         <v>13179</v>
       </c>
       <c r="H207" s="25" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -7717,7 +7716,7 @@
         <v>1001735083582910009900Retail</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C208" s="3">
         <v>100173508</v>
@@ -7735,7 +7734,7 @@
         <v>14063</v>
       </c>
       <c r="H208" s="25" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -7744,7 +7743,7 @@
         <v>1001735087702771001561Retail</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C209" s="3">
         <v>100173508</v>
@@ -7762,7 +7761,7 @@
         <v>14068</v>
       </c>
       <c r="H209" s="25" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -7771,7 +7770,7 @@
         <v>1001735087703202003475Retail</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C210" s="3">
         <v>100173508</v>
@@ -7789,7 +7788,7 @@
         <v>35232</v>
       </c>
       <c r="H210" s="25" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -7798,7 +7797,7 @@
         <v>1001735087501165007956Retail</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C211" s="3">
         <v>100173508</v>
@@ -7816,7 +7815,7 @@
         <v>35214</v>
       </c>
       <c r="H211" s="25" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -7825,7 +7824,7 @@
         <v>1001735087703202221800Retail</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C212" s="3">
         <v>100173508</v>
@@ -7843,7 +7842,7 @@
         <v>276272</v>
       </c>
       <c r="H212" s="25" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -7852,7 +7851,7 @@
         <v>1001735087591044401036Retail</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C213" s="3">
         <v>100173508</v>
@@ -7870,7 +7869,7 @@
         <v>77148</v>
       </c>
       <c r="H213" s="25" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -7879,7 +7878,7 @@
         <v>1001735087501165010444Retail</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C214" s="3">
         <v>100173508</v>
@@ -7897,7 +7896,7 @@
         <v>35230</v>
       </c>
       <c r="H214" s="25" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -7906,7 +7905,7 @@
         <v>1001735087591044009225Retail</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C215" s="3">
         <v>100173508</v>
@@ -7924,7 +7923,7 @@
         <v>35054</v>
       </c>
       <c r="H215" s="25" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -7933,7 +7932,7 @@
         <v>1001735087591044007191Retail</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C216" s="3">
         <v>100173508</v>
@@ -7951,7 +7950,7 @@
         <v>35057</v>
       </c>
       <c r="H216" s="25" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -7960,7 +7959,7 @@
         <v>1001735087591044009447Retail</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C217" s="3">
         <v>100173508</v>
@@ -7978,7 +7977,7 @@
         <v>35056</v>
       </c>
       <c r="H217" s="25" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -7987,7 +7986,7 @@
         <v>1001734677703202221275Retail</v>
       </c>
       <c r="B218" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C218" s="23">
         <v>100173467</v>
@@ -8005,7 +8004,7 @@
         <v>7629</v>
       </c>
       <c r="H218" s="22" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -8446,7 +8445,7 @@
         <v>1001734677703202221275Retail</v>
       </c>
       <c r="B235" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C235" s="23">
         <v>100173467</v>
@@ -8464,7 +8463,7 @@
         <v>7629</v>
       </c>
       <c r="H235" s="22" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
@@ -8797,7 +8796,7 @@
         <v>1001735107703202221275Retail</v>
       </c>
       <c r="B248" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C248" s="23">
         <v>100173510</v>
@@ -8815,7 +8814,7 @@
         <v>100011666</v>
       </c>
       <c r="H248" s="22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
@@ -8824,7 +8823,7 @@
         <v>1001735107591044008952Retail</v>
       </c>
       <c r="B249" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C249" s="23">
         <v>100173510</v>
@@ -8842,7 +8841,7 @@
         <v>100000317</v>
       </c>
       <c r="H249" s="22" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
@@ -8851,7 +8850,7 @@
         <v>1001735107591044009010Retail</v>
       </c>
       <c r="B250" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C250" s="23">
         <v>100173510</v>
@@ -8869,7 +8868,7 @@
         <v>100000318</v>
       </c>
       <c r="H250" s="22" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
@@ -8878,7 +8877,7 @@
         <v>1001735107591044401036Retail</v>
       </c>
       <c r="B251" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C251" s="23">
         <v>100173510</v>
@@ -8896,7 +8895,7 @@
         <v>100000367</v>
       </c>
       <c r="H251" s="22" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
@@ -8905,7 +8904,7 @@
         <v>1001735107591044007191Retail</v>
       </c>
       <c r="B252" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C252" s="23">
         <v>100173510</v>
@@ -8923,7 +8922,7 @@
         <v>100000376</v>
       </c>
       <c r="H252" s="22" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
@@ -8932,7 +8931,7 @@
         <v>1001735107703202221237Retail</v>
       </c>
       <c r="B253" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C253" s="23">
         <v>100173510</v>
@@ -8950,7 +8949,7 @@
         <v>100000914</v>
       </c>
       <c r="H253" s="22" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
@@ -8959,7 +8958,7 @@
         <v>1001735107703202221220Retail</v>
       </c>
       <c r="B254" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C254" s="23">
         <v>100173510</v>
@@ -8977,7 +8976,7 @@
         <v>100000916</v>
       </c>
       <c r="H254" s="22" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
@@ -8986,7 +8985,7 @@
         <v>1001735107703202221091Retail</v>
       </c>
       <c r="B255" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C255" s="23">
         <v>100173510</v>
@@ -9004,7 +9003,7 @@
         <v>100000918</v>
       </c>
       <c r="H255" s="22" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
@@ -9013,7 +9012,7 @@
         <v>1001735107703202221305Retail</v>
       </c>
       <c r="B256" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C256" s="23">
         <v>100173510</v>
@@ -9031,7 +9030,7 @@
         <v>100000924</v>
       </c>
       <c r="H256" s="22" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
@@ -9040,7 +9039,7 @@
         <v>1001735107703202221244Retail</v>
       </c>
       <c r="B257" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C257" s="23">
         <v>100173510</v>
@@ -9058,7 +9057,7 @@
         <v>100007750</v>
       </c>
       <c r="H257" s="22" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
@@ -9067,7 +9066,7 @@
         <v>1001735107703202221169Retail</v>
       </c>
       <c r="B258" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C258" s="23">
         <v>100173510</v>
@@ -9085,7 +9084,7 @@
         <v>100007751</v>
       </c>
       <c r="H258" s="22" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
@@ -9094,7 +9093,7 @@
         <v>1001735103582910009900Retail</v>
       </c>
       <c r="B259" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C259" s="23">
         <v>100173510</v>
@@ -9112,7 +9111,7 @@
         <v>100011580</v>
       </c>
       <c r="H259" s="22" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
@@ -9121,7 +9120,7 @@
         <v>1001735107703202221275Retail</v>
       </c>
       <c r="B260" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C260" s="23">
         <v>100173510</v>
@@ -9139,7 +9138,7 @@
         <v>100011666</v>
       </c>
       <c r="H260" s="22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
@@ -9148,7 +9147,7 @@
         <v>1001735107703381002146Retail</v>
       </c>
       <c r="B261" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C261" s="23">
         <v>100173510</v>
@@ -9166,7 +9165,7 @@
         <v>100012451</v>
       </c>
       <c r="H261" s="22" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
@@ -9175,7 +9174,7 @@
         <v>1001735107703202221282Retail</v>
       </c>
       <c r="B262" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C262" s="23">
         <v>100173510</v>
@@ -9193,7 +9192,7 @@
         <v>100013901</v>
       </c>
       <c r="H262" s="22" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
@@ -9202,7 +9201,7 @@
         <v>1001735107703202221152Retail</v>
       </c>
       <c r="B263" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C263" s="23">
         <v>100173510</v>
@@ -9220,7 +9219,7 @@
         <v>100014078</v>
       </c>
       <c r="H263" s="22" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
@@ -9229,7 +9228,7 @@
         <v>1001735107795312100090Retail</v>
       </c>
       <c r="B264" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C264" s="23">
         <v>100173510</v>
@@ -9247,7 +9246,7 @@
         <v>100015676</v>
       </c>
       <c r="H264" s="22" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
@@ -9256,7 +9255,7 @@
         <v>1001735107703202010329Retail</v>
       </c>
       <c r="B265" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C265" s="23">
         <v>100173510</v>
@@ -9274,7 +9273,7 @@
         <v>100016576</v>
       </c>
       <c r="H265" s="22" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
@@ -9283,7 +9282,7 @@
         <v>1001735107501165007956Retail</v>
       </c>
       <c r="B266" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C266" s="23">
         <v>100173510</v>
@@ -9301,7 +9300,7 @@
         <v>100020434</v>
       </c>
       <c r="H266" s="22" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
@@ -9310,7 +9309,7 @@
         <v>1001735107703202221428Retail</v>
       </c>
       <c r="B267" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C267" s="23">
         <v>100173510</v>
@@ -9328,7 +9327,7 @@
         <v>100021503</v>
       </c>
       <c r="H267" s="22" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
@@ -9337,7 +9336,7 @@
         <v>1001735107703202221381Retail</v>
       </c>
       <c r="B268" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C268" s="23">
         <v>100173510</v>
@@ -9355,7 +9354,7 @@
         <v>100021565</v>
       </c>
       <c r="H268" s="22" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
@@ -9364,7 +9363,7 @@
         <v>1001735107702771001561Retail</v>
       </c>
       <c r="B269" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C269" s="23">
         <v>100173510</v>
@@ -9382,7 +9381,7 @@
         <v>100022711</v>
       </c>
       <c r="H269" s="22" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
@@ -9391,7 +9390,7 @@
         <v>1001735107501165010444Retail</v>
       </c>
       <c r="B270" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C270" s="23">
         <v>100173510</v>
@@ -9409,7 +9408,7 @@
         <v>100024193</v>
       </c>
       <c r="H270" s="22" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -9418,7 +9417,7 @@
         <v>1001735107703202221312Retail</v>
       </c>
       <c r="B271" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C271" s="23">
         <v>100173510</v>
@@ -9436,7 +9435,7 @@
         <v>100024939</v>
       </c>
       <c r="H271" s="22" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
@@ -9445,7 +9444,7 @@
         <v>1001735107703202221329Retail</v>
       </c>
       <c r="B272" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C272" s="23">
         <v>100173510</v>
@@ -9463,7 +9462,7 @@
         <v>100024940</v>
       </c>
       <c r="H272" s="22" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
@@ -9472,7 +9471,7 @@
         <v>1001735107703202221336Retail</v>
       </c>
       <c r="B273" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C273" s="23">
         <v>100173510</v>
@@ -9490,7 +9489,7 @@
         <v>100024941</v>
       </c>
       <c r="H273" s="22" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
@@ -9499,7 +9498,7 @@
         <v>1001735107703202003475Retail</v>
       </c>
       <c r="B274" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C274" s="23">
         <v>100173510</v>
@@ -9517,7 +9516,7 @@
         <v>100024967</v>
       </c>
       <c r="H274" s="22" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
@@ -9526,7 +9525,7 @@
         <v>1001735103664798067910Retail</v>
       </c>
       <c r="B275" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C275" s="23">
         <v>100173510</v>
@@ -9544,7 +9543,7 @@
         <v>100028083</v>
       </c>
       <c r="H275" s="22" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
@@ -9553,7 +9552,7 @@
         <v>1001735103664798064728Retail</v>
       </c>
       <c r="B276" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C276" s="23">
         <v>100173510</v>
@@ -9571,7 +9570,7 @@
         <v>100028123</v>
       </c>
       <c r="H276" s="22" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
@@ -9580,7 +9579,7 @@
         <v>1001735107591044009447Retail</v>
       </c>
       <c r="B277" s="23" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C277" s="23">
         <v>100173510</v>
@@ -9598,7 +9597,7 @@
         <v>100000375</v>
       </c>
       <c r="H277" s="22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
@@ -9607,7 +9606,7 @@
         <v>1001735277703202221220Retail</v>
       </c>
       <c r="B278" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C278" s="23">
         <v>100173527</v>
@@ -9622,10 +9621,10 @@
         <v>781955</v>
       </c>
       <c r="G278" s="22" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="H278" s="22" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
@@ -9634,7 +9633,7 @@
         <v>1001735277703202221428Retail</v>
       </c>
       <c r="B279" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C279" s="23">
         <v>100173527</v>
@@ -9649,10 +9648,10 @@
         <v>782090</v>
       </c>
       <c r="G279" s="22" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="H279" s="22" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
@@ -9661,7 +9660,7 @@
         <v>1001735277703202221381Retail</v>
       </c>
       <c r="B280" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C280" s="23">
         <v>100173527</v>
@@ -9676,10 +9675,10 @@
         <v>782089</v>
       </c>
       <c r="G280" s="22" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="H280" s="22" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
@@ -9688,7 +9687,7 @@
         <v>1001735277703202221305Retail</v>
       </c>
       <c r="B281" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C281" s="23">
         <v>100173527</v>
@@ -9703,10 +9702,10 @@
         <v>782086</v>
       </c>
       <c r="G281" s="22" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="H281" s="22" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
@@ -9715,7 +9714,7 @@
         <v>1001735277703202221336Retail</v>
       </c>
       <c r="B282" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C282" s="23">
         <v>100173527</v>
@@ -9730,10 +9729,10 @@
         <v>782093</v>
       </c>
       <c r="G282" s="22" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H282" s="22" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
@@ -9742,7 +9741,7 @@
         <v>1001735277703202221329Retail</v>
       </c>
       <c r="B283" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C283" s="23">
         <v>100173527</v>
@@ -9757,10 +9756,10 @@
         <v>782092</v>
       </c>
       <c r="G283" s="22" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="H283" s="22" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
@@ -9769,7 +9768,7 @@
         <v>1001735277703202221312Retail</v>
       </c>
       <c r="B284" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C284" s="23">
         <v>100173527</v>
@@ -9784,10 +9783,10 @@
         <v>782091</v>
       </c>
       <c r="G284" s="22" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H284" s="22" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
@@ -9823,7 +9822,7 @@
         <v>1001735277703202221282Retail</v>
       </c>
       <c r="B286" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C286" s="23">
         <v>100173527</v>
@@ -9838,10 +9837,10 @@
         <v>782085</v>
       </c>
       <c r="G286" s="22" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H286" s="22" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
@@ -9850,7 +9849,7 @@
         <v>1001735277703202221244Retail</v>
       </c>
       <c r="B287" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C287" s="23">
         <v>100173527</v>
@@ -9865,10 +9864,10 @@
         <v>782065</v>
       </c>
       <c r="G287" s="22" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="H287" s="22" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
@@ -9877,7 +9876,7 @@
         <v>1001735277703202221169Retail</v>
       </c>
       <c r="B288" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C288" s="23">
         <v>100173527</v>
@@ -9892,10 +9891,10 @@
         <v>715503</v>
       </c>
       <c r="G288" s="22" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="H288" s="22" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
@@ -9904,7 +9903,7 @@
         <v>1001735277703202221152Retail</v>
       </c>
       <c r="B289" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C289" s="23">
         <v>100173527</v>
@@ -9919,10 +9918,10 @@
         <v>715506</v>
       </c>
       <c r="G289" s="22" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="H289" s="22" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
@@ -9931,7 +9930,7 @@
         <v>1001735273664798069211Retail</v>
       </c>
       <c r="B290" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C290" s="23">
         <v>100173527</v>
@@ -9946,10 +9945,10 @@
         <v>715717</v>
       </c>
       <c r="G290" s="22" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="H290" s="22" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
@@ -9958,7 +9957,7 @@
         <v>1001735273664798064728Retail</v>
       </c>
       <c r="B291" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C291" s="23">
         <v>100173527</v>
@@ -9973,10 +9972,10 @@
         <v>846778</v>
       </c>
       <c r="G291" s="22" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H291" s="22" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
@@ -9985,7 +9984,7 @@
         <v>1001735273664798066531Retail</v>
       </c>
       <c r="B292" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C292" s="23">
         <v>100173527</v>
@@ -10000,10 +9999,10 @@
         <v>882451</v>
       </c>
       <c r="G292" s="22" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="H292" s="22" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
@@ -10012,7 +10011,7 @@
         <v>1001735277703202010329Retail</v>
       </c>
       <c r="B293" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C293" s="23">
         <v>100173527</v>
@@ -10027,10 +10026,10 @@
         <v>341667</v>
       </c>
       <c r="G293" s="22" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="H293" s="22" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
@@ -10039,7 +10038,7 @@
         <v>1001735277591044009010Retail</v>
       </c>
       <c r="B294" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C294" s="23">
         <v>100173527</v>
@@ -10054,10 +10053,10 @@
         <v>732308</v>
       </c>
       <c r="G294" s="22" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="H294" s="22" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
@@ -10066,7 +10065,7 @@
         <v>1001735277591044008952Retail</v>
       </c>
       <c r="B295" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C295" s="23">
         <v>100173527</v>
@@ -10081,10 +10080,10 @@
         <v>666269</v>
       </c>
       <c r="G295" s="22" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="H295" s="22" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
@@ -10093,7 +10092,7 @@
         <v>1001735277795312100090Retail</v>
       </c>
       <c r="B296" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C296" s="23">
         <v>100173527</v>
@@ -10108,10 +10107,10 @@
         <v>785678</v>
       </c>
       <c r="G296" s="22" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="H296" s="22" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
@@ -10120,7 +10119,7 @@
         <v>1001735277591044009447Retail</v>
       </c>
       <c r="B297" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C297" s="23">
         <v>100173527</v>
@@ -10135,10 +10134,10 @@
         <v>120777</v>
       </c>
       <c r="G297" s="22" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="H297" s="22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
@@ -10147,7 +10146,7 @@
         <v>1001735277591044007191Retail</v>
       </c>
       <c r="B298" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C298" s="23">
         <v>100173527</v>
@@ -10162,10 +10161,10 @@
         <v>120786</v>
       </c>
       <c r="G298" s="22" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="H298" s="22" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
@@ -10174,7 +10173,7 @@
         <v>1001735273582910009900Retail</v>
       </c>
       <c r="B299" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C299" s="23">
         <v>100173527</v>
@@ -10189,10 +10188,10 @@
         <v>873229</v>
       </c>
       <c r="G299" s="22" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H299" s="22" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
@@ -10201,7 +10200,7 @@
         <v>1001735277501165007956Retail</v>
       </c>
       <c r="B300" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C300" s="23">
         <v>100173527</v>
@@ -10216,10 +10215,10 @@
         <v>655678</v>
       </c>
       <c r="G300" s="22" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="H300" s="22" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
@@ -10228,7 +10227,7 @@
         <v>1001735277591044401036Retail</v>
       </c>
       <c r="B301" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C301" s="23">
         <v>100173527</v>
@@ -10243,10 +10242,10 @@
         <v>723871</v>
       </c>
       <c r="G301" s="22" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="H301" s="22" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
@@ -10255,7 +10254,7 @@
         <v>1001735277501165010444Retail</v>
       </c>
       <c r="B302" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C302" s="23">
         <v>100173527</v>
@@ -10270,10 +10269,10 @@
         <v>600723</v>
       </c>
       <c r="G302" s="22" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="H302" s="22" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
@@ -10282,7 +10281,7 @@
         <v>1001735277703202221091Retail</v>
       </c>
       <c r="B303" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C303" s="23">
         <v>100173527</v>
@@ -10297,10 +10296,10 @@
         <v>797130</v>
       </c>
       <c r="G303" s="22" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="H303" s="22" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
@@ -10309,7 +10308,7 @@
         <v>1001735277702771001561Retail</v>
       </c>
       <c r="B304" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C304" s="23">
         <v>100173527</v>
@@ -10324,10 +10323,10 @@
         <v>873239</v>
       </c>
       <c r="G304" s="22" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="H304" s="22" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
@@ -10336,7 +10335,7 @@
         <v>1001735277703202003475Retail</v>
       </c>
       <c r="B305" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C305" s="23">
         <v>100173527</v>
@@ -10351,10 +10350,10 @@
         <v>650554</v>
       </c>
       <c r="G305" s="22" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="H305" s="22" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
@@ -10363,7 +10362,7 @@
         <v>1001735277703202221107Retail</v>
       </c>
       <c r="B306" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C306" s="23">
         <v>100173527</v>
@@ -10381,7 +10380,7 @@
         <v>253026</v>
       </c>
       <c r="H306" s="22" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
@@ -10390,7 +10389,7 @@
         <v>1001734677591044008952Retail</v>
       </c>
       <c r="B307" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C307" s="23">
         <v>100173467</v>
@@ -10408,7 +10407,7 @@
         <v>7608</v>
       </c>
       <c r="H307" s="22" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
@@ -10417,7 +10416,7 @@
         <v>1001734673664798066531Retail</v>
       </c>
       <c r="B308" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C308" s="23">
         <v>100173467</v>
@@ -10435,7 +10434,7 @@
         <v>0</v>
       </c>
       <c r="H308" s="22" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
@@ -10444,7 +10443,7 @@
         <v>1001734677591044009010Retail</v>
       </c>
       <c r="B309" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C309" s="23">
         <v>100173467</v>
@@ -10462,7 +10461,7 @@
         <v>7606</v>
       </c>
       <c r="H309" s="22" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
@@ -10471,7 +10470,7 @@
         <v>1001734677703202010329Retail</v>
       </c>
       <c r="B310" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C310" s="23">
         <v>100173467</v>
@@ -10489,7 +10488,7 @@
         <v>7598</v>
       </c>
       <c r="H310" s="22" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
@@ -10498,7 +10497,7 @@
         <v>1001734677795312100090Retail</v>
       </c>
       <c r="B311" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C311" s="23">
         <v>100173467</v>
@@ -10516,7 +10515,7 @@
         <v>7607</v>
       </c>
       <c r="H311" s="22" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
@@ -10525,7 +10524,7 @@
         <v>1001734677703202221428Retail</v>
       </c>
       <c r="B312" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C312" s="23">
         <v>100173467</v>
@@ -10543,7 +10542,7 @@
         <v>7609</v>
       </c>
       <c r="H312" s="22" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
@@ -10552,7 +10551,7 @@
         <v>1001734677703202221220Retail</v>
       </c>
       <c r="B313" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C313" s="23">
         <v>100173467</v>
@@ -10570,7 +10569,7 @@
         <v>7600</v>
       </c>
       <c r="H313" s="22" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
@@ -10579,7 +10578,7 @@
         <v>1001734677703202221381Retail</v>
       </c>
       <c r="B314" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C314" s="23">
         <v>100173467</v>
@@ -10597,7 +10596,7 @@
         <v>7599</v>
       </c>
       <c r="H314" s="22" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
@@ -10606,7 +10605,7 @@
         <v>1001734673664798064728Retail</v>
       </c>
       <c r="B315" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C315" s="23">
         <v>100173467</v>
@@ -10624,7 +10623,7 @@
         <v>436076</v>
       </c>
       <c r="H315" s="22" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
@@ -10633,7 +10632,7 @@
         <v>1001734677703202221244Retail</v>
       </c>
       <c r="B316" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C316" s="23">
         <v>100173467</v>
@@ -10651,7 +10650,7 @@
         <v>7588</v>
       </c>
       <c r="H316" s="22" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
@@ -10660,7 +10659,7 @@
         <v>1001734677703202221336Retail</v>
       </c>
       <c r="B317" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C317" s="23">
         <v>100173467</v>
@@ -10678,7 +10677,7 @@
         <v>7637</v>
       </c>
       <c r="H317" s="22" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
@@ -10687,7 +10686,7 @@
         <v>1001734677703202221312Retail</v>
       </c>
       <c r="B318" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C318" s="23">
         <v>100173467</v>
@@ -10705,7 +10704,7 @@
         <v>7636</v>
       </c>
       <c r="H318" s="22" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
@@ -10714,7 +10713,7 @@
         <v>1001734677703202221329Retail</v>
       </c>
       <c r="B319" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C319" s="23">
         <v>100173467</v>
@@ -10732,7 +10731,7 @@
         <v>7612</v>
       </c>
       <c r="H319" s="22" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
@@ -10741,7 +10740,7 @@
         <v>1001734677703202221343Retail</v>
       </c>
       <c r="B320" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C320" s="23">
         <v>100173467</v>
@@ -10759,7 +10758,7 @@
         <v>21971</v>
       </c>
       <c r="H320" s="22" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
@@ -10768,7 +10767,7 @@
         <v>1001734677703202221305Retail</v>
       </c>
       <c r="B321" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C321" s="23">
         <v>100173467</v>
@@ -10786,7 +10785,7 @@
         <v>7584</v>
       </c>
       <c r="H321" s="22" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
@@ -10795,7 +10794,7 @@
         <v>1001734677703202221268Retail</v>
       </c>
       <c r="B322" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C322" s="23">
         <v>100173467</v>
@@ -10813,7 +10812,7 @@
         <v>7628</v>
       </c>
       <c r="H322" s="22" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
@@ -10822,7 +10821,7 @@
         <v>1001734677703202221282Retail</v>
       </c>
       <c r="B323" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C323" s="23">
         <v>100173467</v>
@@ -10840,7 +10839,7 @@
         <v>7630</v>
       </c>
       <c r="H323" s="22" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
@@ -10849,7 +10848,7 @@
         <v>1001734677703202221091Retail</v>
       </c>
       <c r="B324" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C324" s="23">
         <v>100173467</v>
@@ -10867,7 +10866,7 @@
         <v>7587</v>
       </c>
       <c r="H324" s="22" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
@@ -10876,7 +10875,7 @@
         <v>1001734677703202221169Retail</v>
       </c>
       <c r="B325" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C325" s="23">
         <v>100173467</v>
@@ -10894,7 +10893,7 @@
         <v>7590</v>
       </c>
       <c r="H325" s="22" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
@@ -10903,7 +10902,7 @@
         <v>1001734677703202221152Retail</v>
       </c>
       <c r="B326" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C326" s="23">
         <v>100173467</v>
@@ -10921,7 +10920,7 @@
         <v>7589</v>
       </c>
       <c r="H326" s="22" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
@@ -10930,7 +10929,7 @@
         <v>1001734677703202221176Retail</v>
       </c>
       <c r="B327" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C327" s="23">
         <v>100173467</v>
@@ -10948,7 +10947,7 @@
         <v>7586</v>
       </c>
       <c r="H327" s="22" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
@@ -10957,7 +10956,7 @@
         <v>1001734673582910009900Retail</v>
       </c>
       <c r="B328" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C328" s="23">
         <v>100173467</v>
@@ -10975,7 +10974,7 @@
         <v>7620</v>
       </c>
       <c r="H328" s="22" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
@@ -10984,7 +10983,7 @@
         <v>1001734677702771001561Retail</v>
       </c>
       <c r="B329" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C329" s="23">
         <v>100173467</v>
@@ -11002,7 +11001,7 @@
         <v>7619</v>
       </c>
       <c r="H329" s="22" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
@@ -11011,7 +11010,7 @@
         <v>1001734677703202003475Retail</v>
       </c>
       <c r="B330" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C330" s="23">
         <v>100173467</v>
@@ -11029,7 +11028,7 @@
         <v>7635</v>
       </c>
       <c r="H330" s="22" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
@@ -11038,7 +11037,7 @@
         <v>1001734677501165007956Retail</v>
       </c>
       <c r="B331" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C331" s="23">
         <v>100173467</v>
@@ -11056,7 +11055,7 @@
         <v>7634</v>
       </c>
       <c r="H331" s="22" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
@@ -11065,7 +11064,7 @@
         <v>1001734677591044401036Retail</v>
       </c>
       <c r="B332" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C332" s="23">
         <v>100173467</v>
@@ -11083,7 +11082,7 @@
         <v>7591</v>
       </c>
       <c r="H332" s="22" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
@@ -11092,7 +11091,7 @@
         <v>1001734677591044009447Retail</v>
       </c>
       <c r="B333" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C333" s="23">
         <v>100173467</v>
@@ -11110,7 +11109,7 @@
         <v>7596</v>
       </c>
       <c r="H333" s="22" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
@@ -11119,7 +11118,7 @@
         <v>1001734677591044007191Retail</v>
       </c>
       <c r="B334" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C334" s="23">
         <v>100173467</v>
@@ -11137,7 +11136,7 @@
         <v>13921</v>
       </c>
       <c r="H334" s="22" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
@@ -11146,7 +11145,7 @@
         <v>1001734677501165010444Retail</v>
       </c>
       <c r="B335" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C335" s="23">
         <v>100173467</v>
@@ -11164,7 +11163,7 @@
         <v>7594</v>
       </c>
       <c r="H335" s="22" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
@@ -11173,7 +11172,7 @@
         <v>1001734677703202221107Retail</v>
       </c>
       <c r="B336" s="23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C336" s="23">
         <v>100173467</v>
@@ -11191,7 +11190,7 @@
         <v>7617</v>
       </c>
       <c r="H336" s="22" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
@@ -11200,7 +11199,7 @@
         <v>1001734497591044009447Retail</v>
       </c>
       <c r="B337" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C337" s="23">
         <v>100173449</v>
@@ -11218,7 +11217,7 @@
         <v>0</v>
       </c>
       <c r="H337" s="22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
@@ -11227,7 +11226,7 @@
         <v>1001734497591044007191Retail</v>
       </c>
       <c r="B338" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C338" s="23">
         <v>100173449</v>
@@ -11245,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="H338" s="22" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
@@ -11254,7 +11253,7 @@
         <v>1001734497703202010329Retail</v>
       </c>
       <c r="B339" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C339" s="23">
         <v>100173449</v>
@@ -11272,7 +11271,7 @@
         <v>0</v>
       </c>
       <c r="H339" s="22" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
@@ -11281,7 +11280,7 @@
         <v>1001734497701165010444Retail</v>
       </c>
       <c r="B340" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C340" s="23">
         <v>100173449</v>
@@ -11299,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="H340" s="22" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
@@ -11308,7 +11307,7 @@
         <v>1001734497703202003475Retail</v>
       </c>
       <c r="B341" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C341" s="23">
         <v>100173449</v>
@@ -11326,7 +11325,7 @@
         <v>0</v>
       </c>
       <c r="H341" s="22" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
@@ -11335,7 +11334,7 @@
         <v>1001734497501165007956Retail</v>
       </c>
       <c r="B342" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C342" s="23">
         <v>100173449</v>
@@ -11353,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="H342" s="22" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
@@ -11362,7 +11361,7 @@
         <v>1001734497591044008952Retail</v>
       </c>
       <c r="B343" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C343" s="23">
         <v>100173449</v>
@@ -11380,7 +11379,7 @@
         <v>0</v>
       </c>
       <c r="H343" s="22" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
@@ -11389,7 +11388,7 @@
         <v>1001734497703202221169Retail</v>
       </c>
       <c r="B344" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C344" s="23">
         <v>100173449</v>
@@ -11407,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="H344" s="22" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
@@ -11416,7 +11415,7 @@
         <v>1001734497703202221152Retail</v>
       </c>
       <c r="B345" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C345" s="23">
         <v>100173449</v>
@@ -11434,7 +11433,7 @@
         <v>0</v>
       </c>
       <c r="H345" s="22" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
@@ -11443,7 +11442,7 @@
         <v>1001734497703381002146Retail</v>
       </c>
       <c r="B346" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C346" s="23">
         <v>100173449</v>
@@ -11461,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="H346" s="22" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
@@ -11470,7 +11469,7 @@
         <v>1001734497591044401036Retail</v>
       </c>
       <c r="B347" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C347" s="23">
         <v>100173449</v>
@@ -11488,7 +11487,7 @@
         <v>0</v>
       </c>
       <c r="H347" s="22" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
@@ -11497,7 +11496,7 @@
         <v>1001734497591044009010Retail</v>
       </c>
       <c r="B348" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C348" s="23">
         <v>100173449</v>
@@ -11515,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="H348" s="22" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
@@ -11524,7 +11523,7 @@
         <v>1001734497703202221220Retail</v>
       </c>
       <c r="B349" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C349" s="23">
         <v>100173449</v>
@@ -11542,7 +11541,7 @@
         <v>0</v>
       </c>
       <c r="H349" s="22" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
@@ -11551,7 +11550,7 @@
         <v>1001734497703202221244Retail</v>
       </c>
       <c r="B350" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C350" s="23">
         <v>100173449</v>
@@ -11569,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="H350" s="22" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
@@ -11578,7 +11577,7 @@
         <v>1001734497703202221282Retail</v>
       </c>
       <c r="B351" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C351" s="23">
         <v>100173449</v>
@@ -11596,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="H351" s="22" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
@@ -11605,7 +11604,7 @@
         <v>1001734497703202221305Retail</v>
       </c>
       <c r="B352" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C352" s="23">
         <v>100173449</v>
@@ -11623,7 +11622,7 @@
         <v>0</v>
       </c>
       <c r="H352" s="22" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
@@ -11632,7 +11631,7 @@
         <v>1001734497703202221381Retail</v>
       </c>
       <c r="B353" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C353" s="23">
         <v>100173449</v>
@@ -11650,7 +11649,7 @@
         <v>0</v>
       </c>
       <c r="H353" s="22" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
@@ -11659,7 +11658,7 @@
         <v>1001734497703202221428Retail</v>
       </c>
       <c r="B354" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C354" s="23">
         <v>100173449</v>
@@ -11677,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="H354" s="22" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
@@ -11686,7 +11685,7 @@
         <v>1001734497703202221312Retail</v>
       </c>
       <c r="B355" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C355" s="23">
         <v>100173449</v>
@@ -11704,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="H355" s="22" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
@@ -11713,7 +11712,7 @@
         <v>1001734497703202221329Retail</v>
       </c>
       <c r="B356" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C356" s="23">
         <v>100173449</v>
@@ -11731,7 +11730,7 @@
         <v>0</v>
       </c>
       <c r="H356" s="22" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
@@ -11740,7 +11739,7 @@
         <v>1001734497703202221336Retail</v>
       </c>
       <c r="B357" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C357" s="23">
         <v>100173449</v>
@@ -11758,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="H357" s="22" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
@@ -11767,7 +11766,7 @@
         <v>1001734497795312100090Retail</v>
       </c>
       <c r="B358" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C358" s="23">
         <v>100173449</v>
@@ -11785,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="H358" s="22" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
@@ -11794,7 +11793,7 @@
         <v>1001734497703202221091Retail</v>
       </c>
       <c r="B359" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C359" s="23">
         <v>100173449</v>
@@ -11812,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="H359" s="22" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
@@ -11821,7 +11820,7 @@
         <v>1001734493664798064728Retail</v>
       </c>
       <c r="B360" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C360" s="23">
         <v>100173449</v>
@@ -11839,7 +11838,7 @@
         <v>0</v>
       </c>
       <c r="H360" s="22" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
@@ -11848,7 +11847,7 @@
         <v>1001734493582910009900Retail</v>
       </c>
       <c r="B361" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C361" s="23">
         <v>100173449</v>
@@ -11866,7 +11865,7 @@
         <v>0</v>
       </c>
       <c r="H361" s="22" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
@@ -11875,7 +11874,7 @@
         <v>1001734497702771001561Retail</v>
       </c>
       <c r="B362" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C362" s="23">
         <v>100173449</v>
@@ -11893,7 +11892,7 @@
         <v>0</v>
       </c>
       <c r="H362" s="22" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
@@ -11902,7 +11901,7 @@
         <v>1001734493664798066531Retail</v>
       </c>
       <c r="B363" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C363" s="23">
         <v>100173449</v>
@@ -11920,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="H363" s="22" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
@@ -11929,7 +11928,7 @@
         <v>1001735277703202221237Retail</v>
       </c>
       <c r="B364" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C364" s="23">
         <v>100173527</v>
@@ -11944,10 +11943,10 @@
         <v>782064</v>
       </c>
       <c r="G364" s="22" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="H364" s="22" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
@@ -11956,7 +11955,7 @@
         <v>1001735277703202221275Retail</v>
       </c>
       <c r="B365" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C365" s="23">
         <v>100173527</v>
@@ -11971,10 +11970,10 @@
         <v>782074</v>
       </c>
       <c r="G365" s="22" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="H365" s="22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
@@ -11983,7 +11982,7 @@
         <v>1001735277703202221275Retail</v>
       </c>
       <c r="B366" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C366" s="23">
         <v>100173527</v>
@@ -11998,10 +11997,10 @@
         <v>939016</v>
       </c>
       <c r="G366" s="22" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="H366" s="22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
@@ -12010,7 +12009,7 @@
         <v>1001734497703202221275Retail</v>
       </c>
       <c r="B367" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C367" s="23">
         <v>100173449</v>
@@ -12028,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="H367" s="22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="368" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12037,7 +12036,7 @@
         <v>1001734497703202221275Retail</v>
       </c>
       <c r="B368" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C368" s="23">
         <v>100173449</v>
@@ -12055,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="H368" s="22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
@@ -12064,7 +12063,7 @@
         <v>1001735103664798066531Retail</v>
       </c>
       <c r="B369" s="28" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C369" s="29">
         <v>100173510</v>
@@ -12082,7 +12081,7 @@
         <v>100028578</v>
       </c>
       <c r="H369" s="32" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -12254,7 +12253,7 @@
         <v>104</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -12411,21 +12410,21 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>100</v>
@@ -12433,10 +12432,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>100</v>
@@ -12444,10 +12443,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>100</v>
@@ -12455,10 +12454,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>100</v>
@@ -12466,10 +12465,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>100</v>
@@ -12477,10 +12476,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>100</v>
@@ -12488,43 +12487,43 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>100</v>
@@ -12532,10 +12531,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>100</v>
@@ -12543,10 +12542,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>100</v>
@@ -12554,10 +12553,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>100</v>
@@ -12565,10 +12564,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>100</v>
@@ -12576,10 +12575,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>100</v>
@@ -12604,486 +12603,428 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="33" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="35">
         <v>10</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="34" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="34" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="34" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="34" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="34" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="34" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="34" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="34" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="34" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>139</v>
+      <c r="C12" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="35" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="B19" s="34" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="C19" s="34" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="13" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="B20" s="34" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="C20" s="34" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="14" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="35" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>119</v>
+      <c r="B21" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>122</v>
+      <c r="A22" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>125</v>
+      <c r="A23" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>128</v>
+      <c r="A24" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>131</v>
+      <c r="A25" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>134</v>
+      <c r="A26" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>128</v>
+      <c r="A27" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>77</v>
+      <c r="A28" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>182</v>
+      <c r="A29" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>144</v>
+      <c r="A30" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>144</v>
+      <c r="A31" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>144</v>
+      <c r="A32" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>144</v>
+      <c r="A33" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>144</v>
+      <c r="A34" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>163</v>
-      </c>
+      <c r="A35" s="18"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>166</v>
-      </c>
+      <c r="A36" s="18"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>183</v>
-      </c>
+      <c r="A37" s="18"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>144</v>
-      </c>
+      <c r="A38" s="18"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>144</v>
-      </c>
+      <c r="A39" s="18"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>144</v>
-      </c>
+      <c r="A40" s="18"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>144</v>
-      </c>
+      <c r="A41" s="18"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>182</v>
-      </c>
+      <c r="A42" s="18"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>144</v>
-      </c>
+      <c r="A43" s="20"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>100</v>
-      </c>
+      <c r="A44" s="16"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Plantillas/Base Maestra/Maestra.xlsx
+++ b/Plantillas/Base Maestra/Maestra.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D072E3-3F71-49D0-8AA9-6458F801316D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0A40A3-042C-4513-8248-E441D6677F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="6240" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="388">
   <si>
     <t>KeyPLU</t>
   </si>
@@ -1194,9 +1194,6 @@
   </si>
   <si>
     <t xml:space="preserve">	041069</t>
-  </si>
-  <si>
-    <t>ode</t>
   </si>
   <si>
     <t>Error en sistema</t>
@@ -1206,7 +1203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1244,14 +1241,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1411,7 +1400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1497,9 +1486,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1510,93 +1496,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -1790,6 +1690,75 @@
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1804,43 +1773,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Maestra" displayName="Maestra" ref="A1:H369" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Maestra" displayName="Maestra" ref="A1:H369" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:H369" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="8">
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="KeyPLU" dataDxfId="17">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="KeyPLU" dataDxfId="12">
       <calculatedColumnFormula>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CLIENTE" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SoldTO" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canal" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EAN" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GMID" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="PLU" dataDxfId="11"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CLIENTE" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SoldTO" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canal" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EAN" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GMID" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="PLU" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}" name="MR_8" displayName="MR_8" ref="A1:C44" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}" name="MR_8" displayName="MR_8" ref="A1:C44" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:C44" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9E916551-61FD-448A-B81B-5ADC55507D88}" name="Code" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{9566008B-5A00-4796-9B0E-602672187BF5}" name="Reason (shift)" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{85494BE8-8F70-4A24-AB4B-AE2EEF433E3E}" name="Definition" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{9E916551-61FD-448A-B81B-5ADC55507D88}" name="Code" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{9566008B-5A00-4796-9B0E-602672187BF5}" name="Reason (shift)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{85494BE8-8F70-4A24-AB4B-AE2EEF433E3E}" name="Definition" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C283A7A-442C-43A3-984C-CEFD22907B9A}" name="MR_7" displayName="MR_7" ref="A1:C44" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C283A7A-442C-43A3-984C-CEFD22907B9A}" name="MR_7" displayName="MR_7" ref="A1:C44" totalsRowShown="0" dataDxfId="18">
   <autoFilter ref="A1:C44" xr:uid="{6C283A7A-442C-43A3-984C-CEFD22907B9A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E2C9FFF9-ECC7-427D-8735-33E33790C3E9}" name="ode" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{83957DAE-DC52-4558-9499-0075AFBDD203}" name="Reason (shift)" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{8C5DC287-A9AC-47B8-B209-A750C1A41565}" name="Definition" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E2C9FFF9-ECC7-427D-8735-33E33790C3E9}" name="Code" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{83957DAE-DC52-4558-9499-0075AFBDD203}" name="Reason (shift)" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{8C5DC287-A9AC-47B8-B209-A750C1A41565}" name="Definition" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12603,376 +12572,376 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
+        <v>10</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="33" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="35">
-        <v>10</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="34" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="34" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="34" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="34" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="34" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="B32" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>100</v>
-      </c>
-    </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
+      <c r="A34" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" s="33" t="s">
         <v>100</v>
       </c>
     </row>

--- a/Plantillas/Base Maestra/Maestra.xlsx
+++ b/Plantillas/Base Maestra/Maestra.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0A40A3-042C-4513-8248-E441D6677F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFB7982-4B5F-43D0-BC43-10D6B37BF217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="6240" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="723">
   <si>
     <t>KeyPLU</t>
   </si>
@@ -1197,6 +1197,1011 @@
   </si>
   <si>
     <t>Error en sistema</t>
+  </si>
+  <si>
+    <t>1001786637703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001786633582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221176RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703381002146RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221800RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001786637591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001786633664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001786633664798071214RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221312RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001734993582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221176RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703381002146RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221800RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202221282RETAIL</t>
+  </si>
+  <si>
+    <t>1001734997703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001734993664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001735123582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221176RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703381002146RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127702605107407RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001735123664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001735127703202221244INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202221305INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202221312INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202221169INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127591044007191INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127591044009447INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127591044008952INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127501165007956INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127591044401036INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127591044009010INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202010329INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703381002146INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202221152INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127795312100090INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127702605107407INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202221381INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202221428INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127702771001561INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735127703202221282INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735123582910009900INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001735093664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221312RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221282RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221176RETAIL</t>
+  </si>
+  <si>
+    <t>1001735093664798069211RETAIL</t>
+  </si>
+  <si>
+    <t>1001735093582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097703202221800RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001735097591044008952INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097591044009010INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202010329INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097795312100090INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221428INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221381INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221244INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221091INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221312INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221305INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221275INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221282INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221169INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221152INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221176INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735093664798069211INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735093582910009900INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097702771001561INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097703202221800INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097591044401036INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097501165010444INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097591044009447INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735097591044007191INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>1001735077795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077706263600645RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077706263600621RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077706263600638RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221237RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202121230RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202121223RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202121292RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221176RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202121155RETAIL</t>
+  </si>
+  <si>
+    <t>1001735073582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077706263600072RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077703202221800RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001735077706263600775RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221237RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221312RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221282RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087706263200364RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087706263200388RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221176RETAIL</t>
+  </si>
+  <si>
+    <t>1001735083582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087703202221800RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087591044009225RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001735087591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221237RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001735103582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703381002146RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221282RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221312RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001735103664798067910RETAIL</t>
+  </si>
+  <si>
+    <t>1001735103664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001735107591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221312RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221282RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001735273664798069211RETAIL</t>
+  </si>
+  <si>
+    <t>1001735273664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001735273664798066531RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001735273582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221107RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001734673664798066531RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001734673664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221312RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221343RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221268RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221282RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221176RETAIL</t>
+  </si>
+  <si>
+    <t>1001734673582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677501165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001734677703202221107RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497591044009447RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497591044007191RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202010329RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497701165010444RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202003475RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497501165007956RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497591044008952RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221169RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221152RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703381002146RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497591044401036RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497591044009010RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221220RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221244RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221282RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221305RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221381RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221428RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221312RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221329RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221336RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497795312100090RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221091RETAIL</t>
+  </si>
+  <si>
+    <t>1001734493664798064728RETAIL</t>
+  </si>
+  <si>
+    <t>1001734493582910009900RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497702771001561RETAIL</t>
+  </si>
+  <si>
+    <t>1001734493664798066531RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221237RETAIL</t>
+  </si>
+  <si>
+    <t>1001735277703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001734497703202221275RETAIL</t>
+  </si>
+  <si>
+    <t>1001735103664798066531RETAIL</t>
   </si>
 </sst>
 </file>
@@ -1400,7 +2405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1492,11 +2497,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1648,16 +2669,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1774,30 +2785,27 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Maestra" displayName="Maestra" ref="A1:H369" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:H369" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="8">
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="KeyPLU" dataDxfId="12">
-      <calculatedColumnFormula>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CLIENTE" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SoldTO" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canal" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EAN" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GMID" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="PLU" dataDxfId="6"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="KeyPLU" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CLIENTE" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="SoldTO" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Canal" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EAN" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GMID" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="PLU" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}" name="MR_8" displayName="MR_8" ref="A1:C44" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}" name="MR_8" displayName="MR_8" ref="A1:C44" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A1:C44" xr:uid="{C34B2477-E8F3-4E66-8E12-8ED97703DC93}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9E916551-61FD-448A-B81B-5ADC55507D88}" name="Code" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{9566008B-5A00-4796-9B0E-602672187BF5}" name="Reason (shift)" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{85494BE8-8F70-4A24-AB4B-AE2EEF433E3E}" name="Definition" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9E916551-61FD-448A-B81B-5ADC55507D88}" name="Code" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{9566008B-5A00-4796-9B0E-602672187BF5}" name="Reason (shift)" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{85494BE8-8F70-4A24-AB4B-AE2EEF433E3E}" name="Definition" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2092,7 +3100,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2118,9 +3126,8 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221244Retail</v>
+      <c r="A2" s="35" t="s">
+        <v>388</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>8</v>
@@ -2145,9 +3152,8 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221220Retail</v>
+      <c r="A3" s="35" t="s">
+        <v>389</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>8</v>
@@ -2172,9 +3178,8 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221091Retail</v>
+      <c r="A4" s="35" t="s">
+        <v>390</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -2199,9 +3204,8 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221305Retail</v>
+      <c r="A5" s="35" t="s">
+        <v>391</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>8</v>
@@ -2226,9 +3230,8 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637501165007956Retail</v>
+      <c r="A6" s="35" t="s">
+        <v>392</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
@@ -2253,9 +3256,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221152Retail</v>
+      <c r="A7" s="35" t="s">
+        <v>393</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
@@ -2280,9 +3282,8 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637591044009010Retail</v>
+      <c r="A8" s="35" t="s">
+        <v>394</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
@@ -2307,9 +3308,8 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637702771001561Retail</v>
+      <c r="A9" s="35" t="s">
+        <v>395</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>8</v>
@@ -2334,9 +3334,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637501165010444Retail</v>
+      <c r="A10" s="35" t="s">
+        <v>396</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
@@ -2361,9 +3360,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221275Retail</v>
+      <c r="A11" s="35" t="s">
+        <v>397</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
@@ -2388,9 +3386,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221336Retail</v>
+      <c r="A12" s="35" t="s">
+        <v>398</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
@@ -2415,9 +3412,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786633582910009900Retail</v>
+      <c r="A13" s="35" t="s">
+        <v>399</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -2442,9 +3438,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202010329Retail</v>
+      <c r="A14" s="35" t="s">
+        <v>400</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>8</v>
@@ -2469,9 +3464,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637795312100090Retail</v>
+      <c r="A15" s="35" t="s">
+        <v>401</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>8</v>
@@ -2496,9 +3490,8 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221169Retail</v>
+      <c r="A16" s="35" t="s">
+        <v>402</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>8</v>
@@ -2523,9 +3516,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221176Retail</v>
+      <c r="A17" s="35" t="s">
+        <v>403</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
@@ -2550,9 +3542,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703381002146Retail</v>
+      <c r="A18" s="35" t="s">
+        <v>404</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
@@ -2577,9 +3568,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221800Retail</v>
+      <c r="A19" s="35" t="s">
+        <v>405</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>8</v>
@@ -2604,9 +3594,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221428Retail</v>
+      <c r="A20" s="35" t="s">
+        <v>406</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -2631,9 +3620,8 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637591044401036Retail</v>
+      <c r="A21" s="35" t="s">
+        <v>407</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>8</v>
@@ -2658,9 +3646,8 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221329Retail</v>
+      <c r="A22" s="35" t="s">
+        <v>408</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>8</v>
@@ -2685,9 +3672,8 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202003475Retail</v>
+      <c r="A23" s="35" t="s">
+        <v>409</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>8</v>
@@ -2712,9 +3698,8 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637703202221381Retail</v>
+      <c r="A24" s="35" t="s">
+        <v>410</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>8</v>
@@ -2739,9 +3724,8 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786637591044008952Retail</v>
+      <c r="A25" s="35" t="s">
+        <v>411</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>8</v>
@@ -2766,9 +3750,8 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786633664798064728Retail</v>
+      <c r="A26" s="35" t="s">
+        <v>412</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>8</v>
@@ -2793,9 +3776,8 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001786633664798071214Retail</v>
+      <c r="A27" s="35" t="s">
+        <v>413</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>8</v>
@@ -2820,9 +3802,8 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221244Retail</v>
+      <c r="A28" s="35" t="s">
+        <v>414</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>35</v>
@@ -2847,9 +3828,8 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221329Retail</v>
+      <c r="A29" s="35" t="s">
+        <v>415</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>35</v>
@@ -2874,9 +3854,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221305Retail</v>
+      <c r="A30" s="35" t="s">
+        <v>416</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>35</v>
@@ -2901,9 +3880,8 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221312Retail</v>
+      <c r="A31" s="35" t="s">
+        <v>417</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>35</v>
@@ -2928,9 +3906,8 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221169Retail</v>
+      <c r="A32" s="35" t="s">
+        <v>418</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>35</v>
@@ -2955,9 +3932,8 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044007191Retail</v>
+      <c r="A33" s="35" t="s">
+        <v>419</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>35</v>
@@ -2982,9 +3958,8 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044009447Retail</v>
+      <c r="A34" s="35" t="s">
+        <v>420</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>35</v>
@@ -3009,9 +3984,8 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221091Retail</v>
+      <c r="A35" s="35" t="s">
+        <v>421</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>35</v>
@@ -3036,9 +4010,8 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044008952Retail</v>
+      <c r="A36" s="35" t="s">
+        <v>422</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>35</v>
@@ -3063,9 +4036,8 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997501165007956Retail</v>
+      <c r="A37" s="35" t="s">
+        <v>423</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>35</v>
@@ -3090,9 +4062,8 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044401036Retail</v>
+      <c r="A38" s="35" t="s">
+        <v>424</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>35</v>
@@ -3117,9 +4088,8 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044009010Retail</v>
+      <c r="A39" s="35" t="s">
+        <v>425</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>35</v>
@@ -3144,9 +4114,8 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202010329Retail</v>
+      <c r="A40" s="35" t="s">
+        <v>426</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>35</v>
@@ -3171,9 +4140,8 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221220Retail</v>
+      <c r="A41" s="35" t="s">
+        <v>427</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>35</v>
@@ -3198,9 +4166,8 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221336Retail</v>
+      <c r="A42" s="35" t="s">
+        <v>428</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>35</v>
@@ -3225,9 +4192,8 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734993582910009900Retail</v>
+      <c r="A43" s="35" t="s">
+        <v>429</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>35</v>
@@ -3252,9 +4218,8 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221275Retail</v>
+      <c r="A44" s="35" t="s">
+        <v>430</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>35</v>
@@ -3279,9 +4244,8 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221176Retail</v>
+      <c r="A45" s="35" t="s">
+        <v>431</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>35</v>
@@ -3306,9 +4270,8 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703381002146Retail</v>
+      <c r="A46" s="35" t="s">
+        <v>432</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>35</v>
@@ -3333,9 +4296,8 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221152Retail</v>
+      <c r="A47" s="35" t="s">
+        <v>433</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>35</v>
@@ -3360,9 +4322,8 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997795312100090Retail</v>
+      <c r="A48" s="35" t="s">
+        <v>434</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>35</v>
@@ -3387,9 +4348,8 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221800Retail</v>
+      <c r="A49" s="35" t="s">
+        <v>435</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>35</v>
@@ -3414,9 +4374,8 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221381Retail</v>
+      <c r="A50" s="35" t="s">
+        <v>436</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>35</v>
@@ -3441,9 +4400,8 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221428Retail</v>
+      <c r="A51" s="35" t="s">
+        <v>437</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>35</v>
@@ -3468,9 +4426,8 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997702771001561Retail</v>
+      <c r="A52" s="35" t="s">
+        <v>438</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>35</v>
@@ -3495,9 +4452,8 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997501165010444Retail</v>
+      <c r="A53" s="35" t="s">
+        <v>439</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>35</v>
@@ -3522,9 +4478,8 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221282Retail</v>
+      <c r="A54" s="35" t="s">
+        <v>440</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>35</v>
@@ -3549,9 +4504,8 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202003475Retail</v>
+      <c r="A55" s="35" t="s">
+        <v>441</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>35</v>
@@ -3576,9 +4530,8 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734993664798064728Retail</v>
+      <c r="A56" s="35" t="s">
+        <v>442</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>35</v>
@@ -3603,9 +4556,8 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221244Retail</v>
+      <c r="A57" s="35" t="s">
+        <v>443</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>60</v>
@@ -3630,9 +4582,8 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221329Retail</v>
+      <c r="A58" s="35" t="s">
+        <v>444</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>60</v>
@@ -3657,9 +4608,8 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221305Retail</v>
+      <c r="A59" s="35" t="s">
+        <v>445</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>60</v>
@@ -3684,9 +4634,8 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221169Retail</v>
+      <c r="A60" s="35" t="s">
+        <v>446</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>60</v>
@@ -3711,9 +4660,8 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044007191Retail</v>
+      <c r="A61" s="35" t="s">
+        <v>447</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>60</v>
@@ -3738,9 +4686,8 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044009447Retail</v>
+      <c r="A62" s="35" t="s">
+        <v>448</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>60</v>
@@ -3765,9 +4712,8 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044008952Retail</v>
+      <c r="A63" s="35" t="s">
+        <v>449</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>60</v>
@@ -3792,9 +4738,8 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127501165007956Retail</v>
+      <c r="A64" s="35" t="s">
+        <v>450</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>60</v>
@@ -3819,9 +4764,8 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202003475Retail</v>
+      <c r="A65" s="35" t="s">
+        <v>451</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>60</v>
@@ -3846,9 +4790,8 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044401036Retail</v>
+      <c r="A66" s="35" t="s">
+        <v>452</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>60</v>
@@ -3873,9 +4816,8 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044009010Retail</v>
+      <c r="A67" s="35" t="s">
+        <v>453</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>60</v>
@@ -3900,9 +4842,8 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202010329Retail</v>
+      <c r="A68" s="35" t="s">
+        <v>454</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>60</v>
@@ -3927,9 +4868,8 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221220Retail</v>
+      <c r="A69" s="35" t="s">
+        <v>455</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>60</v>
@@ -3954,9 +4894,8 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221336Retail</v>
+      <c r="A70" s="35" t="s">
+        <v>456</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>60</v>
@@ -3981,9 +4920,8 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735123582910009900Retail</v>
+      <c r="A71" s="35" t="s">
+        <v>457</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>60</v>
@@ -4008,9 +4946,8 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221275Retail</v>
+      <c r="A72" s="35" t="s">
+        <v>458</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>60</v>
@@ -4035,9 +4972,8 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221176Retail</v>
+      <c r="A73" s="35" t="s">
+        <v>459</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>60</v>
@@ -4062,9 +4998,8 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703381002146Retail</v>
+      <c r="A74" s="35" t="s">
+        <v>460</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>60</v>
@@ -4089,9 +5024,8 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221152Retail</v>
+      <c r="A75" s="35" t="s">
+        <v>461</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>60</v>
@@ -4116,9 +5050,8 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127795312100090Retail</v>
+      <c r="A76" s="35" t="s">
+        <v>462</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>60</v>
@@ -4143,9 +5076,8 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127702605107407Retail</v>
+      <c r="A77" s="35" t="s">
+        <v>463</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>60</v>
@@ -4170,9 +5102,8 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221381Retail</v>
+      <c r="A78" s="35" t="s">
+        <v>464</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>60</v>
@@ -4197,9 +5128,8 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221428Retail</v>
+      <c r="A79" s="35" t="s">
+        <v>465</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>60</v>
@@ -4224,9 +5154,8 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127702771001561Retail</v>
+      <c r="A80" s="35" t="s">
+        <v>466</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>60</v>
@@ -4251,9 +5180,8 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127501165010444Retail</v>
+      <c r="A81" s="35" t="s">
+        <v>467</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>60</v>
@@ -4278,9 +5206,8 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735123664798064728Retail</v>
+      <c r="A82" s="35" t="s">
+        <v>468</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>60</v>
@@ -4305,9 +5232,8 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221244Institucional</v>
+      <c r="A83" s="35" t="s">
+        <v>469</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>60</v>
@@ -4332,9 +5258,8 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221305Institucional</v>
+      <c r="A84" s="35" t="s">
+        <v>470</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>60</v>
@@ -4359,9 +5284,8 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221312Institucional</v>
+      <c r="A85" s="35" t="s">
+        <v>471</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>60</v>
@@ -4386,9 +5310,8 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221169Institucional</v>
+      <c r="A86" s="35" t="s">
+        <v>472</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>60</v>
@@ -4413,9 +5336,8 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044007191Institucional</v>
+      <c r="A87" s="35" t="s">
+        <v>473</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>60</v>
@@ -4440,9 +5362,8 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044009447Institucional</v>
+      <c r="A88" s="35" t="s">
+        <v>474</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>60</v>
@@ -4467,9 +5388,8 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044008952Institucional</v>
+      <c r="A89" s="35" t="s">
+        <v>475</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>60</v>
@@ -4494,9 +5414,8 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127501165007956Institucional</v>
+      <c r="A90" s="35" t="s">
+        <v>476</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>60</v>
@@ -4521,9 +5440,8 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044401036Institucional</v>
+      <c r="A91" s="35" t="s">
+        <v>477</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>60</v>
@@ -4548,9 +5466,8 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127591044009010Institucional</v>
+      <c r="A92" s="35" t="s">
+        <v>478</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>60</v>
@@ -4575,9 +5492,8 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202010329Institucional</v>
+      <c r="A93" s="35" t="s">
+        <v>479</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>60</v>
@@ -4602,9 +5518,8 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703381002146Institucional</v>
+      <c r="A94" s="35" t="s">
+        <v>480</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>60</v>
@@ -4629,9 +5544,8 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221152Institucional</v>
+      <c r="A95" s="35" t="s">
+        <v>481</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>60</v>
@@ -4656,9 +5570,8 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127795312100090Institucional</v>
+      <c r="A96" s="35" t="s">
+        <v>482</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>60</v>
@@ -4683,9 +5596,8 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127702605107407Institucional</v>
+      <c r="A97" s="35" t="s">
+        <v>483</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>60</v>
@@ -4710,9 +5622,8 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221381Institucional</v>
+      <c r="A98" s="35" t="s">
+        <v>484</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>60</v>
@@ -4737,9 +5648,8 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221428Institucional</v>
+      <c r="A99" s="35" t="s">
+        <v>485</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>60</v>
@@ -4764,9 +5674,8 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127702771001561Institucional</v>
+      <c r="A100" s="35" t="s">
+        <v>486</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>60</v>
@@ -4791,9 +5700,8 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735127703202221282Institucional</v>
+      <c r="A101" s="35" t="s">
+        <v>487</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>60</v>
@@ -4818,9 +5726,8 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735123582910009900Institucional</v>
+      <c r="A102" s="35" t="s">
+        <v>488</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>60</v>
@@ -4845,9 +5752,8 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044008952Retail</v>
+      <c r="A103" s="35" t="s">
+        <v>489</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>176</v>
@@ -4872,9 +5778,8 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044009010Retail</v>
+      <c r="A104" s="35" t="s">
+        <v>490</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>176</v>
@@ -4899,9 +5804,8 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202010329Retail</v>
+      <c r="A105" s="35" t="s">
+        <v>491</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>176</v>
@@ -4926,9 +5830,8 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097795312100090Retail</v>
+      <c r="A106" s="35" t="s">
+        <v>492</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>176</v>
@@ -4953,9 +5856,8 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221220Retail</v>
+      <c r="A107" s="35" t="s">
+        <v>493</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>176</v>
@@ -4980,9 +5882,8 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221428Retail</v>
+      <c r="A108" s="35" t="s">
+        <v>494</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>176</v>
@@ -5007,9 +5908,8 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221381Retail</v>
+      <c r="A109" s="35" t="s">
+        <v>495</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>176</v>
@@ -5034,9 +5934,8 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735093664798064728Retail</v>
+      <c r="A110" s="35" t="s">
+        <v>496</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>176</v>
@@ -5061,9 +5960,8 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221244Retail</v>
+      <c r="A111" s="35" t="s">
+        <v>497</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>176</v>
@@ -5088,9 +5986,8 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221091Retail</v>
+      <c r="A112" s="35" t="s">
+        <v>498</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>176</v>
@@ -5115,9 +6012,8 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221305Retail</v>
+      <c r="A113" s="35" t="s">
+        <v>499</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>176</v>
@@ -5142,9 +6038,8 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221336Retail</v>
+      <c r="A114" s="35" t="s">
+        <v>500</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>176</v>
@@ -5169,9 +6064,8 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221312Retail</v>
+      <c r="A115" s="35" t="s">
+        <v>501</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>176</v>
@@ -5196,9 +6090,8 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221329Retail</v>
+      <c r="A116" s="35" t="s">
+        <v>502</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>176</v>
@@ -5223,9 +6116,8 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221275Retail</v>
+      <c r="A117" s="35" t="s">
+        <v>503</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>176</v>
@@ -5250,9 +6142,8 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221282Retail</v>
+      <c r="A118" s="35" t="s">
+        <v>504</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>176</v>
@@ -5277,9 +6168,8 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221169Retail</v>
+      <c r="A119" s="35" t="s">
+        <v>505</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>176</v>
@@ -5304,9 +6194,8 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221152Retail</v>
+      <c r="A120" s="35" t="s">
+        <v>506</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>176</v>
@@ -5331,9 +6220,8 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221176Retail</v>
+      <c r="A121" s="35" t="s">
+        <v>507</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>176</v>
@@ -5358,9 +6246,8 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735093664798069211Retail</v>
+      <c r="A122" s="35" t="s">
+        <v>508</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>176</v>
@@ -5385,9 +6272,8 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735093582910009900Retail</v>
+      <c r="A123" s="35" t="s">
+        <v>509</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>176</v>
@@ -5412,9 +6298,8 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097702771001561Retail</v>
+      <c r="A124" s="35" t="s">
+        <v>510</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>176</v>
@@ -5439,9 +6324,8 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097501165007956Retail</v>
+      <c r="A125" s="35" t="s">
+        <v>511</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>176</v>
@@ -5466,9 +6350,8 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202003475Retail</v>
+      <c r="A126" s="35" t="s">
+        <v>512</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>176</v>
@@ -5493,9 +6376,8 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221800Retail</v>
+      <c r="A127" s="35" t="s">
+        <v>513</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>176</v>
@@ -5520,9 +6402,8 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044401036Retail</v>
+      <c r="A128" s="35" t="s">
+        <v>514</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>176</v>
@@ -5547,9 +6428,8 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097501165010444Retail</v>
+      <c r="A129" s="35" t="s">
+        <v>515</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>176</v>
@@ -5574,9 +6454,8 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044009447Retail</v>
+      <c r="A130" s="35" t="s">
+        <v>516</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>176</v>
@@ -5601,9 +6480,8 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044007191Retail</v>
+      <c r="A131" s="35" t="s">
+        <v>517</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>176</v>
@@ -5628,9 +6506,8 @@
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044008952Institucional</v>
+      <c r="A132" s="35" t="s">
+        <v>518</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>176</v>
@@ -5655,9 +6532,8 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044009010Institucional</v>
+      <c r="A133" s="35" t="s">
+        <v>519</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>176</v>
@@ -5682,9 +6558,8 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202010329Institucional</v>
+      <c r="A134" s="35" t="s">
+        <v>520</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>176</v>
@@ -5709,9 +6584,8 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097795312100090Institucional</v>
+      <c r="A135" s="35" t="s">
+        <v>521</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>176</v>
@@ -5736,9 +6610,8 @@
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221428Institucional</v>
+      <c r="A136" s="35" t="s">
+        <v>522</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>176</v>
@@ -5763,9 +6636,8 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221381Institucional</v>
+      <c r="A137" s="35" t="s">
+        <v>523</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>176</v>
@@ -5790,9 +6662,8 @@
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221244Institucional</v>
+      <c r="A138" s="35" t="s">
+        <v>524</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>176</v>
@@ -5817,9 +6688,8 @@
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221091Institucional</v>
+      <c r="A139" s="35" t="s">
+        <v>525</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>176</v>
@@ -5844,9 +6714,8 @@
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221312Institucional</v>
+      <c r="A140" s="35" t="s">
+        <v>526</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>176</v>
@@ -5871,9 +6740,8 @@
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221305Institucional</v>
+      <c r="A141" s="35" t="s">
+        <v>527</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>176</v>
@@ -5898,9 +6766,8 @@
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221275Institucional</v>
+      <c r="A142" s="35" t="s">
+        <v>528</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>176</v>
@@ -5925,9 +6792,8 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221282Institucional</v>
+      <c r="A143" s="35" t="s">
+        <v>529</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>176</v>
@@ -5952,9 +6818,8 @@
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221169Institucional</v>
+      <c r="A144" s="35" t="s">
+        <v>530</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>176</v>
@@ -5979,9 +6844,8 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221152Institucional</v>
+      <c r="A145" s="35" t="s">
+        <v>531</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>176</v>
@@ -6006,9 +6870,8 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221176Institucional</v>
+      <c r="A146" s="35" t="s">
+        <v>532</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>176</v>
@@ -6033,9 +6896,8 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735093664798069211Institucional</v>
+      <c r="A147" s="35" t="s">
+        <v>533</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>176</v>
@@ -6060,9 +6922,8 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735093582910009900Institucional</v>
+      <c r="A148" s="35" t="s">
+        <v>534</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>176</v>
@@ -6087,9 +6948,8 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097702771001561Institucional</v>
+      <c r="A149" s="35" t="s">
+        <v>535</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>176</v>
@@ -6114,9 +6974,8 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097703202221800Institucional</v>
+      <c r="A150" s="35" t="s">
+        <v>536</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>176</v>
@@ -6141,9 +7000,8 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044401036Institucional</v>
+      <c r="A151" s="35" t="s">
+        <v>537</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>176</v>
@@ -6168,9 +7026,8 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097501165010444Institucional</v>
+      <c r="A152" s="35" t="s">
+        <v>538</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>176</v>
@@ -6195,9 +7052,8 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044009447Institucional</v>
+      <c r="A153" s="35" t="s">
+        <v>539</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>176</v>
@@ -6222,9 +7078,8 @@
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735097591044007191Institucional</v>
+      <c r="A154" s="35" t="s">
+        <v>540</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>176</v>
@@ -6249,9 +7104,8 @@
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077795312100090Retail</v>
+      <c r="A155" s="35" t="s">
+        <v>541</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>261</v>
@@ -6276,9 +7130,8 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077591044008952Retail</v>
+      <c r="A156" s="35" t="s">
+        <v>542</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>261</v>
@@ -6303,9 +7156,8 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077591044009010Retail</v>
+      <c r="A157" s="35" t="s">
+        <v>543</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>261</v>
@@ -6330,9 +7182,8 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202010329Retail</v>
+      <c r="A158" s="35" t="s">
+        <v>544</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>261</v>
@@ -6357,9 +7208,8 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077706263600645Retail</v>
+      <c r="A159" s="35" t="s">
+        <v>545</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>261</v>
@@ -6384,9 +7234,8 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077706263600621Retail</v>
+      <c r="A160" s="35" t="s">
+        <v>546</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>261</v>
@@ -6411,9 +7260,8 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077706263600638Retail</v>
+      <c r="A161" s="35" t="s">
+        <v>547</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>261</v>
@@ -6438,9 +7286,8 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221237Retail</v>
+      <c r="A162" s="35" t="s">
+        <v>548</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>261</v>
@@ -6465,9 +7312,8 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221428Retail</v>
+      <c r="A163" s="35" t="s">
+        <v>549</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>261</v>
@@ -6492,9 +7338,8 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221220Retail</v>
+      <c r="A164" s="35" t="s">
+        <v>550</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>261</v>
@@ -6519,9 +7364,8 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221381Retail</v>
+      <c r="A165" s="35" t="s">
+        <v>551</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>261</v>
@@ -6546,9 +7390,8 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202121230Retail</v>
+      <c r="A166" s="35" t="s">
+        <v>552</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>261</v>
@@ -6573,9 +7416,8 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202121223Retail</v>
+      <c r="A167" s="35" t="s">
+        <v>553</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>261</v>
@@ -6600,9 +7442,8 @@
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221244Retail</v>
+      <c r="A168" s="35" t="s">
+        <v>554</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>261</v>
@@ -6627,9 +7468,8 @@
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221091Retail</v>
+      <c r="A169" s="35" t="s">
+        <v>555</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>261</v>
@@ -6654,9 +7494,8 @@
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221336Retail</v>
+      <c r="A170" s="35" t="s">
+        <v>556</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>261</v>
@@ -6681,9 +7520,8 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221329Retail</v>
+      <c r="A171" s="35" t="s">
+        <v>557</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>261</v>
@@ -6708,9 +7546,8 @@
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221305Retail</v>
+      <c r="A172" s="35" t="s">
+        <v>558</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>261</v>
@@ -6735,9 +7572,8 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221275Retail</v>
+      <c r="A173" s="35" t="s">
+        <v>559</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>261</v>
@@ -6762,9 +7598,8 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202121292Retail</v>
+      <c r="A174" s="35" t="s">
+        <v>560</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>261</v>
@@ -6789,9 +7624,8 @@
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221169Retail</v>
+      <c r="A175" s="35" t="s">
+        <v>561</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>261</v>
@@ -6816,9 +7650,8 @@
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221152Retail</v>
+      <c r="A176" s="35" t="s">
+        <v>562</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>261</v>
@@ -6843,9 +7676,8 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221176Retail</v>
+      <c r="A177" s="35" t="s">
+        <v>563</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>261</v>
@@ -6870,9 +7702,8 @@
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202121155Retail</v>
+      <c r="A178" s="35" t="s">
+        <v>564</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>261</v>
@@ -6897,9 +7728,8 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735073582910009900Retail</v>
+      <c r="A179" s="35" t="s">
+        <v>565</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>261</v>
@@ -6924,9 +7754,8 @@
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077702771001561Retail</v>
+      <c r="A180" s="35" t="s">
+        <v>566</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>261</v>
@@ -6951,9 +7780,8 @@
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077706263600072Retail</v>
+      <c r="A181" s="35" t="s">
+        <v>567</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>261</v>
@@ -6978,9 +7806,8 @@
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202003475Retail</v>
+      <c r="A182" s="35" t="s">
+        <v>568</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>261</v>
@@ -7005,9 +7832,8 @@
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077501165007956Retail</v>
+      <c r="A183" s="35" t="s">
+        <v>569</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>261</v>
@@ -7032,9 +7858,8 @@
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077703202221800Retail</v>
+      <c r="A184" s="35" t="s">
+        <v>570</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>261</v>
@@ -7059,9 +7884,8 @@
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077591044401036Retail</v>
+      <c r="A185" s="35" t="s">
+        <v>571</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>261</v>
@@ -7086,9 +7910,8 @@
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077501165010444Retail</v>
+      <c r="A186" s="35" t="s">
+        <v>572</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>261</v>
@@ -7113,9 +7936,8 @@
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735077706263600775Retail</v>
+      <c r="A187" s="35" t="s">
+        <v>573</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>261</v>
@@ -7140,9 +7962,8 @@
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087591044008952Retail</v>
+      <c r="A188" s="35" t="s">
+        <v>574</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>260</v>
@@ -7167,9 +7988,8 @@
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087591044009010Retail</v>
+      <c r="A189" s="35" t="s">
+        <v>575</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>260</v>
@@ -7194,9 +8014,8 @@
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202010329Retail</v>
+      <c r="A190" s="35" t="s">
+        <v>576</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>260</v>
@@ -7221,9 +8040,8 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087795312100090Retail</v>
+      <c r="A191" s="35" t="s">
+        <v>577</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>260</v>
@@ -7248,9 +8066,8 @@
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221237Retail</v>
+      <c r="A192" s="35" t="s">
+        <v>578</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>260</v>
@@ -7275,9 +8092,8 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221428Retail</v>
+      <c r="A193" s="35" t="s">
+        <v>579</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>260</v>
@@ -7302,9 +8118,8 @@
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221220Retail</v>
+      <c r="A194" s="35" t="s">
+        <v>580</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>260</v>
@@ -7329,9 +8144,8 @@
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221381Retail</v>
+      <c r="A195" s="35" t="s">
+        <v>581</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>260</v>
@@ -7356,9 +8170,8 @@
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221244Retail</v>
+      <c r="A196" s="35" t="s">
+        <v>582</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>260</v>
@@ -7383,9 +8196,8 @@
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221312Retail</v>
+      <c r="A197" s="35" t="s">
+        <v>583</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>260</v>
@@ -7410,9 +8222,8 @@
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221329Retail</v>
+      <c r="A198" s="35" t="s">
+        <v>584</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>260</v>
@@ -7437,9 +8248,8 @@
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221305Retail</v>
+      <c r="A199" s="35" t="s">
+        <v>585</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>260</v>
@@ -7464,9 +8274,8 @@
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221275Retail</v>
+      <c r="A200" s="35" t="s">
+        <v>586</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>260</v>
@@ -7491,9 +8300,8 @@
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221282Retail</v>
+      <c r="A201" s="35" t="s">
+        <v>587</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>260</v>
@@ -7518,9 +8326,8 @@
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221091Retail</v>
+      <c r="A202" s="35" t="s">
+        <v>588</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>260</v>
@@ -7545,9 +8352,8 @@
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087706263200364Retail</v>
+      <c r="A203" s="35" t="s">
+        <v>589</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>260</v>
@@ -7572,9 +8378,8 @@
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087706263200388Retail</v>
+      <c r="A204" s="35" t="s">
+        <v>590</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>260</v>
@@ -7599,9 +8404,8 @@
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221169Retail</v>
+      <c r="A205" s="35" t="s">
+        <v>591</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>260</v>
@@ -7626,9 +8430,8 @@
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221152Retail</v>
+      <c r="A206" s="35" t="s">
+        <v>592</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>260</v>
@@ -7653,9 +8456,8 @@
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221176Retail</v>
+      <c r="A207" s="35" t="s">
+        <v>593</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>260</v>
@@ -7680,9 +8482,8 @@
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735083582910009900Retail</v>
+      <c r="A208" s="35" t="s">
+        <v>594</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>260</v>
@@ -7707,9 +8508,8 @@
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087702771001561Retail</v>
+      <c r="A209" s="35" t="s">
+        <v>595</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>260</v>
@@ -7734,9 +8534,8 @@
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202003475Retail</v>
+      <c r="A210" s="35" t="s">
+        <v>596</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>260</v>
@@ -7761,9 +8560,8 @@
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087501165007956Retail</v>
+      <c r="A211" s="35" t="s">
+        <v>597</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>260</v>
@@ -7788,9 +8586,8 @@
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087703202221800Retail</v>
+      <c r="A212" s="35" t="s">
+        <v>598</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>260</v>
@@ -7815,9 +8612,8 @@
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087591044401036Retail</v>
+      <c r="A213" s="35" t="s">
+        <v>599</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>260</v>
@@ -7842,9 +8638,8 @@
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087501165010444Retail</v>
+      <c r="A214" s="35" t="s">
+        <v>600</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>260</v>
@@ -7869,9 +8664,8 @@
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087591044009225Retail</v>
+      <c r="A215" s="35" t="s">
+        <v>601</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>260</v>
@@ -7896,9 +8690,8 @@
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087591044007191Retail</v>
+      <c r="A216" s="35" t="s">
+        <v>602</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>260</v>
@@ -7923,9 +8716,8 @@
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735087591044009447Retail</v>
+      <c r="A217" s="35" t="s">
+        <v>603</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>260</v>
@@ -7950,9 +8742,8 @@
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221275Retail</v>
+      <c r="A218" s="35" t="s">
+        <v>604</v>
       </c>
       <c r="B218" s="23" t="s">
         <v>292</v>
@@ -7977,9 +8768,8 @@
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221244Retail</v>
+      <c r="A219" s="35" t="s">
+        <v>414</v>
       </c>
       <c r="B219" s="23" t="s">
         <v>35</v>
@@ -8004,9 +8794,8 @@
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221329Retail</v>
+      <c r="A220" s="35" t="s">
+        <v>415</v>
       </c>
       <c r="B220" s="23" t="s">
         <v>35</v>
@@ -8031,9 +8820,8 @@
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A221" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221305Retail</v>
+      <c r="A221" s="35" t="s">
+        <v>416</v>
       </c>
       <c r="B221" s="23" t="s">
         <v>35</v>
@@ -8058,9 +8846,8 @@
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221312Retail</v>
+      <c r="A222" s="35" t="s">
+        <v>417</v>
       </c>
       <c r="B222" s="23" t="s">
         <v>35</v>
@@ -8085,9 +8872,8 @@
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221169Retail</v>
+      <c r="A223" s="35" t="s">
+        <v>418</v>
       </c>
       <c r="B223" s="23" t="s">
         <v>35</v>
@@ -8112,9 +8898,8 @@
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044007191Retail</v>
+      <c r="A224" s="35" t="s">
+        <v>419</v>
       </c>
       <c r="B224" s="23" t="s">
         <v>35</v>
@@ -8139,9 +8924,8 @@
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044009447Retail</v>
+      <c r="A225" s="35" t="s">
+        <v>420</v>
       </c>
       <c r="B225" s="23" t="s">
         <v>35</v>
@@ -8166,9 +8950,8 @@
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A226" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221091Retail</v>
+      <c r="A226" s="35" t="s">
+        <v>421</v>
       </c>
       <c r="B226" s="23" t="s">
         <v>35</v>
@@ -8193,9 +8976,8 @@
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044008952Retail</v>
+      <c r="A227" s="35" t="s">
+        <v>422</v>
       </c>
       <c r="B227" s="23" t="s">
         <v>35</v>
@@ -8220,9 +9002,8 @@
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A228" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997501165007956Retail</v>
+      <c r="A228" s="35" t="s">
+        <v>423</v>
       </c>
       <c r="B228" s="23" t="s">
         <v>35</v>
@@ -8247,9 +9028,8 @@
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044401036Retail</v>
+      <c r="A229" s="35" t="s">
+        <v>424</v>
       </c>
       <c r="B229" s="23" t="s">
         <v>35</v>
@@ -8274,9 +9054,8 @@
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997591044009010Retail</v>
+      <c r="A230" s="35" t="s">
+        <v>425</v>
       </c>
       <c r="B230" s="23" t="s">
         <v>35</v>
@@ -8301,9 +9080,8 @@
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A231" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202010329Retail</v>
+      <c r="A231" s="35" t="s">
+        <v>426</v>
       </c>
       <c r="B231" s="23" t="s">
         <v>35</v>
@@ -8328,9 +9106,8 @@
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A232" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221220Retail</v>
+      <c r="A232" s="35" t="s">
+        <v>427</v>
       </c>
       <c r="B232" s="23" t="s">
         <v>35</v>
@@ -8355,9 +9132,8 @@
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A233" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221336Retail</v>
+      <c r="A233" s="35" t="s">
+        <v>428</v>
       </c>
       <c r="B233" s="23" t="s">
         <v>35</v>
@@ -8382,9 +9158,8 @@
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A234" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734993582910009900Retail</v>
+      <c r="A234" s="35" t="s">
+        <v>429</v>
       </c>
       <c r="B234" s="23" t="s">
         <v>35</v>
@@ -8409,9 +9184,8 @@
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A235" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221275Retail</v>
+      <c r="A235" s="35" t="s">
+        <v>604</v>
       </c>
       <c r="B235" s="23" t="s">
         <v>292</v>
@@ -8436,9 +9210,8 @@
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A236" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221176Retail</v>
+      <c r="A236" s="35" t="s">
+        <v>431</v>
       </c>
       <c r="B236" s="23" t="s">
         <v>35</v>
@@ -8463,9 +9236,8 @@
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703381002146Retail</v>
+      <c r="A237" s="35" t="s">
+        <v>432</v>
       </c>
       <c r="B237" s="23" t="s">
         <v>35</v>
@@ -8490,9 +9262,8 @@
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A238" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221152Retail</v>
+      <c r="A238" s="35" t="s">
+        <v>433</v>
       </c>
       <c r="B238" s="23" t="s">
         <v>35</v>
@@ -8517,9 +9288,8 @@
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A239" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997795312100090Retail</v>
+      <c r="A239" s="35" t="s">
+        <v>434</v>
       </c>
       <c r="B239" s="23" t="s">
         <v>35</v>
@@ -8544,9 +9314,8 @@
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A240" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221800Retail</v>
+      <c r="A240" s="35" t="s">
+        <v>435</v>
       </c>
       <c r="B240" s="23" t="s">
         <v>35</v>
@@ -8571,9 +9340,8 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221381Retail</v>
+      <c r="A241" s="35" t="s">
+        <v>436</v>
       </c>
       <c r="B241" s="23" t="s">
         <v>35</v>
@@ -8598,9 +9366,8 @@
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221428Retail</v>
+      <c r="A242" s="35" t="s">
+        <v>437</v>
       </c>
       <c r="B242" s="23" t="s">
         <v>35</v>
@@ -8625,9 +9392,8 @@
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A243" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997702771001561Retail</v>
+      <c r="A243" s="35" t="s">
+        <v>438</v>
       </c>
       <c r="B243" s="23" t="s">
         <v>35</v>
@@ -8652,9 +9418,8 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997501165010444Retail</v>
+      <c r="A244" s="35" t="s">
+        <v>439</v>
       </c>
       <c r="B244" s="23" t="s">
         <v>35</v>
@@ -8679,9 +9444,8 @@
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221282Retail</v>
+      <c r="A245" s="35" t="s">
+        <v>440</v>
       </c>
       <c r="B245" s="23" t="s">
         <v>35</v>
@@ -8706,9 +9470,8 @@
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A246" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202003475Retail</v>
+      <c r="A246" s="35" t="s">
+        <v>441</v>
       </c>
       <c r="B246" s="23" t="s">
         <v>35</v>
@@ -8733,9 +9496,8 @@
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A247" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734993664798064728Retail</v>
+      <c r="A247" s="35" t="s">
+        <v>442</v>
       </c>
       <c r="B247" s="23" t="s">
         <v>35</v>
@@ -8760,9 +9522,8 @@
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A248" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221275Retail</v>
+      <c r="A248" s="35" t="s">
+        <v>605</v>
       </c>
       <c r="B248" s="23" t="s">
         <v>294</v>
@@ -8787,9 +9548,8 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107591044008952Retail</v>
+      <c r="A249" s="35" t="s">
+        <v>606</v>
       </c>
       <c r="B249" s="23" t="s">
         <v>294</v>
@@ -8814,9 +9574,8 @@
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A250" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107591044009010Retail</v>
+      <c r="A250" s="35" t="s">
+        <v>607</v>
       </c>
       <c r="B250" s="23" t="s">
         <v>294</v>
@@ -8841,9 +9600,8 @@
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A251" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107591044401036Retail</v>
+      <c r="A251" s="35" t="s">
+        <v>608</v>
       </c>
       <c r="B251" s="23" t="s">
         <v>294</v>
@@ -8868,9 +9626,8 @@
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A252" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107591044007191Retail</v>
+      <c r="A252" s="35" t="s">
+        <v>609</v>
       </c>
       <c r="B252" s="23" t="s">
         <v>294</v>
@@ -8895,9 +9652,8 @@
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A253" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221237Retail</v>
+      <c r="A253" s="35" t="s">
+        <v>610</v>
       </c>
       <c r="B253" s="23" t="s">
         <v>294</v>
@@ -8922,9 +9678,8 @@
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A254" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221220Retail</v>
+      <c r="A254" s="35" t="s">
+        <v>611</v>
       </c>
       <c r="B254" s="23" t="s">
         <v>294</v>
@@ -8949,9 +9704,8 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A255" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221091Retail</v>
+      <c r="A255" s="35" t="s">
+        <v>612</v>
       </c>
       <c r="B255" s="23" t="s">
         <v>294</v>
@@ -8976,9 +9730,8 @@
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A256" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221305Retail</v>
+      <c r="A256" s="35" t="s">
+        <v>613</v>
       </c>
       <c r="B256" s="23" t="s">
         <v>294</v>
@@ -9003,9 +9756,8 @@
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221244Retail</v>
+      <c r="A257" s="35" t="s">
+        <v>614</v>
       </c>
       <c r="B257" s="23" t="s">
         <v>294</v>
@@ -9030,9 +9782,8 @@
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221169Retail</v>
+      <c r="A258" s="35" t="s">
+        <v>615</v>
       </c>
       <c r="B258" s="23" t="s">
         <v>294</v>
@@ -9057,9 +9808,8 @@
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A259" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735103582910009900Retail</v>
+      <c r="A259" s="35" t="s">
+        <v>616</v>
       </c>
       <c r="B259" s="23" t="s">
         <v>294</v>
@@ -9084,9 +9834,8 @@
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A260" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221275Retail</v>
+      <c r="A260" s="35" t="s">
+        <v>605</v>
       </c>
       <c r="B260" s="23" t="s">
         <v>294</v>
@@ -9111,9 +9860,8 @@
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A261" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703381002146Retail</v>
+      <c r="A261" s="35" t="s">
+        <v>617</v>
       </c>
       <c r="B261" s="23" t="s">
         <v>294</v>
@@ -9138,9 +9886,8 @@
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A262" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221282Retail</v>
+      <c r="A262" s="35" t="s">
+        <v>618</v>
       </c>
       <c r="B262" s="23" t="s">
         <v>294</v>
@@ -9165,9 +9912,8 @@
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A263" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221152Retail</v>
+      <c r="A263" s="35" t="s">
+        <v>619</v>
       </c>
       <c r="B263" s="23" t="s">
         <v>294</v>
@@ -9192,9 +9938,8 @@
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A264" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107795312100090Retail</v>
+      <c r="A264" s="35" t="s">
+        <v>620</v>
       </c>
       <c r="B264" s="23" t="s">
         <v>294</v>
@@ -9219,9 +9964,8 @@
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A265" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202010329Retail</v>
+      <c r="A265" s="35" t="s">
+        <v>621</v>
       </c>
       <c r="B265" s="23" t="s">
         <v>294</v>
@@ -9246,9 +9990,8 @@
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A266" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107501165007956Retail</v>
+      <c r="A266" s="35" t="s">
+        <v>622</v>
       </c>
       <c r="B266" s="23" t="s">
         <v>294</v>
@@ -9273,9 +10016,8 @@
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A267" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221428Retail</v>
+      <c r="A267" s="35" t="s">
+        <v>623</v>
       </c>
       <c r="B267" s="23" t="s">
         <v>294</v>
@@ -9300,9 +10042,8 @@
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A268" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221381Retail</v>
+      <c r="A268" s="35" t="s">
+        <v>624</v>
       </c>
       <c r="B268" s="23" t="s">
         <v>294</v>
@@ -9327,9 +10068,8 @@
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A269" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107702771001561Retail</v>
+      <c r="A269" s="35" t="s">
+        <v>625</v>
       </c>
       <c r="B269" s="23" t="s">
         <v>294</v>
@@ -9354,9 +10094,8 @@
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A270" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107501165010444Retail</v>
+      <c r="A270" s="35" t="s">
+        <v>626</v>
       </c>
       <c r="B270" s="23" t="s">
         <v>294</v>
@@ -9381,9 +10120,8 @@
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A271" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221312Retail</v>
+      <c r="A271" s="35" t="s">
+        <v>627</v>
       </c>
       <c r="B271" s="23" t="s">
         <v>294</v>
@@ -9408,9 +10146,8 @@
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A272" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221329Retail</v>
+      <c r="A272" s="35" t="s">
+        <v>628</v>
       </c>
       <c r="B272" s="23" t="s">
         <v>294</v>
@@ -9435,9 +10172,8 @@
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A273" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202221336Retail</v>
+      <c r="A273" s="35" t="s">
+        <v>629</v>
       </c>
       <c r="B273" s="23" t="s">
         <v>294</v>
@@ -9462,9 +10198,8 @@
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A274" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107703202003475Retail</v>
+      <c r="A274" s="35" t="s">
+        <v>630</v>
       </c>
       <c r="B274" s="23" t="s">
         <v>294</v>
@@ -9489,9 +10224,8 @@
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A275" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735103664798067910Retail</v>
+      <c r="A275" s="35" t="s">
+        <v>631</v>
       </c>
       <c r="B275" s="23" t="s">
         <v>294</v>
@@ -9516,9 +10250,8 @@
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A276" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735103664798064728Retail</v>
+      <c r="A276" s="35" t="s">
+        <v>632</v>
       </c>
       <c r="B276" s="23" t="s">
         <v>294</v>
@@ -9543,9 +10276,8 @@
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A277" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735107591044009447Retail</v>
+      <c r="A277" s="35" t="s">
+        <v>633</v>
       </c>
       <c r="B277" s="23" t="s">
         <v>294</v>
@@ -9570,9 +10302,8 @@
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A278" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221220Retail</v>
+      <c r="A278" s="35" t="s">
+        <v>634</v>
       </c>
       <c r="B278" s="23" t="s">
         <v>324</v>
@@ -9597,9 +10328,8 @@
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A279" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221428Retail</v>
+      <c r="A279" s="35" t="s">
+        <v>635</v>
       </c>
       <c r="B279" s="23" t="s">
         <v>324</v>
@@ -9624,9 +10354,8 @@
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A280" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221381Retail</v>
+      <c r="A280" s="35" t="s">
+        <v>636</v>
       </c>
       <c r="B280" s="23" t="s">
         <v>324</v>
@@ -9651,9 +10380,8 @@
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A281" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221305Retail</v>
+      <c r="A281" s="35" t="s">
+        <v>637</v>
       </c>
       <c r="B281" s="23" t="s">
         <v>324</v>
@@ -9678,9 +10406,8 @@
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A282" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221336Retail</v>
+      <c r="A282" s="35" t="s">
+        <v>638</v>
       </c>
       <c r="B282" s="23" t="s">
         <v>324</v>
@@ -9705,9 +10432,8 @@
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A283" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221329Retail</v>
+      <c r="A283" s="35" t="s">
+        <v>639</v>
       </c>
       <c r="B283" s="23" t="s">
         <v>324</v>
@@ -9732,9 +10458,8 @@
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A284" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221312Retail</v>
+      <c r="A284" s="35" t="s">
+        <v>640</v>
       </c>
       <c r="B284" s="23" t="s">
         <v>324</v>
@@ -9759,9 +10484,8 @@
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A285" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734997703202221275Retail</v>
+      <c r="A285" s="35" t="s">
+        <v>430</v>
       </c>
       <c r="B285" s="23" t="s">
         <v>35</v>
@@ -9786,9 +10510,8 @@
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A286" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221282Retail</v>
+      <c r="A286" s="35" t="s">
+        <v>641</v>
       </c>
       <c r="B286" s="23" t="s">
         <v>324</v>
@@ -9813,9 +10536,8 @@
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A287" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221244Retail</v>
+      <c r="A287" s="35" t="s">
+        <v>642</v>
       </c>
       <c r="B287" s="23" t="s">
         <v>324</v>
@@ -9840,9 +10562,8 @@
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A288" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221169Retail</v>
+      <c r="A288" s="35" t="s">
+        <v>643</v>
       </c>
       <c r="B288" s="23" t="s">
         <v>324</v>
@@ -9867,9 +10588,8 @@
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A289" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221152Retail</v>
+      <c r="A289" s="35" t="s">
+        <v>644</v>
       </c>
       <c r="B289" s="23" t="s">
         <v>324</v>
@@ -9894,9 +10614,8 @@
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A290" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735273664798069211Retail</v>
+      <c r="A290" s="35" t="s">
+        <v>645</v>
       </c>
       <c r="B290" s="23" t="s">
         <v>324</v>
@@ -9921,9 +10640,8 @@
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A291" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735273664798064728Retail</v>
+      <c r="A291" s="35" t="s">
+        <v>646</v>
       </c>
       <c r="B291" s="23" t="s">
         <v>324</v>
@@ -9948,9 +10666,8 @@
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A292" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735273664798066531Retail</v>
+      <c r="A292" s="35" t="s">
+        <v>647</v>
       </c>
       <c r="B292" s="23" t="s">
         <v>324</v>
@@ -9975,9 +10692,8 @@
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A293" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202010329Retail</v>
+      <c r="A293" s="35" t="s">
+        <v>648</v>
       </c>
       <c r="B293" s="23" t="s">
         <v>324</v>
@@ -10002,9 +10718,8 @@
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A294" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277591044009010Retail</v>
+      <c r="A294" s="35" t="s">
+        <v>649</v>
       </c>
       <c r="B294" s="23" t="s">
         <v>324</v>
@@ -10029,9 +10744,8 @@
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A295" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277591044008952Retail</v>
+      <c r="A295" s="35" t="s">
+        <v>650</v>
       </c>
       <c r="B295" s="23" t="s">
         <v>324</v>
@@ -10056,9 +10770,8 @@
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A296" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277795312100090Retail</v>
+      <c r="A296" s="35" t="s">
+        <v>651</v>
       </c>
       <c r="B296" s="23" t="s">
         <v>324</v>
@@ -10083,9 +10796,8 @@
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A297" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277591044009447Retail</v>
+      <c r="A297" s="35" t="s">
+        <v>652</v>
       </c>
       <c r="B297" s="23" t="s">
         <v>324</v>
@@ -10110,9 +10822,8 @@
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A298" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277591044007191Retail</v>
+      <c r="A298" s="35" t="s">
+        <v>653</v>
       </c>
       <c r="B298" s="23" t="s">
         <v>324</v>
@@ -10137,9 +10848,8 @@
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A299" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735273582910009900Retail</v>
+      <c r="A299" s="35" t="s">
+        <v>654</v>
       </c>
       <c r="B299" s="23" t="s">
         <v>324</v>
@@ -10164,9 +10874,8 @@
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A300" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277501165007956Retail</v>
+      <c r="A300" s="35" t="s">
+        <v>655</v>
       </c>
       <c r="B300" s="23" t="s">
         <v>324</v>
@@ -10191,9 +10900,8 @@
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A301" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277591044401036Retail</v>
+      <c r="A301" s="35" t="s">
+        <v>656</v>
       </c>
       <c r="B301" s="23" t="s">
         <v>324</v>
@@ -10218,9 +10926,8 @@
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277501165010444Retail</v>
+      <c r="A302" s="35" t="s">
+        <v>657</v>
       </c>
       <c r="B302" s="23" t="s">
         <v>324</v>
@@ -10245,9 +10952,8 @@
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A303" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221091Retail</v>
+      <c r="A303" s="35" t="s">
+        <v>658</v>
       </c>
       <c r="B303" s="23" t="s">
         <v>324</v>
@@ -10272,9 +10978,8 @@
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A304" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277702771001561Retail</v>
+      <c r="A304" s="35" t="s">
+        <v>659</v>
       </c>
       <c r="B304" s="23" t="s">
         <v>324</v>
@@ -10299,9 +11004,8 @@
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A305" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202003475Retail</v>
+      <c r="A305" s="35" t="s">
+        <v>660</v>
       </c>
       <c r="B305" s="23" t="s">
         <v>324</v>
@@ -10326,9 +11030,8 @@
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A306" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221107Retail</v>
+      <c r="A306" s="35" t="s">
+        <v>661</v>
       </c>
       <c r="B306" s="23" t="s">
         <v>324</v>
@@ -10353,9 +11056,8 @@
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A307" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677591044008952Retail</v>
+      <c r="A307" s="35" t="s">
+        <v>662</v>
       </c>
       <c r="B307" s="23" t="s">
         <v>292</v>
@@ -10380,9 +11082,8 @@
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A308" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734673664798066531Retail</v>
+      <c r="A308" s="35" t="s">
+        <v>663</v>
       </c>
       <c r="B308" s="23" t="s">
         <v>292</v>
@@ -10407,9 +11108,8 @@
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A309" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677591044009010Retail</v>
+      <c r="A309" s="35" t="s">
+        <v>664</v>
       </c>
       <c r="B309" s="23" t="s">
         <v>292</v>
@@ -10434,9 +11134,8 @@
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A310" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202010329Retail</v>
+      <c r="A310" s="35" t="s">
+        <v>665</v>
       </c>
       <c r="B310" s="23" t="s">
         <v>292</v>
@@ -10461,9 +11160,8 @@
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A311" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677795312100090Retail</v>
+      <c r="A311" s="35" t="s">
+        <v>666</v>
       </c>
       <c r="B311" s="23" t="s">
         <v>292</v>
@@ -10488,9 +11186,8 @@
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A312" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221428Retail</v>
+      <c r="A312" s="35" t="s">
+        <v>667</v>
       </c>
       <c r="B312" s="23" t="s">
         <v>292</v>
@@ -10515,9 +11212,8 @@
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A313" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221220Retail</v>
+      <c r="A313" s="35" t="s">
+        <v>668</v>
       </c>
       <c r="B313" s="23" t="s">
         <v>292</v>
@@ -10542,9 +11238,8 @@
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A314" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221381Retail</v>
+      <c r="A314" s="35" t="s">
+        <v>669</v>
       </c>
       <c r="B314" s="23" t="s">
         <v>292</v>
@@ -10569,9 +11264,8 @@
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A315" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734673664798064728Retail</v>
+      <c r="A315" s="35" t="s">
+        <v>670</v>
       </c>
       <c r="B315" s="23" t="s">
         <v>292</v>
@@ -10596,9 +11290,8 @@
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A316" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221244Retail</v>
+      <c r="A316" s="35" t="s">
+        <v>671</v>
       </c>
       <c r="B316" s="23" t="s">
         <v>292</v>
@@ -10623,9 +11316,8 @@
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A317" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221336Retail</v>
+      <c r="A317" s="35" t="s">
+        <v>672</v>
       </c>
       <c r="B317" s="23" t="s">
         <v>292</v>
@@ -10650,9 +11342,8 @@
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A318" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221312Retail</v>
+      <c r="A318" s="35" t="s">
+        <v>673</v>
       </c>
       <c r="B318" s="23" t="s">
         <v>292</v>
@@ -10677,9 +11368,8 @@
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A319" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221329Retail</v>
+      <c r="A319" s="35" t="s">
+        <v>674</v>
       </c>
       <c r="B319" s="23" t="s">
         <v>292</v>
@@ -10704,9 +11394,8 @@
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A320" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221343Retail</v>
+      <c r="A320" s="35" t="s">
+        <v>675</v>
       </c>
       <c r="B320" s="23" t="s">
         <v>292</v>
@@ -10731,9 +11420,8 @@
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A321" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221305Retail</v>
+      <c r="A321" s="35" t="s">
+        <v>676</v>
       </c>
       <c r="B321" s="23" t="s">
         <v>292</v>
@@ -10758,9 +11446,8 @@
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A322" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221268Retail</v>
+      <c r="A322" s="35" t="s">
+        <v>677</v>
       </c>
       <c r="B322" s="23" t="s">
         <v>292</v>
@@ -10785,9 +11472,8 @@
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A323" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221282Retail</v>
+      <c r="A323" s="35" t="s">
+        <v>678</v>
       </c>
       <c r="B323" s="23" t="s">
         <v>292</v>
@@ -10812,9 +11498,8 @@
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A324" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221091Retail</v>
+      <c r="A324" s="35" t="s">
+        <v>679</v>
       </c>
       <c r="B324" s="23" t="s">
         <v>292</v>
@@ -10839,9 +11524,8 @@
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A325" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221169Retail</v>
+      <c r="A325" s="35" t="s">
+        <v>680</v>
       </c>
       <c r="B325" s="23" t="s">
         <v>292</v>
@@ -10866,9 +11550,8 @@
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A326" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221152Retail</v>
+      <c r="A326" s="35" t="s">
+        <v>681</v>
       </c>
       <c r="B326" s="23" t="s">
         <v>292</v>
@@ -10893,9 +11576,8 @@
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A327" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221176Retail</v>
+      <c r="A327" s="35" t="s">
+        <v>682</v>
       </c>
       <c r="B327" s="23" t="s">
         <v>292</v>
@@ -10920,9 +11602,8 @@
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A328" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734673582910009900Retail</v>
+      <c r="A328" s="35" t="s">
+        <v>683</v>
       </c>
       <c r="B328" s="23" t="s">
         <v>292</v>
@@ -10947,9 +11628,8 @@
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A329" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677702771001561Retail</v>
+      <c r="A329" s="35" t="s">
+        <v>684</v>
       </c>
       <c r="B329" s="23" t="s">
         <v>292</v>
@@ -10974,9 +11654,8 @@
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A330" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202003475Retail</v>
+      <c r="A330" s="35" t="s">
+        <v>685</v>
       </c>
       <c r="B330" s="23" t="s">
         <v>292</v>
@@ -11001,9 +11680,8 @@
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A331" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677501165007956Retail</v>
+      <c r="A331" s="35" t="s">
+        <v>686</v>
       </c>
       <c r="B331" s="23" t="s">
         <v>292</v>
@@ -11028,9 +11706,8 @@
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A332" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677591044401036Retail</v>
+      <c r="A332" s="35" t="s">
+        <v>687</v>
       </c>
       <c r="B332" s="23" t="s">
         <v>292</v>
@@ -11055,9 +11732,8 @@
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A333" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677591044009447Retail</v>
+      <c r="A333" s="35" t="s">
+        <v>688</v>
       </c>
       <c r="B333" s="23" t="s">
         <v>292</v>
@@ -11082,9 +11758,8 @@
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A334" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677591044007191Retail</v>
+      <c r="A334" s="35" t="s">
+        <v>689</v>
       </c>
       <c r="B334" s="23" t="s">
         <v>292</v>
@@ -11109,9 +11784,8 @@
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A335" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677501165010444Retail</v>
+      <c r="A335" s="35" t="s">
+        <v>690</v>
       </c>
       <c r="B335" s="23" t="s">
         <v>292</v>
@@ -11136,9 +11810,8 @@
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A336" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734677703202221107Retail</v>
+      <c r="A336" s="35" t="s">
+        <v>691</v>
       </c>
       <c r="B336" s="23" t="s">
         <v>292</v>
@@ -11163,9 +11836,8 @@
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A337" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497591044009447Retail</v>
+      <c r="A337" s="35" t="s">
+        <v>692</v>
       </c>
       <c r="B337" s="23" t="s">
         <v>384</v>
@@ -11190,9 +11862,8 @@
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A338" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497591044007191Retail</v>
+      <c r="A338" s="35" t="s">
+        <v>693</v>
       </c>
       <c r="B338" s="23" t="s">
         <v>384</v>
@@ -11217,9 +11888,8 @@
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A339" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202010329Retail</v>
+      <c r="A339" s="35" t="s">
+        <v>694</v>
       </c>
       <c r="B339" s="23" t="s">
         <v>384</v>
@@ -11244,9 +11914,8 @@
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A340" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497701165010444Retail</v>
+      <c r="A340" s="35" t="s">
+        <v>695</v>
       </c>
       <c r="B340" s="23" t="s">
         <v>384</v>
@@ -11271,9 +11940,8 @@
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A341" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202003475Retail</v>
+      <c r="A341" s="35" t="s">
+        <v>696</v>
       </c>
       <c r="B341" s="23" t="s">
         <v>384</v>
@@ -11298,9 +11966,8 @@
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A342" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497501165007956Retail</v>
+      <c r="A342" s="35" t="s">
+        <v>697</v>
       </c>
       <c r="B342" s="23" t="s">
         <v>384</v>
@@ -11325,9 +11992,8 @@
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A343" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497591044008952Retail</v>
+      <c r="A343" s="35" t="s">
+        <v>698</v>
       </c>
       <c r="B343" s="23" t="s">
         <v>384</v>
@@ -11352,9 +12018,8 @@
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A344" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221169Retail</v>
+      <c r="A344" s="35" t="s">
+        <v>699</v>
       </c>
       <c r="B344" s="23" t="s">
         <v>384</v>
@@ -11379,9 +12044,8 @@
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A345" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221152Retail</v>
+      <c r="A345" s="35" t="s">
+        <v>700</v>
       </c>
       <c r="B345" s="23" t="s">
         <v>384</v>
@@ -11406,9 +12070,8 @@
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A346" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703381002146Retail</v>
+      <c r="A346" s="35" t="s">
+        <v>701</v>
       </c>
       <c r="B346" s="23" t="s">
         <v>384</v>
@@ -11433,9 +12096,8 @@
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A347" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497591044401036Retail</v>
+      <c r="A347" s="35" t="s">
+        <v>702</v>
       </c>
       <c r="B347" s="23" t="s">
         <v>384</v>
@@ -11460,9 +12122,8 @@
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A348" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497591044009010Retail</v>
+      <c r="A348" s="35" t="s">
+        <v>703</v>
       </c>
       <c r="B348" s="23" t="s">
         <v>384</v>
@@ -11487,9 +12148,8 @@
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A349" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221220Retail</v>
+      <c r="A349" s="35" t="s">
+        <v>704</v>
       </c>
       <c r="B349" s="23" t="s">
         <v>384</v>
@@ -11514,9 +12174,8 @@
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A350" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221244Retail</v>
+      <c r="A350" s="35" t="s">
+        <v>705</v>
       </c>
       <c r="B350" s="23" t="s">
         <v>384</v>
@@ -11541,9 +12200,8 @@
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A351" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221282Retail</v>
+      <c r="A351" s="35" t="s">
+        <v>706</v>
       </c>
       <c r="B351" s="23" t="s">
         <v>384</v>
@@ -11568,9 +12226,8 @@
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A352" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221305Retail</v>
+      <c r="A352" s="35" t="s">
+        <v>707</v>
       </c>
       <c r="B352" s="23" t="s">
         <v>384</v>
@@ -11595,9 +12252,8 @@
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A353" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221381Retail</v>
+      <c r="A353" s="35" t="s">
+        <v>708</v>
       </c>
       <c r="B353" s="23" t="s">
         <v>384</v>
@@ -11622,9 +12278,8 @@
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A354" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221428Retail</v>
+      <c r="A354" s="35" t="s">
+        <v>709</v>
       </c>
       <c r="B354" s="23" t="s">
         <v>384</v>
@@ -11649,9 +12304,8 @@
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A355" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221312Retail</v>
+      <c r="A355" s="35" t="s">
+        <v>710</v>
       </c>
       <c r="B355" s="23" t="s">
         <v>384</v>
@@ -11676,9 +12330,8 @@
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A356" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221329Retail</v>
+      <c r="A356" s="35" t="s">
+        <v>711</v>
       </c>
       <c r="B356" s="23" t="s">
         <v>384</v>
@@ -11703,9 +12356,8 @@
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A357" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221336Retail</v>
+      <c r="A357" s="35" t="s">
+        <v>712</v>
       </c>
       <c r="B357" s="23" t="s">
         <v>384</v>
@@ -11730,9 +12382,8 @@
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A358" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497795312100090Retail</v>
+      <c r="A358" s="35" t="s">
+        <v>713</v>
       </c>
       <c r="B358" s="23" t="s">
         <v>384</v>
@@ -11757,9 +12408,8 @@
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A359" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221091Retail</v>
+      <c r="A359" s="35" t="s">
+        <v>714</v>
       </c>
       <c r="B359" s="23" t="s">
         <v>384</v>
@@ -11784,9 +12434,8 @@
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A360" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734493664798064728Retail</v>
+      <c r="A360" s="35" t="s">
+        <v>715</v>
       </c>
       <c r="B360" s="23" t="s">
         <v>384</v>
@@ -11811,9 +12460,8 @@
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A361" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734493582910009900Retail</v>
+      <c r="A361" s="35" t="s">
+        <v>716</v>
       </c>
       <c r="B361" s="23" t="s">
         <v>384</v>
@@ -11838,9 +12486,8 @@
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A362" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497702771001561Retail</v>
+      <c r="A362" s="35" t="s">
+        <v>717</v>
       </c>
       <c r="B362" s="23" t="s">
         <v>384</v>
@@ -11865,9 +12512,8 @@
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A363" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734493664798066531Retail</v>
+      <c r="A363" s="35" t="s">
+        <v>718</v>
       </c>
       <c r="B363" s="23" t="s">
         <v>384</v>
@@ -11892,9 +12538,8 @@
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A364" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221237Retail</v>
+      <c r="A364" s="35" t="s">
+        <v>719</v>
       </c>
       <c r="B364" s="23" t="s">
         <v>324</v>
@@ -11919,9 +12564,8 @@
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A365" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221275Retail</v>
+      <c r="A365" s="35" t="s">
+        <v>720</v>
       </c>
       <c r="B365" s="23" t="s">
         <v>324</v>
@@ -11946,9 +12590,8 @@
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A366" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735277703202221275Retail</v>
+      <c r="A366" s="35" t="s">
+        <v>720</v>
       </c>
       <c r="B366" s="23" t="s">
         <v>324</v>
@@ -11973,9 +12616,8 @@
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A367" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221275Retail</v>
+      <c r="A367" s="35" t="s">
+        <v>721</v>
       </c>
       <c r="B367" s="23" t="s">
         <v>384</v>
@@ -12000,9 +12642,8 @@
       </c>
     </row>
     <row r="368" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001734497703202221275Retail</v>
+      <c r="A368" s="35" t="s">
+        <v>721</v>
       </c>
       <c r="B368" s="23" t="s">
         <v>384</v>
@@ -12027,9 +12668,8 @@
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A369" s="3" t="str">
-        <f>+Maestra[[#This Row],[SoldTO]]&amp;Maestra[[#This Row],[EAN]]&amp;Maestra[[#This Row],[Canal]]</f>
-        <v>1001735103664798066531Retail</v>
+      <c r="A369" s="35" t="s">
+        <v>722</v>
       </c>
       <c r="B369" s="28" t="s">
         <v>294</v>
